--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10250,7 +10250,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 16/07/2026 20:32 UTC</t>
+          <t>Generado: 17/07/2026 14:25 UTC</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-16T20:32:41+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-07-17T14:25:30+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G8" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G13" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -17,8 +17,11 @@
     <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Metodología y fuentes" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Control de actualizaciones" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -144,6 +147,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="FF6C6F6A"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -152,12 +161,6 @@
       <name val="Calibri"/>
       <color rgb="FF161A1D"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF6C6F6A"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -645,13 +648,13 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -681,13 +684,13 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -10228,7 +10231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10250,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 17/07/2026 14:25 UTC</t>
+          <t>Generado: 20/07/2026 01:40 UTC</t>
         </is>
       </c>
     </row>
@@ -10459,45 +10462,43 @@
     <row r="10">
       <c r="A10" s="65" t="inlineStr">
         <is>
-          <t>Inversión Extranjera Directa (IED)</t>
+          <t>Tasa de desocupación nacional</t>
         </is>
       </c>
       <c r="B10" s="65" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
         </is>
       </c>
       <c r="C10" s="65" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensual</t>
         </is>
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>1T-26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="E10" s="65" t="n">
-        <v>23590.62204554513</v>
-      </c>
-      <c r="F10" s="65" t="n">
-        <v>1705.227100742525</v>
-      </c>
+        <v>0.027</v>
+      </c>
+      <c r="F10" s="65" t="n"/>
       <c r="G10" s="65" t="inlineStr">
         <is>
-          <t>Millones de dólares</t>
+          <t>Porcentaje de la PEA</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="64" t="inlineStr">
         <is>
-          <t>Tasa de desocupación nacional</t>
+          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
         </is>
       </c>
       <c r="B11" s="64" t="inlineStr">
         <is>
-          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
+          <t>INEGI</t>
         </is>
       </c>
       <c r="C11" s="64" t="inlineStr">
@@ -10511,19 +10512,21 @@
         </is>
       </c>
       <c r="E11" s="64" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="F11" s="64" t="n"/>
+        <v>3.94</v>
+      </c>
+      <c r="F11" s="64" t="n">
+        <v>4.19</v>
+      </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
-          <t>Porcentaje de la PEA</t>
+          <t>Variación anual (%)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="65" t="inlineStr">
         <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
+          <t>Indicador Mensual de Consumo Privado</t>
         </is>
       </c>
       <c r="B12" s="65" t="inlineStr">
@@ -10538,25 +10541,25 @@
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Mar 26 P</t>
         </is>
       </c>
       <c r="E12" s="65" t="n">
-        <v>3.94</v>
+        <v>113.5132947678</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>4.19</v>
+        <v>0.0867002724360284</v>
       </c>
       <c r="G12" s="65" t="inlineStr">
         <is>
-          <t>Variación anual (%)</t>
+          <t>Índice base 2018=100</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="64" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Consumo Privado</t>
+          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
         </is>
       </c>
       <c r="B13" s="64" t="inlineStr">
@@ -10569,34 +10572,184 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="D13" s="64" t="inlineStr">
-        <is>
-          <t>Mar 26 P</t>
-        </is>
-      </c>
-      <c r="E13" s="64" t="n">
-        <v>113.5132947678</v>
-      </c>
-      <c r="F13" s="64" t="n">
-        <v>0.0867002724360284</v>
-      </c>
+      <c r="D13" s="64" t="n"/>
+      <c r="E13" s="64" t="n"/>
+      <c r="F13" s="64" t="n"/>
       <c r="G13" s="64" t="inlineStr">
         <is>
           <t>Índice base 2018=100</t>
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="65" t="inlineStr">
+        <is>
+          <t>Indicador Oportuno de la Actividad Económica</t>
+        </is>
+      </c>
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="D14" s="65" t="n"/>
+      <c r="E14" s="65" t="n"/>
+      <c r="F14" s="65" t="n"/>
+      <c r="G14" s="65" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="66" t="inlineStr">
-        <is>
-          <t>Nota: cifras oficiales sujetas a revisión. Análisis por reglas deterministas; no se atribuye causalidad. La fuente de la tasa de desocupación es INEGI/ENOE (la OCDE se usa sólo como comparativo internacional).</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="64" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de la Industria Manufacturera</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C15" s="64" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="D15" s="64" t="n"/>
+      <c r="E15" s="64" t="n"/>
+      <c r="F15" s="64" t="n"/>
+      <c r="G15" s="64" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="65" t="inlineStr">
+        <is>
+          <t>Inversión Extranjera Directa (IED)</t>
+        </is>
+      </c>
+      <c r="B16" s="65" t="inlineStr">
+        <is>
+          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+        </is>
+      </c>
+      <c r="C16" s="65" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="D16" s="65" t="inlineStr">
+        <is>
+          <t>1T-26</t>
+        </is>
+      </c>
+      <c r="E16" s="65" t="n">
+        <v>23590.62204554513</v>
+      </c>
+      <c r="F16" s="65" t="n">
+        <v>1705.227100742525</v>
+      </c>
+      <c r="G16" s="65" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="64" t="inlineStr">
+        <is>
+          <t>Tipo de cambio FIX</t>
+        </is>
+      </c>
+      <c r="B17" s="64" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C17" s="64" t="inlineStr">
+        <is>
+          <t>Diaria</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="n"/>
+      <c r="E17" s="64" t="n"/>
+      <c r="F17" s="64" t="n"/>
+      <c r="G17" s="64" t="inlineStr">
+        <is>
+          <t>Pesos por dólar</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="65" t="inlineStr">
+        <is>
+          <t>Tasa de interés objetivo</t>
+        </is>
+      </c>
+      <c r="B18" s="65" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C18" s="65" t="inlineStr">
+        <is>
+          <t>Por reunión</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="n"/>
+      <c r="E18" s="65" t="n"/>
+      <c r="F18" s="65" t="n"/>
+      <c r="G18" s="65" t="inlineStr">
+        <is>
+          <t>Porcentaje anual</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="64" t="inlineStr">
+        <is>
+          <t>Reservas internacionales</t>
+        </is>
+      </c>
+      <c r="B19" s="64" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C19" s="64" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="D19" s="64" t="n"/>
+      <c r="E19" s="64" t="n"/>
+      <c r="F19" s="64" t="n"/>
+      <c r="G19" s="64" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="66" t="inlineStr">
+        <is>
+          <t>Nota: cifras oficiales sujetas a revisión. Análisis por reglas deterministas; no se atribuye causalidad. La fuente de la tasa de desocupación es INEGI/ENOE. Los indicadores en estado 'pendiente de token' o 'dato de respaldo' no se presentan como actualización automática (ver 'Control de actualizaciones').</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:G16"/>
+    <mergeCell ref="A21:G22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11414,7 +11567,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: pendiente de token</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>Índice (inversión)</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Var. mensual (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>Sin observaciones cargadas todavía. Se activará al configurar INEGI_TOKEN y confirmar la serie oficial. No se muestran cifras estimadas ni inventadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>Indicador Oportuno de la Actividad Económica</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: pendiente de token</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>Estimación puntual (%)</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Límite inferior (%)</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Límite superior (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>Sin observaciones cargadas todavía. Se activará al configurar INEGI_TOKEN y confirmar la serie oficial. No se muestran cifras estimadas ni inventadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:D6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de la Industria Manufacturera</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice · Estado: pendiente de token</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>Producción (índice)</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Var. mensual (%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="66" t="inlineStr">
+        <is>
+          <t>Sin observaciones cargadas todavía. Se activará al configurar INEGI_TOKEN y confirmar la serie oficial. No se muestran cifras estimadas ni inventadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A5:C6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -11689,12 +12031,12 @@
     <row r="9">
       <c r="A9" s="83" t="inlineStr">
         <is>
-          <t>Inversión Extranjera Directa (IED)</t>
+          <t>Tasa de desocupación nacional</t>
         </is>
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
         </is>
       </c>
       <c r="C9" s="83" t="inlineStr">
@@ -11704,35 +12046,39 @@
       </c>
       <c r="D9" s="83" t="inlineStr">
         <is>
-          <t>Millones de dólares</t>
+          <t>Porcentaje de la PEA</t>
         </is>
       </c>
       <c r="E9" s="83" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Serie original</t>
         </is>
       </c>
       <c r="F9" s="83" t="inlineStr">
         <is>
-          <t>Trimestral</t>
+          <t>Mensual</t>
         </is>
       </c>
       <c r="G9" s="83" t="inlineStr">
         <is>
-          <t>Descarga oficial RNIE / DataMéxico</t>
-        </is>
-      </c>
-      <c r="H9" s="83" t="inlineStr"/>
+          <t>INEGI BIE API</t>
+        </is>
+      </c>
+      <c r="H9" s="83" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/temas/empleo/</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>Tasa de desocupación nacional</t>
+          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
         </is>
       </c>
       <c r="B10" s="82" t="inlineStr">
         <is>
-          <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
+          <t>INEGI</t>
         </is>
       </c>
       <c r="C10" s="82" t="inlineStr">
@@ -11742,12 +12088,12 @@
       </c>
       <c r="D10" s="82" t="inlineStr">
         <is>
-          <t>Porcentaje de la PEA</t>
+          <t>Variación anual (%)</t>
         </is>
       </c>
       <c r="E10" s="82" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>No aplica</t>
         </is>
       </c>
       <c r="F10" s="82" t="inlineStr">
@@ -11762,14 +12108,14 @@
       </c>
       <c r="H10" s="82" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/empleo/</t>
+          <t>https://www.inegi.org.mx/temas/inpc/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="83" t="inlineStr">
         <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
+          <t>Indicador Mensual de Consumo Privado</t>
         </is>
       </c>
       <c r="B11" s="83" t="inlineStr">
@@ -11784,12 +12130,12 @@
       </c>
       <c r="D11" s="83" t="inlineStr">
         <is>
-          <t>Variación anual (%)</t>
+          <t>Índice base 2018=100</t>
         </is>
       </c>
       <c r="E11" s="83" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>Serie original</t>
         </is>
       </c>
       <c r="F11" s="83" t="inlineStr">
@@ -11804,14 +12150,14 @@
       </c>
       <c r="H11" s="83" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/inpc/</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3#D733671_600917</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Consumo Privado</t>
+          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
         </is>
       </c>
       <c r="B12" s="82" t="inlineStr">
@@ -11846,7 +12192,255 @@
       </c>
       <c r="H12" s="82" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3#D733671_600917</t>
+          <t>https://www.inegi.org.mx/temas/inversionfija/</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="83" t="inlineStr">
+        <is>
+          <t>Indicador Oportuno de la Actividad Económica</t>
+        </is>
+      </c>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C13" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="83" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="E13" s="83" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="F13" s="83" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G13" s="83" t="inlineStr">
+        <is>
+          <t>INEGI (comunicado / BIE)</t>
+        </is>
+      </c>
+      <c r="H13" s="83" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/investigacion/ioae/</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de la Industria Manufacturera</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C14" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="82" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="E14" s="82" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="F14" s="82" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G14" s="82" t="inlineStr">
+        <is>
+          <t>INEGI BIE API</t>
+        </is>
+      </c>
+      <c r="H14" s="82" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/programas/emim/</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="inlineStr">
+        <is>
+          <t>Inversión Extranjera Directa (IED)</t>
+        </is>
+      </c>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+        </is>
+      </c>
+      <c r="C15" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="83" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="E15" s="83" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F15" s="83" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G15" s="83" t="inlineStr">
+        <is>
+          <t>Descarga oficial RNIE / DataMéxico</t>
+        </is>
+      </c>
+      <c r="H15" s="83" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Tipo de cambio FIX</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C16" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D16" s="82" t="inlineStr">
+        <is>
+          <t>Pesos por dólar</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F16" s="82" t="inlineStr">
+        <is>
+          <t>Diaria</t>
+        </is>
+      </c>
+      <c r="G16" s="82" t="inlineStr">
+        <is>
+          <t>Banxico SIE API</t>
+        </is>
+      </c>
+      <c r="H16" s="82" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="inlineStr">
+        <is>
+          <t>Tasa de interés objetivo</t>
+        </is>
+      </c>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C17" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="83" t="inlineStr">
+        <is>
+          <t>Porcentaje anual</t>
+        </is>
+      </c>
+      <c r="E17" s="83" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F17" s="83" t="inlineStr">
+        <is>
+          <t>Por reunión</t>
+        </is>
+      </c>
+      <c r="G17" s="83" t="inlineStr">
+        <is>
+          <t>Banxico SIE API</t>
+        </is>
+      </c>
+      <c r="H17" s="83" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/mercados/tasas-de-referencia.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>Reservas internacionales</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C18" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="82" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="E18" s="82" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F18" s="82" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="G18" s="82" t="inlineStr">
+        <is>
+          <t>Banxico SIE API</t>
+        </is>
+      </c>
+      <c r="H18" s="82" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
         </is>
       </c>
     </row>
@@ -11855,22 +12449,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="50" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11883,7 +12483,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-17T14:25:30+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-07-20T01:40:08+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -11895,30 +12495,60 @@
       </c>
       <c r="B4" s="63" t="inlineStr">
         <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Origen del dato</t>
+        </is>
+      </c>
+      <c r="E4" s="63" t="inlineStr">
+        <is>
+          <t>Requiere token</t>
+        </is>
+      </c>
+      <c r="F4" s="63" t="inlineStr">
+        <is>
+          <t>Serie confirmada</t>
+        </is>
+      </c>
+      <c r="G4" s="63" t="inlineStr">
+        <is>
           <t>Última observación</t>
         </is>
       </c>
-      <c r="C4" s="63" t="inlineStr">
+      <c r="H4" s="63" t="inlineStr">
+        <is>
+          <t>Periodo de referencia</t>
+        </is>
+      </c>
+      <c r="I4" s="63" t="inlineStr">
+        <is>
+          <t>Fecha de publicación</t>
+        </is>
+      </c>
+      <c r="J4" s="63" t="inlineStr">
         <is>
           <t>Fecha de consulta</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="K4" s="63" t="inlineStr">
         <is>
           <t>Actualización archivo</t>
         </is>
       </c>
-      <c r="E4" s="63" t="inlineStr">
-        <is>
-          <t>Estatus</t>
-        </is>
-      </c>
-      <c r="F4" s="63" t="inlineStr">
+      <c r="L4" s="63" t="inlineStr">
         <is>
           <t>Revisión detectada</t>
         </is>
       </c>
-      <c r="G4" s="63" t="inlineStr">
+      <c r="M4" s="63" t="inlineStr">
         <is>
           <t>Observaciones de calidad</t>
         </is>
@@ -11932,30 +12562,60 @@
       </c>
       <c r="B5" s="83" t="inlineStr">
         <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C5" s="83" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D5" s="83" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E5" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F5" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G5" s="83" t="inlineStr">
+        <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="C5" s="83" t="inlineStr">
+      <c r="H5" s="83" t="inlineStr">
+        <is>
+          <t>1T-26 P</t>
+        </is>
+      </c>
+      <c r="I5" s="83" t="inlineStr">
+        <is>
+          <t>Aproximadamente 50 días después de haber concluido el trimestre</t>
+        </is>
+      </c>
+      <c r="J5" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D5" s="83" t="inlineStr">
+      <c r="K5" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E5" s="83" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F5" s="83" t="inlineStr">
+      <c r="L5" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G5" s="83" t="inlineStr"/>
+      <c r="M5" s="83" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
@@ -11965,30 +12625,60 @@
       </c>
       <c r="B6" s="82" t="inlineStr">
         <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C6" s="82" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D6" s="82" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E6" s="82" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F6" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G6" s="82" t="inlineStr">
+        <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr">
+      <c r="H6" s="82" t="inlineStr">
+        <is>
+          <t>1T-26 P</t>
+        </is>
+      </c>
+      <c r="I6" s="82" t="inlineStr">
+        <is>
+          <t>Aproximadamente 50 días después de haber concluido el trimestre</t>
+        </is>
+      </c>
+      <c r="J6" s="82" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D6" s="82" t="inlineStr">
+      <c r="K6" s="82" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E6" s="82" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F6" s="82" t="inlineStr">
+      <c r="L6" s="82" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G6" s="82" t="inlineStr"/>
+      <c r="M6" s="82" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="83" t="inlineStr">
@@ -11998,30 +12688,60 @@
       </c>
       <c r="B7" s="83" t="inlineStr">
         <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C7" s="83" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D7" s="83" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E7" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F7" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G7" s="83" t="inlineStr">
+        <is>
           <t>Abr 26 P</t>
         </is>
       </c>
-      <c r="C7" s="83" t="inlineStr">
+      <c r="H7" s="83" t="inlineStr">
+        <is>
+          <t>Abr 26 P</t>
+        </is>
+      </c>
+      <c r="I7" s="83" t="inlineStr">
+        <is>
+          <t>Aproximadamente 55 días después de haber concluido el mes</t>
+        </is>
+      </c>
+      <c r="J7" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D7" s="83" t="inlineStr">
+      <c r="K7" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E7" s="83" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F7" s="83" t="inlineStr">
+      <c r="L7" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G7" s="83" t="inlineStr"/>
+      <c r="M7" s="83" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="84" t="inlineStr">
@@ -12031,32 +12751,58 @@
       </c>
       <c r="B8" s="84" t="inlineStr">
         <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C8" s="84" t="inlineStr">
+        <is>
+          <t>dato en revisión</t>
+        </is>
+      </c>
+      <c r="D8" s="84" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E8" s="84" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F8" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G8" s="84" t="inlineStr">
+        <is>
           <t>Abr 26 P</t>
         </is>
       </c>
-      <c r="C8" s="84" t="inlineStr">
+      <c r="H8" s="84" t="inlineStr">
+        <is>
+          <t>Abr 26 P</t>
+        </is>
+      </c>
+      <c r="I8" s="84" t="n"/>
+      <c r="J8" s="84" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D8" s="84" t="inlineStr">
+      <c r="K8" s="84" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E8" s="84" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F8" s="84" t="inlineStr">
+      <c r="L8" s="84" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G8" s="84" t="inlineStr">
-        <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+      <c r="M8" s="84" t="inlineStr">
+        <is>
+          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
@@ -12068,171 +12814,641 @@
       </c>
       <c r="B9" s="83" t="inlineStr">
         <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C9" s="83" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D9" s="83" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E9" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F9" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G9" s="83" t="inlineStr">
+        <is>
           <t>May 26 O</t>
         </is>
       </c>
-      <c r="C9" s="83" t="inlineStr">
+      <c r="H9" s="83" t="inlineStr">
+        <is>
+          <t>May 26 O</t>
+        </is>
+      </c>
+      <c r="I9" s="83" t="inlineStr">
+        <is>
+          <t>Aproximadamente 30 a 45 días posteriores al cierre del mes</t>
+        </is>
+      </c>
+      <c r="J9" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D9" s="83" t="inlineStr">
+      <c r="K9" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E9" s="83" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F9" s="83" t="inlineStr">
+      <c r="L9" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G9" s="83" t="inlineStr"/>
+      <c r="M9" s="83" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>Inversión Extranjera Directa (IED)</t>
+          <t>Tasa de desocupación nacional</t>
         </is>
       </c>
       <c r="B10" s="82" t="inlineStr">
         <is>
-          <t>1T-26</t>
+          <t>principal</t>
         </is>
       </c>
       <c r="C10" s="82" t="inlineStr">
         <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D10" s="82" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E10" s="82" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F10" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G10" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="H10" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="I10" s="82" t="inlineStr">
+        <is>
+          <t>Aproximadamente 25-30 días después de haber concluido el mes</t>
+        </is>
+      </c>
+      <c r="J10" s="82" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D10" s="82" t="inlineStr">
+      <c r="K10" s="82" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E10" s="82" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F10" s="82" t="inlineStr">
+      <c r="L10" s="82" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G10" s="82" t="inlineStr"/>
+      <c r="M10" s="82" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="83" t="inlineStr">
         <is>
-          <t>Tasa de desocupación nacional</t>
+          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
         </is>
       </c>
       <c r="B11" s="83" t="inlineStr">
         <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C11" s="83" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D11" s="83" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E11" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F11" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G11" s="83" t="inlineStr">
+        <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C11" s="83" t="inlineStr">
+      <c r="H11" s="83" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="I11" s="83" t="n"/>
+      <c r="J11" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D11" s="83" t="inlineStr">
+      <c r="K11" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E11" s="83" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F11" s="83" t="inlineStr">
+      <c r="L11" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G11" s="83" t="inlineStr"/>
+      <c r="M11" s="83" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="82" t="inlineStr">
-        <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
-        </is>
-      </c>
-      <c r="B12" s="82" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
+        <is>
+          <t>Indicador Mensual de Consumo Privado</t>
+        </is>
+      </c>
+      <c r="B12" s="84" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C12" s="84" t="inlineStr">
+        <is>
+          <t>dato en revisión</t>
+        </is>
+      </c>
+      <c r="D12" s="84" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E12" s="84" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F12" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G12" s="84" t="inlineStr">
+        <is>
+          <t>Mar 26 P</t>
+        </is>
+      </c>
+      <c r="H12" s="84" t="inlineStr">
+        <is>
+          <t>Mar 26 P</t>
+        </is>
+      </c>
+      <c r="I12" s="84" t="inlineStr">
+        <is>
+          <t>Aproximadamente 21 días después de haber concluido el mes</t>
+        </is>
+      </c>
+      <c r="J12" s="84" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D12" s="82" t="inlineStr">
+      <c r="K12" s="84" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E12" s="82" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F12" s="82" t="inlineStr">
+      <c r="L12" s="84" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M12" s="84" t="inlineStr">
+        <is>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="83" t="inlineStr">
+        <is>
+          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
+        </is>
+      </c>
+      <c r="B13" s="83" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C13" s="83" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D13" s="83" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E13" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F13" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G12" s="82" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="84" t="inlineStr">
-        <is>
-          <t>Indicador Mensual de Consumo Privado</t>
-        </is>
-      </c>
-      <c r="B13" s="84" t="inlineStr">
-        <is>
-          <t>Mar 26 P</t>
-        </is>
-      </c>
-      <c r="C13" s="84" t="inlineStr">
+      <c r="G13" s="83" t="n"/>
+      <c r="H13" s="83" t="n"/>
+      <c r="I13" s="83" t="inlineStr">
+        <is>
+          <t>Aproximadamente 55 días tras el cierre del mes</t>
+        </is>
+      </c>
+      <c r="J13" s="83" t="n"/>
+      <c r="K13" s="83" t="n"/>
+      <c r="L13" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M13" s="83" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Indicador Oportuno de la Actividad Económica</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C14" s="82" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D14" s="82" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E14" s="82" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F14" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G14" s="82" t="n"/>
+      <c r="H14" s="82" t="n"/>
+      <c r="I14" s="82" t="inlineStr">
+        <is>
+          <t>Fin de mes del periodo estimado</t>
+        </is>
+      </c>
+      <c r="J14" s="82" t="n"/>
+      <c r="K14" s="82" t="n"/>
+      <c r="L14" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M14" s="82" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="83" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de la Industria Manufacturera</t>
+        </is>
+      </c>
+      <c r="B15" s="83" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C15" s="83" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D15" s="83" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E15" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F15" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G15" s="83" t="n"/>
+      <c r="H15" s="83" t="n"/>
+      <c r="I15" s="83" t="inlineStr">
+        <is>
+          <t>Aproximadamente 40 días tras el cierre del mes</t>
+        </is>
+      </c>
+      <c r="J15" s="83" t="n"/>
+      <c r="K15" s="83" t="n"/>
+      <c r="L15" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M15" s="83" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Inversión Extranjera Directa (IED)</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C16" s="82" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D16" s="82" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E16" s="82" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="82" t="inlineStr">
+        <is>
+          <t>1T-26</t>
+        </is>
+      </c>
+      <c r="H16" s="82" t="inlineStr">
+        <is>
+          <t>1T-26</t>
+        </is>
+      </c>
+      <c r="I16" s="82" t="inlineStr">
+        <is>
+          <t>Aproximadamente 45 días posteriores al cierre del trimestre</t>
+        </is>
+      </c>
+      <c r="J16" s="82" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="D13" s="84" t="inlineStr">
+      <c r="K16" s="82" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="E13" s="84" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="F13" s="84" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G13" s="84" t="inlineStr">
-        <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="85" t="inlineStr">
+      <c r="L16" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M16" s="82" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="83" t="inlineStr">
+        <is>
+          <t>Tipo de cambio FIX</t>
+        </is>
+      </c>
+      <c r="B17" s="83" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C17" s="83" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D17" s="83" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E17" s="83" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F17" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G17" s="83" t="n"/>
+      <c r="H17" s="83" t="n"/>
+      <c r="I17" s="83" t="inlineStr">
+        <is>
+          <t>Días hábiles</t>
+        </is>
+      </c>
+      <c r="J17" s="83" t="n"/>
+      <c r="K17" s="83" t="n"/>
+      <c r="L17" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M17" s="83" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>Tasa de interés objetivo</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C18" s="82" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D18" s="82" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E18" s="82" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F18" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" s="82" t="n"/>
+      <c r="H18" s="82" t="n"/>
+      <c r="I18" s="82" t="inlineStr">
+        <is>
+          <t>Días de anuncio de política monetaria</t>
+        </is>
+      </c>
+      <c r="J18" s="82" t="n"/>
+      <c r="K18" s="82" t="n"/>
+      <c r="L18" s="82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M18" s="82" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="83" t="inlineStr">
+        <is>
+          <t>Reservas internacionales</t>
+        </is>
+      </c>
+      <c r="B19" s="83" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C19" s="83" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D19" s="83" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E19" s="83" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F19" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" s="83" t="n"/>
+      <c r="H19" s="83" t="n"/>
+      <c r="I19" s="83" t="inlineStr">
+        <is>
+          <t>Semanal (martes)</t>
+        </is>
+      </c>
+      <c r="J19" s="83" t="n"/>
+      <c r="K19" s="83" t="n"/>
+      <c r="L19" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="M19" s="83" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="85" t="inlineStr">
         <is>
           <t>Advertencias del pipeline:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>• [IMFBCF] sin observaciones (estado: pendiente de token).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>• [IOAE] sin observaciones (estado: pendiente de token).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>• [EMIM] sin observaciones (estado: pendiente de token).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>• [TIPOCAMBIO] sin observaciones (estado: pendiente de token).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>• [TASA] sin observaciones (estado: pendiente de token).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>• [RESERVAS] sin observaciones (estado: pendiente de token).</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10250,7 +10250,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 17/07/2026 14:25 UTC</t>
+          <t>Generado: 20/07/2026 15:02 UTC</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-17T14:25:30+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-07-20T15:02:57+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G8" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G13" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10250,7 +10250,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 20/07/2026 15:02 UTC</t>
+          <t>Generado: 21/07/2026 14:56 UTC</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-20T15:02:57+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-07-21T14:56:39+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G8" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G13" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10250,7 +10250,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 21/07/2026 14:56 UTC</t>
+          <t>Generado: 22/07/2026 14:56 UTC</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-21T14:56:39+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-07-22T14:56:05+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G8" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G13" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10250,7 +10250,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 22/07/2026 14:56 UTC</t>
+          <t>Generado: 23/07/2026 15:02 UTC</t>
         </is>
       </c>
     </row>
@@ -11883,7 +11883,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-22T14:56:05+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-07-23T15:02:32+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G8" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="G13" s="84" t="inlineStr">
         <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.; Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -832,14 +832,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -882,16 +882,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -933,10 +933,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -959,18 +959,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1000,7 +1000,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1187,7 +1187,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1198,7 +1198,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1235,23 +1235,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1449,8 +1449,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1462,9 +1462,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1500,7 +1500,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1514,7 +1514,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1529,9 +1529,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1554,16 +1554,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1588,16 +1588,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1650,16 +1650,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1688,16 +1688,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1722,10 +1722,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1740,14 +1740,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1770,16 +1770,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1820,7 +1820,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1832,10 +1832,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1847,10 +1847,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1861,11 +1861,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1904,18 +1904,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2047,7 +2047,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2059,10 +2059,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2081,18 +2081,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2224,7 +2224,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2236,10 +2236,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2271,18 +2271,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2318,18 +2318,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2461,7 +2461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2473,10 +2473,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2496,18 +2496,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2650,8 +2650,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2663,9 +2663,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2703,7 +2703,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2720,16 +2720,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2758,16 +2758,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2792,10 +2792,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2810,14 +2810,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2845,16 +2845,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2896,10 +2896,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3016,10 +3016,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3136,10 +3136,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3147,18 +3147,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3312,7 +3312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3324,10 +3324,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3337,18 +3337,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3472,8 +3472,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3485,9 +3485,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3524,7 +3524,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3539,9 +3539,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3564,16 +3564,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3599,16 +3599,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3661,16 +3661,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3699,16 +3699,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3733,10 +3733,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3751,14 +3751,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3781,16 +3781,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3831,7 +3831,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3843,10 +3843,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="19050">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3871,18 +3871,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3907,18 +3907,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3949,7 +3949,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4066,7 +4066,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4077,7 +4077,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4094,18 +4094,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4240,7 +4240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4252,10 +4252,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4281,18 +4281,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4437,8 +4437,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4450,9 +4450,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4489,7 +4489,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4506,16 +4506,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4544,16 +4544,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4578,10 +4578,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4596,14 +4596,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4634,16 +4634,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4685,10 +4685,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4699,10 +4699,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4712,16 +4712,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4756,16 +4756,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4795,7 +4795,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4927,7 +4927,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4939,10 +4939,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4954,16 +4954,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5004,10 +5004,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5018,11 +5018,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5050,16 +5050,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5085,16 +5085,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5239,8 +5239,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5252,9 +5252,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5290,7 +5290,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5305,9 +5305,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5330,16 +5330,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5365,16 +5365,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5427,16 +5427,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5465,16 +5465,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5499,10 +5499,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5517,14 +5517,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5556,16 +5556,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5607,10 +5607,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5817,7 +5817,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5828,7 +5828,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5895,18 +5895,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6087,8 +6087,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6100,9 +6100,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6138,7 +6138,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6155,16 +6155,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6217,16 +6217,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6256,16 +6256,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6290,10 +6290,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6308,14 +6308,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6339,16 +6339,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6390,10 +6390,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6403,18 +6403,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6442,18 +6442,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6481,18 +6481,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6520,18 +6520,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6559,18 +6559,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6596,18 +6596,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6638,7 +6638,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6832,10 +6832,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7034,8 +7034,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7047,9 +7047,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7085,7 +7085,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7100,9 +7100,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7131,16 +7131,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7166,16 +7166,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7205,16 +7205,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7239,10 +7239,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7257,14 +7257,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7287,16 +7287,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7337,7 +7337,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="pct20">
+            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7345,7 +7345,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln w="38100">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7354,16 +7354,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7510,7 +7510,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7522,10 +7522,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7585,16 +7585,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7772,16 +7772,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7810,16 +7810,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7844,10 +7844,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7862,14 +7862,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7897,16 +7897,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7948,10 +7948,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8116,10 +8116,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8284,10 +8284,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8468,7 +8468,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8480,10 +8480,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8496,18 +8496,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8706,8 +8706,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8719,9 +8719,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8757,7 +8757,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8774,16 +8774,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8812,16 +8812,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8846,10 +8846,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8864,14 +8864,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8894,16 +8894,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8944,7 +8944,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8956,10 +8956,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9011,16 +9011,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9059,16 +9059,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9219,7 +9219,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9230,7 +9230,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9257,16 +9257,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9410,8 +9410,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9423,9 +9423,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9462,7 +9462,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9478,16 +9478,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9542,16 +9542,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9580,16 +9580,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9614,10 +9614,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9632,7 +9632,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9652,9 +9652,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9664,7 +9664,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9684,9 +9684,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9696,7 +9696,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9716,9 +9716,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9728,7 +9728,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9748,9 +9748,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9760,7 +9760,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9780,9 +9780,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9792,7 +9792,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9812,9 +9812,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9824,7 +9824,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9844,9 +9844,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9856,7 +9856,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9876,9 +9876,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9888,7 +9888,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9908,9 +9908,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9920,7 +9920,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9940,9 +9940,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 03/08/2026 15:37 UTC</t>
+          <t>Generado: 03/08/2026 03:31 UTC</t>
         </is>
       </c>
     </row>
@@ -10316,10 +10316,10 @@
         </is>
       </c>
       <c r="E5" s="64" t="n">
-        <v>24973976.1</v>
+        <v>24973976.071</v>
       </c>
       <c r="F5" s="64" t="n">
-        <v>0.002423004906679571</v>
+        <v>0.002423</v>
       </c>
       <c r="G5" s="64" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
     <row r="6">
       <c r="A6" s="65" t="inlineStr">
         <is>
-          <t>Producto Interno Bruto por actividad económica</t>
+          <t>Producto Interno Bruto por sector de actividad</t>
         </is>
       </c>
       <c r="B6" s="65" t="inlineStr">
@@ -10394,7 +10394,7 @@
     <row r="8">
       <c r="A8" s="65" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Actividad Industrial (IMAI)</t>
+          <t>Indicador Mensual de la Actividad Industrial</t>
         </is>
       </c>
       <c r="B8" s="65" t="inlineStr">
@@ -10409,14 +10409,14 @@
       </c>
       <c r="D8" s="65" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="E8" s="65" t="n">
-        <v>102.4</v>
+        <v>101.629971</v>
       </c>
       <c r="F8" s="65" t="n">
-        <v>0.02093718843469605</v>
+        <v>-0.007713</v>
       </c>
       <c r="G8" s="65" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
     <row r="9">
       <c r="A9" s="64" t="inlineStr">
         <is>
-          <t>Balanza comercial de mercancías de México</t>
+          <t>Balanza comercial</t>
         </is>
       </c>
       <c r="B9" s="64" t="inlineStr">
@@ -10442,14 +10442,14 @@
       </c>
       <c r="D9" s="64" t="inlineStr">
         <is>
-          <t>May 26 O</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="E9" s="64" t="n">
-        <v>69544.49099999999</v>
+        <v>72551.015</v>
       </c>
       <c r="F9" s="64" t="n">
-        <v>67285.323</v>
+        <v>68461.11900000001</v>
       </c>
       <c r="G9" s="64" t="inlineStr">
         <is>
@@ -10460,7 +10460,7 @@
     <row r="10">
       <c r="A10" s="65" t="inlineStr">
         <is>
-          <t>Tasa de desocupación nacional</t>
+          <t>Tasa de desocupación</t>
         </is>
       </c>
       <c r="B10" s="65" t="inlineStr">
@@ -10475,11 +10475,11 @@
       </c>
       <c r="D10" s="65" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.027</v>
+        <v>0.028985</v>
       </c>
       <c r="F10" s="65" t="n"/>
       <c r="G10" s="65" t="inlineStr">
@@ -10491,7 +10491,7 @@
     <row r="11">
       <c r="A11" s="64" t="inlineStr">
         <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
+          <t>Índice de Precios al Consumidor</t>
         </is>
       </c>
       <c r="B11" s="64" t="inlineStr">
@@ -10506,14 +10506,14 @@
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="E11" s="64" t="n">
-        <v>3.94</v>
+        <v>3.365977</v>
       </c>
       <c r="F11" s="64" t="n">
-        <v>4.19</v>
+        <v>4.03192</v>
       </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
@@ -10524,7 +10524,7 @@
     <row r="12">
       <c r="A12" s="65" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Consumo Privado</t>
+          <t>Indicador mensual del consumo privado</t>
         </is>
       </c>
       <c r="B12" s="65" t="inlineStr">
@@ -11583,7 +11583,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: pendiente de token</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: pendiente de confirmar serie</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11645,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: pendiente de token</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: pendiente de confirmar serie</t>
         </is>
       </c>
     </row>
@@ -11711,7 +11711,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice · Estado: pendiente de token</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice · Estado: pendiente de confirmar serie</t>
         </is>
       </c>
     </row>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="C4" s="82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>737375</t>
         </is>
       </c>
       <c r="D4" s="82" t="inlineStr">
@@ -11854,14 +11854,14 @@
       </c>
       <c r="H4" s="82" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3#D733671_600917</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="83" t="inlineStr">
         <is>
-          <t>Producto Interno Bruto por actividad económica</t>
+          <t>Producto Interno Bruto por sector de actividad</t>
         </is>
       </c>
       <c r="B5" s="83" t="inlineStr">
@@ -11938,14 +11938,14 @@
       </c>
       <c r="H6" s="82" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=1090#D737121</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="83" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Actividad Industrial (IMAI)</t>
+          <t>Indicador Mensual de la Actividad Industrial</t>
         </is>
       </c>
       <c r="B7" s="83" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="C7" s="83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>737234</t>
         </is>
       </c>
       <c r="D7" s="83" t="inlineStr">
@@ -11980,14 +11980,14 @@
       </c>
       <c r="H7" s="83" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/imai/</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="82" t="inlineStr">
         <is>
-          <t>Balanza comercial de mercancías de México</t>
+          <t>Balanza comercial</t>
         </is>
       </c>
       <c r="B8" s="82" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="C8" s="82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>33226</t>
         </is>
       </c>
       <c r="D8" s="82" t="inlineStr">
@@ -12022,14 +12022,14 @@
       </c>
       <c r="H8" s="82" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/balanza/#informacion_general</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="83" t="inlineStr">
         <is>
-          <t>Tasa de desocupación nacional</t>
+          <t>Tasa de desocupación</t>
         </is>
       </c>
       <c r="B9" s="83" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="C9" s="83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>444603</t>
         </is>
       </c>
       <c r="D9" s="83" t="inlineStr">
@@ -12064,14 +12064,14 @@
       </c>
       <c r="H9" s="83" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/empleo/</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=4#D444603</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
+          <t>Índice de Precios al Consumidor</t>
         </is>
       </c>
       <c r="B10" s="82" t="inlineStr">
@@ -12081,7 +12081,7 @@
       </c>
       <c r="C10" s="82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>334452</t>
         </is>
       </c>
       <c r="D10" s="82" t="inlineStr">
@@ -12106,14 +12106,14 @@
       </c>
       <c r="H10" s="82" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/inpc/</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="83" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Consumo Privado</t>
+          <t>Indicador mensual del consumo privado</t>
         </is>
       </c>
       <c r="B11" s="83" t="inlineStr">
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-03T15:37:44+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-03T03:31:44+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12571,12 +12571,12 @@
       </c>
       <c r="C5" s="83" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D5" s="83" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E5" s="83" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="F5" s="83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G5" s="83" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="K5" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L5" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M5" s="83" t="inlineStr">
@@ -12629,7 +12629,7 @@
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
         <is>
-          <t>Producto Interno Bruto por actividad económica</t>
+          <t>Producto Interno Bruto por sector de actividad</t>
         </is>
       </c>
       <c r="B6" s="82" t="inlineStr">
@@ -12747,12 +12747,12 @@
       </c>
       <c r="K7" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L7" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M7" s="83" t="inlineStr">
@@ -12765,7 +12765,7 @@
     <row r="8">
       <c r="A8" s="84" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Actividad Industrial (IMAI)</t>
+          <t>Indicador Mensual de la Actividad Industrial</t>
         </is>
       </c>
       <c r="B8" s="84" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="C8" s="84" t="inlineStr">
         <is>
-          <t>dato en revisión</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D8" s="84" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E8" s="84" t="inlineStr">
@@ -12790,17 +12790,17 @@
       </c>
       <c r="F8" s="84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G8" s="84" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="H8" s="84" t="inlineStr">
         <is>
-          <t>Abr 26 P</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="I8" s="84" t="n"/>
@@ -12811,12 +12811,12 @@
       </c>
       <c r="K8" s="84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L8" s="84" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M8" s="84" t="inlineStr">
@@ -12833,7 +12833,7 @@
     <row r="9">
       <c r="A9" s="83" t="inlineStr">
         <is>
-          <t>Balanza comercial de mercancías de México</t>
+          <t>Balanza comercial</t>
         </is>
       </c>
       <c r="B9" s="83" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="C9" s="83" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D9" s="83" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E9" s="83" t="inlineStr">
@@ -12858,17 +12858,17 @@
       </c>
       <c r="F9" s="83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G9" s="83" t="inlineStr">
         <is>
-          <t>May 26 O</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="H9" s="83" t="inlineStr">
         <is>
-          <t>May 26 O</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="I9" s="83" t="inlineStr">
@@ -12883,12 +12883,12 @@
       </c>
       <c r="K9" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L9" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M9" s="83" t="inlineStr">
@@ -12901,7 +12901,7 @@
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>Tasa de desocupación nacional</t>
+          <t>Tasa de desocupación</t>
         </is>
       </c>
       <c r="B10" s="82" t="inlineStr">
@@ -12911,12 +12911,12 @@
       </c>
       <c r="C10" s="82" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D10" s="82" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E10" s="82" t="inlineStr">
@@ -12926,17 +12926,17 @@
       </c>
       <c r="F10" s="82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G10" s="82" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="H10" s="82" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="I10" s="82" t="inlineStr">
@@ -12951,12 +12951,12 @@
       </c>
       <c r="K10" s="82" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L10" s="82" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M10" s="82" t="inlineStr">
@@ -12969,7 +12969,7 @@
     <row r="11">
       <c r="A11" s="83" t="inlineStr">
         <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
+          <t>Índice de Precios al Consumidor</t>
         </is>
       </c>
       <c r="B11" s="83" t="inlineStr">
@@ -12979,12 +12979,12 @@
       </c>
       <c r="C11" s="83" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D11" s="83" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E11" s="83" t="inlineStr">
@@ -12994,17 +12994,17 @@
       </c>
       <c r="F11" s="83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G11" s="83" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="H11" s="83" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="I11" s="83" t="n"/>
@@ -13015,12 +13015,12 @@
       </c>
       <c r="K11" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="L11" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M11" s="83" t="inlineStr">
@@ -13033,7 +13033,7 @@
     <row r="12">
       <c r="A12" s="84" t="inlineStr">
         <is>
-          <t>Indicador Mensual de Consumo Privado</t>
+          <t>Indicador mensual del consumo privado</t>
         </is>
       </c>
       <c r="B12" s="84" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="C13" s="83" t="inlineStr">
         <is>
-          <t>pendiente de token</t>
+          <t>pendiente de confirmar serie</t>
         </is>
       </c>
       <c r="D13" s="83" t="inlineStr">
@@ -13167,7 +13167,7 @@
       </c>
       <c r="C14" s="82" t="inlineStr">
         <is>
-          <t>pendiente de token</t>
+          <t>pendiente de confirmar serie</t>
         </is>
       </c>
       <c r="D14" s="82" t="inlineStr">
@@ -13219,7 +13219,7 @@
       </c>
       <c r="C15" s="83" t="inlineStr">
         <is>
-          <t>pendiente de token</t>
+          <t>pendiente de confirmar serie</t>
         </is>
       </c>
       <c r="D15" s="83" t="inlineStr">
@@ -13492,21 +13492,21 @@
     <row r="23">
       <c r="A23" s="62" t="inlineStr">
         <is>
-          <t>• [IMFBCF] sin observaciones (estado: pendiente de token).</t>
+          <t>• [IMFBCF] sin observaciones (estado: pendiente de confirmar serie).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>• [IOAE] sin observaciones (estado: pendiente de token).</t>
+          <t>• [IOAE] sin observaciones (estado: pendiente de confirmar serie).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="62" t="inlineStr">
         <is>
-          <t>• [EMIM] sin observaciones (estado: pendiente de token).</t>
+          <t>• [EMIM] sin observaciones (estado: pendiente de confirmar serie).</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -475,7 +475,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -684,6 +684,7 @@
     <xf numFmtId="164" fontId="2" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -10253,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 03/08/2026 04:28 UTC</t>
+          <t>Generado: 03/08/2026 15:32 UTC</t>
         </is>
       </c>
     </row>
@@ -10539,14 +10540,14 @@
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>Mar 26 P</t>
+          <t>Abr 26</t>
         </is>
       </c>
       <c r="E12" s="65" t="n">
-        <v>113.5132947678</v>
+        <v>113.7</v>
       </c>
       <c r="F12" s="65" t="n">
-        <v>0.0867002724360284</v>
+        <v>0.001</v>
       </c>
       <c r="G12" s="65" t="inlineStr">
         <is>
@@ -10570,9 +10571,17 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="D13" s="64" t="n"/>
-      <c r="E13" s="64" t="n"/>
-      <c r="F13" s="64" t="n"/>
+      <c r="D13" s="64" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="E13" s="64" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="F13" s="64" t="n">
+        <v>0.04</v>
+      </c>
       <c r="G13" s="64" t="inlineStr">
         <is>
           <t>Índice base 2018=100</t>
@@ -10595,9 +10604,17 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="D14" s="65" t="n"/>
-      <c r="E14" s="65" t="n"/>
-      <c r="F14" s="65" t="n"/>
+      <c r="D14" s="65" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="E14" s="65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F14" s="65" t="n">
+        <v>-1</v>
+      </c>
       <c r="G14" s="65" t="inlineStr">
         <is>
           <t>Variación mensual estimada (%)</t>
@@ -10620,9 +10637,15 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="D15" s="64" t="n"/>
+      <c r="D15" s="64" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
       <c r="E15" s="64" t="n"/>
-      <c r="F15" s="64" t="n"/>
+      <c r="F15" s="64" t="n">
+        <v>-0.006</v>
+      </c>
       <c r="G15" s="64" t="inlineStr">
         <is>
           <t>Índice</t>
@@ -11565,7 +11588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11583,7 +11606,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: pendiente de confirmar serie</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: actualizado automáticamente</t>
         </is>
       </c>
     </row>
@@ -11605,17 +11628,253 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
-        <is>
-          <t>Sin observaciones cargadas todavía. Se activará al configurar INEGI_TOKEN y confirmar la serie oficial. No se muestran cifras estimadas ni inventadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Oct 24</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="n">
+        <v>113.1</v>
+      </c>
+      <c r="C5" s="82" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="n">
+        <v>113.7</v>
+      </c>
+      <c r="C6" s="82" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="n">
+        <v>109.7</v>
+      </c>
+      <c r="C7" s="82" t="n">
+        <v>-0.026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="C8" s="82" t="n">
+        <v>-0.015</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="82" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B9" s="82" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C9" s="82" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B10" s="82" t="n">
+        <v>107.9</v>
+      </c>
+      <c r="C10" s="82" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="C11" s="82" t="n">
+        <v>-0.017</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="C12" s="82" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="C13" s="82" t="n">
+        <v>-0.014</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="C14" s="82" t="n">
+        <v>0.016</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Ago 25</t>
+        </is>
+      </c>
+      <c r="B15" s="82" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="C15" s="82" t="n">
+        <v>-0.027</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="n">
+        <v>101</v>
+      </c>
+      <c r="C16" s="82" t="n">
+        <v>-0.003</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="82" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="n">
+        <v>102.2</v>
+      </c>
+      <c r="C17" s="82" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="C18" s="82" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>Dic 25</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="C19" s="82" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>Ene 26</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="n">
+        <v>102.3</v>
+      </c>
+      <c r="C20" s="82" t="n">
+        <v>-0.011</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="C21" s="82" t="n">
+        <v>-0.008</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B22" s="82" t="n">
+        <v>102</v>
+      </c>
+      <c r="C22" s="82" t="n">
+        <v>0.004</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="C23" s="82" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:C6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11626,7 +11885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11645,7 +11904,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: pendiente de confirmar serie</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: actualizado automáticamente</t>
         </is>
       </c>
     </row>
@@ -11672,17 +11931,326 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
-        <is>
-          <t>Sin observaciones cargadas todavía. Se activará al configurar INEGI_TOKEN y confirmar la serie oficial. No se muestran cifras estimadas ni inventadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C5" s="82" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="D5" s="82" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C6" s="82" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="D6" s="82" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D7" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="C8" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="82" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="82" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B9" s="82" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C9" s="82" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="D9" s="82" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B10" s="82" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C10" s="82" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D10" s="82" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C11" s="82" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D11" s="82" t="n">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="82" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="D12" s="82" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C13" s="82" t="n">
+        <v>-1.6</v>
+      </c>
+      <c r="D13" s="82" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Ago 25</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C14" s="82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D14" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B15" s="82" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="C15" s="82" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="D15" s="82" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="82" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D16" s="82" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="82" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C17" s="82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D17" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>Dic 25</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C18" s="82" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="D18" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>Ene 26</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C19" s="82" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="D19" s="82" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C20" s="82" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D20" s="82" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C21" s="82" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="D21" s="82" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B22" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="82" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D22" s="82" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="C23" s="82" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="D23" s="82" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C24" s="82" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D24" s="82" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:D6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11693,7 +12261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11711,7 +12279,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice · Estado: pendiente de confirmar serie</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice · Estado: dato de respaldo vigente</t>
         </is>
       </c>
     </row>
@@ -11733,17 +12301,160 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="66" t="inlineStr">
-        <is>
-          <t>Sin observaciones cargadas todavía. Se activará al configurar INEGI_TOKEN y confirmar la serie oficial. No se muestran cifras estimadas ni inventadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6"/>
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="n"/>
+      <c r="C5" s="82" t="n">
+        <v>0.011</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="n"/>
+      <c r="C6" s="82" t="n">
+        <v>-0.015</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="n"/>
+      <c r="C7" s="82" t="n">
+        <v>-0.003</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="n"/>
+      <c r="C8" s="82" t="n">
+        <v>-0.007</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="82" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B9" s="82" t="n"/>
+      <c r="C9" s="82" t="n">
+        <v>-0.001</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="B10" s="82" t="n"/>
+      <c r="C10" s="82" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="n"/>
+      <c r="C11" s="82" t="n">
+        <v>-0.002</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="n"/>
+      <c r="C12" s="82" t="n">
+        <v>0.002</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="n"/>
+      <c r="C13" s="82" t="n">
+        <v>0.003</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Dic 25</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="n"/>
+      <c r="C14" s="82" t="n">
+        <v>-0.001</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B15" s="82" t="n"/>
+      <c r="C15" s="82" t="n">
+        <v>-0.003</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="n"/>
+      <c r="C16" s="82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="82" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="n"/>
+      <c r="C17" s="82" t="n">
+        <v>0.005</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n"/>
+      <c r="C18" s="82" t="n">
+        <v>-0.006</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A5:C6"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11817,626 +12528,626 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="82" t="inlineStr">
+      <c r="A4" s="83" t="inlineStr">
         <is>
           <t>Producto Interno Bruto</t>
         </is>
       </c>
-      <c r="B4" s="82" t="inlineStr">
+      <c r="B4" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C4" s="82" t="inlineStr">
+      <c r="C4" s="83" t="inlineStr">
         <is>
           <t>737375</t>
         </is>
       </c>
-      <c r="D4" s="82" t="inlineStr">
+      <c r="D4" s="83" t="inlineStr">
         <is>
           <t>Millones de pesos (a precios de 2018)</t>
         </is>
       </c>
-      <c r="E4" s="82" t="inlineStr">
+      <c r="E4" s="83" t="inlineStr">
         <is>
           <t>Serie original</t>
         </is>
       </c>
-      <c r="F4" s="82" t="inlineStr">
+      <c r="F4" s="83" t="inlineStr">
         <is>
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="G4" s="82" t="inlineStr">
+      <c r="G4" s="83" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H4" s="82" t="inlineStr">
+      <c r="H4" s="83" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=605598#D737375</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="83" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>Producto Interno Bruto por sector de actividad</t>
         </is>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C5" s="83" t="inlineStr">
+      <c r="C5" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="83" t="inlineStr">
+      <c r="D5" s="84" t="inlineStr">
         <is>
           <t>Millones de pesos (a precios de 2018)</t>
         </is>
       </c>
-      <c r="E5" s="83" t="inlineStr">
+      <c r="E5" s="84" t="inlineStr">
         <is>
           <t>Serie original</t>
         </is>
       </c>
-      <c r="F5" s="83" t="inlineStr">
+      <c r="F5" s="84" t="inlineStr">
         <is>
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="G5" s="83" t="inlineStr">
+      <c r="G5" s="84" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H5" s="83" t="inlineStr">
+      <c r="H5" s="84" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/temas/pib/#informacion_general</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Indicador Global de la Actividad Económica</t>
         </is>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
         <is>
           <t>737121</t>
         </is>
       </c>
-      <c r="D6" s="82" t="inlineStr">
+      <c r="D6" s="83" t="inlineStr">
         <is>
           <t>Índice base 2018=100</t>
         </is>
       </c>
-      <c r="E6" s="82" t="inlineStr">
+      <c r="E6" s="83" t="inlineStr">
         <is>
           <t>Serie original</t>
         </is>
       </c>
-      <c r="F6" s="82" t="inlineStr">
+      <c r="F6" s="83" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G6" s="82" t="inlineStr">
+      <c r="G6" s="83" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H6" s="82" t="inlineStr">
+      <c r="H6" s="83" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603589#D737121</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="83" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>Indicador Mensual de la Actividad Industrial</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C7" s="83" t="inlineStr">
+      <c r="C7" s="84" t="inlineStr">
         <is>
           <t>737234</t>
         </is>
       </c>
-      <c r="D7" s="83" t="inlineStr">
+      <c r="D7" s="84" t="inlineStr">
         <is>
           <t>Índice base 2018=100</t>
         </is>
       </c>
-      <c r="E7" s="83" t="inlineStr">
+      <c r="E7" s="84" t="inlineStr">
         <is>
           <t>Serie original</t>
         </is>
       </c>
-      <c r="F7" s="83" t="inlineStr">
+      <c r="F7" s="84" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G7" s="83" t="inlineStr">
+      <c r="G7" s="84" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H7" s="83" t="inlineStr">
+      <c r="H7" s="84" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=603729#D737234</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="82" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Balanza comercial</t>
         </is>
       </c>
-      <c r="B8" s="82" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C8" s="82" t="inlineStr">
+      <c r="C8" s="83" t="inlineStr">
         <is>
           <t>33226</t>
         </is>
       </c>
-      <c r="D8" s="82" t="inlineStr">
+      <c r="D8" s="83" t="inlineStr">
         <is>
           <t>Millones de dólares</t>
         </is>
       </c>
-      <c r="E8" s="82" t="inlineStr">
+      <c r="E8" s="83" t="inlineStr">
         <is>
           <t>Serie original</t>
         </is>
       </c>
-      <c r="F8" s="82" t="inlineStr">
+      <c r="F8" s="83" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G8" s="82" t="inlineStr">
+      <c r="G8" s="83" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H8" s="82" t="inlineStr">
+      <c r="H8" s="83" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=36695#D33226</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="83" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>Tasa de desocupación</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>INEGI — Encuesta Nacional de Ocupación y Empleo (ENOE/ENOEN)</t>
         </is>
       </c>
-      <c r="C9" s="83" t="inlineStr">
+      <c r="C9" s="84" t="inlineStr">
         <is>
           <t>444603</t>
         </is>
       </c>
-      <c r="D9" s="83" t="inlineStr">
+      <c r="D9" s="84" t="inlineStr">
         <is>
           <t>Porcentaje de la PEA</t>
         </is>
       </c>
-      <c r="E9" s="83" t="inlineStr">
+      <c r="E9" s="84" t="inlineStr">
         <is>
           <t>Serie original</t>
         </is>
       </c>
-      <c r="F9" s="83" t="inlineStr">
+      <c r="F9" s="84" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G9" s="83" t="inlineStr">
+      <c r="G9" s="84" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H9" s="83" t="inlineStr">
+      <c r="H9" s="84" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=4#D444603</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Índice de Precios al Consumidor</t>
         </is>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C10" s="82" t="inlineStr">
+      <c r="C10" s="83" t="inlineStr">
         <is>
           <t>334452</t>
         </is>
       </c>
-      <c r="D10" s="82" t="inlineStr">
+      <c r="D10" s="83" t="inlineStr">
         <is>
           <t>Variación anual (%)</t>
         </is>
       </c>
-      <c r="E10" s="82" t="inlineStr">
+      <c r="E10" s="83" t="inlineStr">
         <is>
           <t>No aplica</t>
         </is>
       </c>
-      <c r="F10" s="82" t="inlineStr">
+      <c r="F10" s="83" t="inlineStr">
         <is>
           <t>Mensual</t>
         </is>
       </c>
-      <c r="G10" s="82" t="inlineStr">
+      <c r="G10" s="83" t="inlineStr">
         <is>
           <t>INEGI BIE API</t>
         </is>
       </c>
-      <c r="H10" s="82" t="inlineStr">
+      <c r="H10" s="83" t="inlineStr">
         <is>
           <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=682416#D334452</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="83" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>Indicador mensual del consumo privado</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="C11" s="83" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
+        <is>
+          <t>CONSUMO_pdf</t>
+        </is>
+      </c>
+      <c r="D11" s="84" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="E11" s="84" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="F11" s="84" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G11" s="84" t="inlineStr">
+        <is>
+          <t>INEGI boletín PDF</t>
+        </is>
+      </c>
+      <c r="H11" s="84" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_07.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="83" t="inlineStr">
+        <is>
+          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
+        </is>
+      </c>
+      <c r="B12" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C12" s="83" t="inlineStr">
+        <is>
+          <t>IMFBCF_pdf</t>
+        </is>
+      </c>
+      <c r="D12" s="83" t="inlineStr">
+        <is>
+          <t>Índice base 2018=100</t>
+        </is>
+      </c>
+      <c r="E12" s="83" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="F12" s="83" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G12" s="83" t="inlineStr">
+        <is>
+          <t>INEGI boletín PDF</t>
+        </is>
+      </c>
+      <c r="H12" s="83" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_07.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="84" t="inlineStr">
+        <is>
+          <t>Indicador Oportuno de la Actividad Económica</t>
+        </is>
+      </c>
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C13" s="84" t="inlineStr">
+        <is>
+          <t>IOAE_pdf</t>
+        </is>
+      </c>
+      <c r="D13" s="84" t="inlineStr">
+        <is>
+          <t>Variación mensual estimada (%)</t>
+        </is>
+      </c>
+      <c r="E13" s="84" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="F13" s="84" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G13" s="84" t="inlineStr">
+        <is>
+          <t>INEGI boletín PDF</t>
+        </is>
+      </c>
+      <c r="H13" s="84" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ioae/ioae2026_07.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="83" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de la Industria Manufacturera</t>
+        </is>
+      </c>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C14" s="83" t="inlineStr">
+        <is>
+          <t>EMIM_pdf</t>
+        </is>
+      </c>
+      <c r="D14" s="83" t="inlineStr">
+        <is>
+          <t>Índice</t>
+        </is>
+      </c>
+      <c r="E14" s="83" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="F14" s="83" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G14" s="83" t="inlineStr">
+        <is>
+          <t>INEGI boletín PDF</t>
+        </is>
+      </c>
+      <c r="H14" s="83" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_07.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="84" t="inlineStr">
+        <is>
+          <t>Inversión Extranjera Directa (IED)</t>
+        </is>
+      </c>
+      <c r="B15" s="84" t="inlineStr">
+        <is>
+          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
+        </is>
+      </c>
+      <c r="C15" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D11" s="83" t="inlineStr">
-        <is>
-          <t>Índice base 2018=100</t>
-        </is>
-      </c>
-      <c r="E11" s="83" t="inlineStr">
-        <is>
-          <t>Serie original</t>
-        </is>
-      </c>
-      <c r="F11" s="83" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="G11" s="83" t="inlineStr">
-        <is>
-          <t>INEGI BIE API</t>
-        </is>
-      </c>
-      <c r="H11" s="83" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/app/indicadores/?tm=3#D733671_600917</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="82" t="inlineStr">
-        <is>
-          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
-        </is>
-      </c>
-      <c r="B12" s="82" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="C12" s="82" t="inlineStr">
+      <c r="D15" s="84" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="E15" s="84" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F15" s="84" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G15" s="84" t="inlineStr">
+        <is>
+          <t>Descarga oficial RNIE / DataMéxico</t>
+        </is>
+      </c>
+      <c r="H15" s="84" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="83" t="inlineStr">
+        <is>
+          <t>Tipo de cambio FIX</t>
+        </is>
+      </c>
+      <c r="B16" s="83" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C16" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D12" s="82" t="inlineStr">
-        <is>
-          <t>Índice base 2018=100</t>
-        </is>
-      </c>
-      <c r="E12" s="82" t="inlineStr">
-        <is>
-          <t>Serie original</t>
-        </is>
-      </c>
-      <c r="F12" s="82" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="G12" s="82" t="inlineStr">
-        <is>
-          <t>INEGI BIE API</t>
-        </is>
-      </c>
-      <c r="H12" s="82" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/temas/inversionfija/</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="83" t="inlineStr">
-        <is>
-          <t>Indicador Oportuno de la Actividad Económica</t>
-        </is>
-      </c>
-      <c r="B13" s="83" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="C13" s="83" t="inlineStr">
+      <c r="D16" s="83" t="inlineStr">
+        <is>
+          <t>Pesos por dólar</t>
+        </is>
+      </c>
+      <c r="E16" s="83" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F16" s="83" t="inlineStr">
+        <is>
+          <t>Diaria</t>
+        </is>
+      </c>
+      <c r="G16" s="83" t="inlineStr">
+        <is>
+          <t>Banxico SIE API</t>
+        </is>
+      </c>
+      <c r="H16" s="83" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="84" t="inlineStr">
+        <is>
+          <t>Tasa de interés objetivo</t>
+        </is>
+      </c>
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C17" s="84" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D13" s="83" t="inlineStr">
-        <is>
-          <t>Variación mensual estimada (%)</t>
-        </is>
-      </c>
-      <c r="E13" s="83" t="inlineStr">
-        <is>
-          <t>Serie desestacionalizada</t>
-        </is>
-      </c>
-      <c r="F13" s="83" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="G13" s="83" t="inlineStr">
-        <is>
-          <t>INEGI (comunicado / BIE)</t>
-        </is>
-      </c>
-      <c r="H13" s="83" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/investigacion/ioae/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="82" t="inlineStr">
-        <is>
-          <t>Encuesta Mensual de la Industria Manufacturera</t>
-        </is>
-      </c>
-      <c r="B14" s="82" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="C14" s="82" t="inlineStr">
+      <c r="D17" s="84" t="inlineStr">
+        <is>
+          <t>Porcentaje anual</t>
+        </is>
+      </c>
+      <c r="E17" s="84" t="inlineStr">
+        <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F17" s="84" t="inlineStr">
+        <is>
+          <t>Por reunión</t>
+        </is>
+      </c>
+      <c r="G17" s="84" t="inlineStr">
+        <is>
+          <t>Banxico SIE API</t>
+        </is>
+      </c>
+      <c r="H17" s="84" t="inlineStr">
+        <is>
+          <t>https://www.banxico.org.mx/mercados/tasas-de-referencia.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>Reservas internacionales</t>
+        </is>
+      </c>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
+          <t>Banco de México</t>
+        </is>
+      </c>
+      <c r="C18" s="83" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D14" s="82" t="inlineStr">
-        <is>
-          <t>Índice</t>
-        </is>
-      </c>
-      <c r="E14" s="82" t="inlineStr">
-        <is>
-          <t>Serie original</t>
-        </is>
-      </c>
-      <c r="F14" s="82" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="G14" s="82" t="inlineStr">
-        <is>
-          <t>INEGI BIE API</t>
-        </is>
-      </c>
-      <c r="H14" s="82" t="inlineStr">
-        <is>
-          <t>https://www.inegi.org.mx/programas/emim/</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="83" t="inlineStr">
-        <is>
-          <t>Inversión Extranjera Directa (IED)</t>
-        </is>
-      </c>
-      <c r="B15" s="83" t="inlineStr">
-        <is>
-          <t>Registro Nacional de Inversiones Extranjeras (RNIE). Secretaría de Economía</t>
-        </is>
-      </c>
-      <c r="C15" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D15" s="83" t="inlineStr">
+      <c r="D18" s="83" t="inlineStr">
         <is>
           <t>Millones de dólares</t>
         </is>
       </c>
-      <c r="E15" s="83" t="inlineStr">
+      <c r="E18" s="83" t="inlineStr">
         <is>
           <t>No aplica</t>
         </is>
       </c>
-      <c r="F15" s="83" t="inlineStr">
-        <is>
-          <t>Trimestral</t>
-        </is>
-      </c>
-      <c r="G15" s="83" t="inlineStr">
-        <is>
-          <t>Descarga oficial RNIE / DataMéxico</t>
-        </is>
-      </c>
-      <c r="H15" s="83" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="82" t="inlineStr">
-        <is>
-          <t>Tipo de cambio FIX</t>
-        </is>
-      </c>
-      <c r="B16" s="82" t="inlineStr">
-        <is>
-          <t>Banco de México</t>
-        </is>
-      </c>
-      <c r="C16" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D16" s="82" t="inlineStr">
-        <is>
-          <t>Pesos por dólar</t>
-        </is>
-      </c>
-      <c r="E16" s="82" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="F16" s="82" t="inlineStr">
-        <is>
-          <t>Diaria</t>
-        </is>
-      </c>
-      <c r="G16" s="82" t="inlineStr">
+      <c r="F18" s="83" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="G18" s="83" t="inlineStr">
         <is>
           <t>Banxico SIE API</t>
         </is>
       </c>
-      <c r="H16" s="82" t="inlineStr">
-        <is>
-          <t>https://www.banxico.org.mx/tipcamb/tipCamMIAction.do</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="83" t="inlineStr">
-        <is>
-          <t>Tasa de interés objetivo</t>
-        </is>
-      </c>
-      <c r="B17" s="83" t="inlineStr">
-        <is>
-          <t>Banco de México</t>
-        </is>
-      </c>
-      <c r="C17" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D17" s="83" t="inlineStr">
-        <is>
-          <t>Porcentaje anual</t>
-        </is>
-      </c>
-      <c r="E17" s="83" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="F17" s="83" t="inlineStr">
-        <is>
-          <t>Por reunión</t>
-        </is>
-      </c>
-      <c r="G17" s="83" t="inlineStr">
-        <is>
-          <t>Banxico SIE API</t>
-        </is>
-      </c>
-      <c r="H17" s="83" t="inlineStr">
-        <is>
-          <t>https://www.banxico.org.mx/mercados/tasas-de-referencia.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="82" t="inlineStr">
-        <is>
-          <t>Reservas internacionales</t>
-        </is>
-      </c>
-      <c r="B18" s="82" t="inlineStr">
-        <is>
-          <t>Banco de México</t>
-        </is>
-      </c>
-      <c r="C18" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D18" s="82" t="inlineStr">
-        <is>
-          <t>Millones de dólares</t>
-        </is>
-      </c>
-      <c r="E18" s="82" t="inlineStr">
-        <is>
-          <t>No aplica</t>
-        </is>
-      </c>
-      <c r="F18" s="82" t="inlineStr">
-        <is>
-          <t>Semanal</t>
-        </is>
-      </c>
-      <c r="G18" s="82" t="inlineStr">
-        <is>
-          <t>Banxico SIE API</t>
-        </is>
-      </c>
-      <c r="H18" s="82" t="inlineStr">
+      <c r="H18" s="83" t="inlineStr">
         <is>
           <t>https://www.banxico.org.mx/publicaciones-y-prensa/reservas-internacionales/</t>
         </is>
@@ -12453,7 +13164,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -12482,7 +13193,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-03T04:28:50+00:00 · resultado: OK · modo: online</t>
+          <t>Última corrida del pipeline: 2026-08-03T15:31:49+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12559,931 +13270,979 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="83" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>Producto Interno Bruto</t>
         </is>
       </c>
-      <c r="B5" s="83" t="inlineStr">
+      <c r="B5" s="84" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C5" s="83" t="inlineStr">
+      <c r="C5" s="84" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D5" s="83" t="inlineStr">
+      <c r="D5" s="84" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E5" s="83" t="inlineStr">
+      <c r="E5" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F5" s="83" t="inlineStr">
+      <c r="F5" s="84" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G5" s="83" t="inlineStr">
+      <c r="G5" s="84" t="inlineStr">
         <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="H5" s="83" t="inlineStr">
+      <c r="H5" s="84" t="inlineStr">
         <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="I5" s="83" t="inlineStr">
+      <c r="I5" s="84" t="inlineStr">
         <is>
           <t>Aproximadamente 50 días después de haber concluido el trimestre</t>
         </is>
       </c>
-      <c r="J5" s="83" t="inlineStr">
+      <c r="J5" s="84" t="inlineStr">
         <is>
           <t>30 de octubre de 2026 · 3er trimestre 2026</t>
         </is>
       </c>
-      <c r="K5" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="L5" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="M5" s="83" t="inlineStr">
+      <c r="K5" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L5" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M5" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N5" s="83" t="inlineStr"/>
+      <c r="N5" s="84" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="82" t="inlineStr">
+      <c r="A6" s="83" t="inlineStr">
         <is>
           <t>Producto Interno Bruto por sector de actividad</t>
         </is>
       </c>
-      <c r="B6" s="82" t="inlineStr">
+      <c r="B6" s="83" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C6" s="82" t="inlineStr">
+      <c r="C6" s="83" t="inlineStr">
         <is>
           <t>dato de respaldo vigente</t>
         </is>
       </c>
-      <c r="D6" s="82" t="inlineStr">
+      <c r="D6" s="83" t="inlineStr">
         <is>
           <t>respaldo</t>
         </is>
       </c>
-      <c r="E6" s="82" t="inlineStr">
+      <c r="E6" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F6" s="82" t="inlineStr">
+      <c r="F6" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G6" s="82" t="inlineStr">
+      <c r="G6" s="83" t="inlineStr">
         <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="H6" s="82" t="inlineStr">
+      <c r="H6" s="83" t="inlineStr">
         <is>
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="I6" s="82" t="inlineStr">
+      <c r="I6" s="83" t="inlineStr">
         <is>
           <t>Aproximadamente 50 días después de haber concluido el trimestre</t>
         </is>
       </c>
-      <c r="J6" s="82" t="inlineStr">
+      <c r="J6" s="83" t="inlineStr">
         <is>
           <t>24 de agosto de 2026 · 2° trimestre 2026</t>
         </is>
       </c>
-      <c r="K6" s="82" t="inlineStr">
+      <c r="K6" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="L6" s="82" t="inlineStr">
+      <c r="L6" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="M6" s="82" t="inlineStr">
+      <c r="M6" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N6" s="82" t="inlineStr"/>
+      <c r="N6" s="83" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="83" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>Indicador Global de la Actividad Económica</t>
         </is>
       </c>
-      <c r="B7" s="83" t="inlineStr">
+      <c r="B7" s="84" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C7" s="83" t="inlineStr">
+      <c r="C7" s="84" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D7" s="83" t="inlineStr">
+      <c r="D7" s="84" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E7" s="83" t="inlineStr">
+      <c r="E7" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F7" s="83" t="inlineStr">
+      <c r="F7" s="84" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G7" s="83" t="inlineStr">
+      <c r="G7" s="84" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="H7" s="83" t="inlineStr">
+      <c r="H7" s="84" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="I7" s="83" t="inlineStr">
+      <c r="I7" s="84" t="inlineStr">
         <is>
           <t>Aproximadamente 55 días después de haber concluido el mes</t>
         </is>
       </c>
-      <c r="J7" s="83" t="inlineStr">
+      <c r="J7" s="84" t="inlineStr">
         <is>
           <t>24 de agosto de 2026 · Junio 2026</t>
         </is>
       </c>
-      <c r="K7" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="L7" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="M7" s="83" t="inlineStr">
+      <c r="K7" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L7" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M7" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N7" s="83" t="inlineStr"/>
+      <c r="N7" s="84" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="84" t="inlineStr">
+      <c r="A8" s="85" t="inlineStr">
         <is>
           <t>Indicador Mensual de la Actividad Industrial</t>
         </is>
       </c>
-      <c r="B8" s="84" t="inlineStr">
+      <c r="B8" s="85" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C8" s="84" t="inlineStr">
+      <c r="C8" s="85" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D8" s="84" t="inlineStr">
+      <c r="D8" s="85" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E8" s="84" t="inlineStr">
+      <c r="E8" s="85" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F8" s="84" t="inlineStr">
+      <c r="F8" s="85" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G8" s="84" t="inlineStr">
+      <c r="G8" s="85" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="H8" s="84" t="inlineStr">
+      <c r="H8" s="85" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="I8" s="84" t="n"/>
-      <c r="J8" s="84" t="inlineStr">
+      <c r="I8" s="85" t="n"/>
+      <c r="J8" s="85" t="inlineStr">
         <is>
           <t>11 de agosto de 2026 · Junio 2026</t>
         </is>
       </c>
-      <c r="K8" s="84" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="L8" s="84" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="M8" s="84" t="inlineStr">
+      <c r="K8" s="85" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L8" s="85" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M8" s="85" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="N8" s="84" t="inlineStr">
+      <c r="N8" s="85" t="inlineStr">
         <is>
           <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="83" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>Balanza comercial</t>
         </is>
       </c>
-      <c r="B9" s="83" t="inlineStr">
+      <c r="B9" s="84" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C9" s="83" t="inlineStr">
+      <c r="C9" s="84" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D9" s="83" t="inlineStr">
+      <c r="D9" s="84" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E9" s="83" t="inlineStr">
+      <c r="E9" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F9" s="83" t="inlineStr">
+      <c r="F9" s="84" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G9" s="83" t="inlineStr">
+      <c r="G9" s="84" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="H9" s="83" t="inlineStr">
+      <c r="H9" s="84" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="I9" s="83" t="inlineStr">
+      <c r="I9" s="84" t="inlineStr">
         <is>
           <t>Aproximadamente 30 a 45 días posteriores al cierre del mes</t>
         </is>
       </c>
-      <c r="J9" s="83" t="inlineStr">
+      <c r="J9" s="84" t="inlineStr">
         <is>
           <t>27 de agosto de 2026 · Julio 2026</t>
         </is>
       </c>
-      <c r="K9" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="L9" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="M9" s="83" t="inlineStr">
+      <c r="K9" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L9" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M9" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N9" s="83" t="inlineStr"/>
+      <c r="N9" s="84" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="82" t="inlineStr">
+      <c r="A10" s="83" t="inlineStr">
         <is>
           <t>Tasa de desocupación</t>
         </is>
       </c>
-      <c r="B10" s="82" t="inlineStr">
+      <c r="B10" s="83" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C10" s="82" t="inlineStr">
+      <c r="C10" s="83" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D10" s="82" t="inlineStr">
+      <c r="D10" s="83" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E10" s="82" t="inlineStr">
+      <c r="E10" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F10" s="82" t="inlineStr">
+      <c r="F10" s="83" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G10" s="82" t="inlineStr">
+      <c r="G10" s="83" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="H10" s="82" t="inlineStr">
+      <c r="H10" s="83" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="I10" s="82" t="inlineStr">
+      <c r="I10" s="83" t="inlineStr">
         <is>
           <t>Aproximadamente 25-30 días después de haber concluido el mes</t>
         </is>
       </c>
-      <c r="J10" s="82" t="inlineStr">
+      <c r="J10" s="83" t="inlineStr">
         <is>
           <t>25 de agosto de 2026 · Julio 2026</t>
         </is>
       </c>
-      <c r="K10" s="82" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="L10" s="82" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="M10" s="82" t="inlineStr">
+      <c r="K10" s="83" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L10" s="83" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M10" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N10" s="82" t="inlineStr"/>
+      <c r="N10" s="83" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="83" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>Índice de Precios al Consumidor</t>
         </is>
       </c>
-      <c r="B11" s="83" t="inlineStr">
+      <c r="B11" s="84" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C11" s="83" t="inlineStr">
+      <c r="C11" s="84" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D11" s="83" t="inlineStr">
+      <c r="D11" s="84" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E11" s="83" t="inlineStr">
+      <c r="E11" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F11" s="83" t="inlineStr">
+      <c r="F11" s="84" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G11" s="83" t="inlineStr">
+      <c r="G11" s="84" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="H11" s="83" t="inlineStr">
+      <c r="H11" s="84" t="inlineStr">
         <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="I11" s="83" t="n"/>
-      <c r="J11" s="83" t="inlineStr">
+      <c r="I11" s="84" t="n"/>
+      <c r="J11" s="84" t="inlineStr">
         <is>
           <t>07 de agosto de 2026 · Julio 2026</t>
         </is>
       </c>
-      <c r="K11" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="L11" s="83" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="M11" s="83" t="inlineStr">
+      <c r="K11" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L11" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M11" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N11" s="83" t="inlineStr"/>
+      <c r="N11" s="84" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="84" t="inlineStr">
+      <c r="A12" s="85" t="inlineStr">
         <is>
           <t>Indicador mensual del consumo privado</t>
         </is>
       </c>
-      <c r="B12" s="84" t="inlineStr">
+      <c r="B12" s="85" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C12" s="84" t="inlineStr">
-        <is>
-          <t>dato en revisión</t>
-        </is>
-      </c>
-      <c r="D12" s="84" t="inlineStr">
+      <c r="C12" s="85" t="inlineStr">
+        <is>
+          <t>actualizado automáticamente</t>
+        </is>
+      </c>
+      <c r="D12" s="85" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="E12" s="85" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F12" s="85" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G12" s="85" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="H12" s="85" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="I12" s="85" t="inlineStr">
+        <is>
+          <t>Aproximadamente 21 días después de haber concluido el mes</t>
+        </is>
+      </c>
+      <c r="J12" s="85" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026 · Mayo 2026</t>
+        </is>
+      </c>
+      <c r="K12" s="85" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L12" s="85" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M12" s="85" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="N12" s="85" t="inlineStr">
+        <is>
+          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="84" t="inlineStr">
+        <is>
+          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
+        </is>
+      </c>
+      <c r="B13" s="84" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C13" s="84" t="inlineStr">
+        <is>
+          <t>actualizado automáticamente</t>
+        </is>
+      </c>
+      <c r="D13" s="84" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="E13" s="84" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F13" s="84" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G13" s="84" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="H13" s="84" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="I13" s="84" t="inlineStr">
+        <is>
+          <t>Aproximadamente 55 días tras el cierre del mes</t>
+        </is>
+      </c>
+      <c r="J13" s="84" t="inlineStr">
+        <is>
+          <t>05 de agosto de 2026 · Mayo 2026</t>
+        </is>
+      </c>
+      <c r="K13" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L13" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M13" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N13" s="84" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="83" t="inlineStr">
+        <is>
+          <t>Indicador Oportuno de la Actividad Económica</t>
+        </is>
+      </c>
+      <c r="B14" s="83" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C14" s="83" t="inlineStr">
+        <is>
+          <t>actualizado automáticamente</t>
+        </is>
+      </c>
+      <c r="D14" s="83" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="E14" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F14" s="83" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G14" s="83" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="H14" s="83" t="inlineStr">
+        <is>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="I14" s="83" t="inlineStr">
+        <is>
+          <t>Fin de mes del periodo estimado</t>
+        </is>
+      </c>
+      <c r="J14" s="83" t="inlineStr">
+        <is>
+          <t>20 de agosto de 2026 · Julio 2026</t>
+        </is>
+      </c>
+      <c r="K14" s="83" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L14" s="83" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M14" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N14" s="83" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="84" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de la Industria Manufacturera</t>
+        </is>
+      </c>
+      <c r="B15" s="84" t="inlineStr">
+        <is>
+          <t>principal</t>
+        </is>
+      </c>
+      <c r="C15" s="84" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D15" s="84" t="inlineStr">
         <is>
           <t>respaldo</t>
         </is>
       </c>
-      <c r="E12" s="84" t="inlineStr">
+      <c r="E15" s="84" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F12" s="84" t="inlineStr">
+      <c r="F15" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G12" s="84" t="inlineStr">
-        <is>
-          <t>Mar 26 P</t>
-        </is>
-      </c>
-      <c r="H12" s="84" t="inlineStr">
-        <is>
-          <t>Mar 26 P</t>
-        </is>
-      </c>
-      <c r="I12" s="84" t="inlineStr">
-        <is>
-          <t>Aproximadamente 21 días después de haber concluido el mes</t>
-        </is>
-      </c>
-      <c r="J12" s="84" t="inlineStr">
-        <is>
-          <t>05 de agosto de 2026 · Mayo 2026</t>
-        </is>
-      </c>
-      <c r="K12" s="84" t="inlineStr">
+      <c r="G15" s="84" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="H15" s="84" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="I15" s="84" t="inlineStr">
+        <is>
+          <t>Aproximadamente 40 días tras el cierre del mes</t>
+        </is>
+      </c>
+      <c r="J15" s="84" t="inlineStr">
+        <is>
+          <t>17 de agosto de 2026 · Junio 2026</t>
+        </is>
+      </c>
+      <c r="K15" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="L15" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="M15" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N15" s="84" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="83" t="inlineStr">
+        <is>
+          <t>Inversión Extranjera Directa (IED)</t>
+        </is>
+      </c>
+      <c r="B16" s="83" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C16" s="83" t="inlineStr">
+        <is>
+          <t>dato de respaldo vigente</t>
+        </is>
+      </c>
+      <c r="D16" s="83" t="inlineStr">
+        <is>
+          <t>respaldo</t>
+        </is>
+      </c>
+      <c r="E16" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G16" s="83" t="inlineStr">
+        <is>
+          <t>1T-26</t>
+        </is>
+      </c>
+      <c r="H16" s="83" t="inlineStr">
+        <is>
+          <t>1T-26</t>
+        </is>
+      </c>
+      <c r="I16" s="83" t="inlineStr">
+        <is>
+          <t>Aproximadamente 45 días posteriores al cierre del trimestre</t>
+        </is>
+      </c>
+      <c r="J16" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="L12" s="84" t="inlineStr">
+      <c r="L16" s="83" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="M12" s="84" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N12" s="84" t="inlineStr">
-        <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="83" t="inlineStr">
-        <is>
-          <t>Indicador Mensual de la Formación Bruta de Capital Fijo</t>
-        </is>
-      </c>
-      <c r="B13" s="83" t="inlineStr">
-        <is>
-          <t>principal</t>
-        </is>
-      </c>
-      <c r="C13" s="83" t="inlineStr">
-        <is>
-          <t>pendiente de confirmar serie</t>
-        </is>
-      </c>
-      <c r="D13" s="83" t="inlineStr">
+      <c r="M16" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N16" s="83" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="84" t="inlineStr">
+        <is>
+          <t>Tipo de cambio FIX</t>
+        </is>
+      </c>
+      <c r="B17" s="84" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C17" s="84" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D17" s="84" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="E13" s="83" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="F13" s="83" t="inlineStr">
+      <c r="E17" s="84" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F17" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G13" s="83" t="n"/>
-      <c r="H13" s="83" t="n"/>
-      <c r="I13" s="83" t="inlineStr">
-        <is>
-          <t>Aproximadamente 55 días tras el cierre del mes</t>
-        </is>
-      </c>
-      <c r="J13" s="83" t="inlineStr">
-        <is>
-          <t>05 de agosto de 2026 · Mayo 2026</t>
-        </is>
-      </c>
-      <c r="K13" s="83" t="n"/>
-      <c r="L13" s="83" t="n"/>
-      <c r="M13" s="83" t="inlineStr">
+      <c r="G17" s="84" t="n"/>
+      <c r="H17" s="84" t="n"/>
+      <c r="I17" s="84" t="inlineStr">
+        <is>
+          <t>Días hábiles</t>
+        </is>
+      </c>
+      <c r="J17" s="84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="84" t="n"/>
+      <c r="L17" s="84" t="n"/>
+      <c r="M17" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N13" s="83" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="82" t="inlineStr">
-        <is>
-          <t>Indicador Oportuno de la Actividad Económica</t>
-        </is>
-      </c>
-      <c r="B14" s="82" t="inlineStr">
-        <is>
-          <t>principal</t>
-        </is>
-      </c>
-      <c r="C14" s="82" t="inlineStr">
-        <is>
-          <t>pendiente de confirmar serie</t>
-        </is>
-      </c>
-      <c r="D14" s="82" t="inlineStr">
+      <c r="N17" s="84" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="83" t="inlineStr">
+        <is>
+          <t>Tasa de interés objetivo</t>
+        </is>
+      </c>
+      <c r="B18" s="83" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C18" s="83" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D18" s="83" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="E14" s="82" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="F14" s="82" t="inlineStr">
+      <c r="E18" s="83" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F18" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G14" s="82" t="n"/>
-      <c r="H14" s="82" t="n"/>
-      <c r="I14" s="82" t="inlineStr">
-        <is>
-          <t>Fin de mes del periodo estimado</t>
-        </is>
-      </c>
-      <c r="J14" s="82" t="inlineStr">
-        <is>
-          <t>20 de agosto de 2026 · Julio 2026</t>
-        </is>
-      </c>
-      <c r="K14" s="82" t="n"/>
-      <c r="L14" s="82" t="n"/>
-      <c r="M14" s="82" t="inlineStr">
+      <c r="G18" s="83" t="n"/>
+      <c r="H18" s="83" t="n"/>
+      <c r="I18" s="83" t="inlineStr">
+        <is>
+          <t>Días de anuncio de política monetaria</t>
+        </is>
+      </c>
+      <c r="J18" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="83" t="n"/>
+      <c r="L18" s="83" t="n"/>
+      <c r="M18" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N14" s="82" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="83" t="inlineStr">
-        <is>
-          <t>Encuesta Mensual de la Industria Manufacturera</t>
-        </is>
-      </c>
-      <c r="B15" s="83" t="inlineStr">
-        <is>
-          <t>principal</t>
-        </is>
-      </c>
-      <c r="C15" s="83" t="inlineStr">
-        <is>
-          <t>pendiente de confirmar serie</t>
-        </is>
-      </c>
-      <c r="D15" s="83" t="inlineStr">
+      <c r="N18" s="83" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="84" t="inlineStr">
+        <is>
+          <t>Reservas internacionales</t>
+        </is>
+      </c>
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C19" s="84" t="inlineStr">
+        <is>
+          <t>pendiente de token</t>
+        </is>
+      </c>
+      <c r="D19" s="84" t="inlineStr">
         <is>
           <t>pendiente</t>
         </is>
       </c>
-      <c r="E15" s="83" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="F15" s="83" t="inlineStr">
+      <c r="E19" s="84" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F19" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="G15" s="83" t="n"/>
-      <c r="H15" s="83" t="n"/>
-      <c r="I15" s="83" t="inlineStr">
-        <is>
-          <t>Aproximadamente 40 días tras el cierre del mes</t>
-        </is>
-      </c>
-      <c r="J15" s="83" t="inlineStr">
-        <is>
-          <t>17 de agosto de 2026 · Junio 2026</t>
-        </is>
-      </c>
-      <c r="K15" s="83" t="n"/>
-      <c r="L15" s="83" t="n"/>
-      <c r="M15" s="83" t="inlineStr">
+      <c r="G19" s="84" t="n"/>
+      <c r="H19" s="84" t="n"/>
+      <c r="I19" s="84" t="inlineStr">
+        <is>
+          <t>Semanal (martes)</t>
+        </is>
+      </c>
+      <c r="J19" s="84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="84" t="n"/>
+      <c r="L19" s="84" t="n"/>
+      <c r="M19" s="84" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N15" s="83" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="82" t="inlineStr">
-        <is>
-          <t>Inversión Extranjera Directa (IED)</t>
-        </is>
-      </c>
-      <c r="B16" s="82" t="inlineStr">
-        <is>
-          <t>complementario</t>
-        </is>
-      </c>
-      <c r="C16" s="82" t="inlineStr">
-        <is>
-          <t>dato de respaldo vigente</t>
-        </is>
-      </c>
-      <c r="D16" s="82" t="inlineStr">
-        <is>
-          <t>respaldo</t>
-        </is>
-      </c>
-      <c r="E16" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G16" s="82" t="inlineStr">
-        <is>
-          <t>1T-26</t>
-        </is>
-      </c>
-      <c r="H16" s="82" t="inlineStr">
-        <is>
-          <t>1T-26</t>
-        </is>
-      </c>
-      <c r="I16" s="82" t="inlineStr">
-        <is>
-          <t>Aproximadamente 45 días posteriores al cierre del trimestre</t>
-        </is>
-      </c>
-      <c r="J16" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K16" s="82" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="L16" s="82" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="M16" s="82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N16" s="82" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="83" t="inlineStr">
-        <is>
-          <t>Tipo de cambio FIX</t>
-        </is>
-      </c>
-      <c r="B17" s="83" t="inlineStr">
-        <is>
-          <t>complementario</t>
-        </is>
-      </c>
-      <c r="C17" s="83" t="inlineStr">
-        <is>
-          <t>pendiente de token</t>
-        </is>
-      </c>
-      <c r="D17" s="83" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="E17" s="83" t="inlineStr">
-        <is>
-          <t>BANXICO</t>
-        </is>
-      </c>
-      <c r="F17" s="83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G17" s="83" t="n"/>
-      <c r="H17" s="83" t="n"/>
-      <c r="I17" s="83" t="inlineStr">
-        <is>
-          <t>Días hábiles</t>
-        </is>
-      </c>
-      <c r="J17" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K17" s="83" t="n"/>
-      <c r="L17" s="83" t="n"/>
-      <c r="M17" s="83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N17" s="83" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="82" t="inlineStr">
-        <is>
-          <t>Tasa de interés objetivo</t>
-        </is>
-      </c>
-      <c r="B18" s="82" t="inlineStr">
-        <is>
-          <t>complementario</t>
-        </is>
-      </c>
-      <c r="C18" s="82" t="inlineStr">
-        <is>
-          <t>pendiente de token</t>
-        </is>
-      </c>
-      <c r="D18" s="82" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="E18" s="82" t="inlineStr">
-        <is>
-          <t>BANXICO</t>
-        </is>
-      </c>
-      <c r="F18" s="82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G18" s="82" t="n"/>
-      <c r="H18" s="82" t="n"/>
-      <c r="I18" s="82" t="inlineStr">
-        <is>
-          <t>Días de anuncio de política monetaria</t>
-        </is>
-      </c>
-      <c r="J18" s="82" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K18" s="82" t="n"/>
-      <c r="L18" s="82" t="n"/>
-      <c r="M18" s="82" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N18" s="82" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="83" t="inlineStr">
-        <is>
-          <t>Reservas internacionales</t>
-        </is>
-      </c>
-      <c r="B19" s="83" t="inlineStr">
-        <is>
-          <t>complementario</t>
-        </is>
-      </c>
-      <c r="C19" s="83" t="inlineStr">
-        <is>
-          <t>pendiente de token</t>
-        </is>
-      </c>
-      <c r="D19" s="83" t="inlineStr">
-        <is>
-          <t>pendiente</t>
-        </is>
-      </c>
-      <c r="E19" s="83" t="inlineStr">
-        <is>
-          <t>BANXICO</t>
-        </is>
-      </c>
-      <c r="F19" s="83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G19" s="83" t="n"/>
-      <c r="H19" s="83" t="n"/>
-      <c r="I19" s="83" t="inlineStr">
-        <is>
-          <t>Semanal (martes)</t>
-        </is>
-      </c>
-      <c r="J19" s="83" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="83" t="n"/>
-      <c r="L19" s="83" t="n"/>
-      <c r="M19" s="83" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="N19" s="83" t="inlineStr"/>
+      <c r="N19" s="84" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="85" t="inlineStr">
+      <c r="A22" s="86" t="inlineStr">
         <is>
           <t>Advertencias del pipeline:</t>
         </is>
@@ -13492,119 +14251,28 @@
     <row r="23">
       <c r="A23" s="62" t="inlineStr">
         <is>
-          <t>• BANXICO_TOKEN ausente: se omiten tipo de cambio y tasa objetivo; se conservan datos previos.</t>
+          <t>• [TIPOCAMBIO] sin observaciones (estado: pendiente de token).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>• INEGI PIB: 33 observaciones (serie 737372, base BIE-BISE); última 1T-26 = 24973976.071; actualización BIE 18/06/2026 12:00:00 a. m..</t>
+          <t>• [TASA] sin observaciones (estado: pendiente de token).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="62" t="inlineStr">
         <is>
-          <t>• INEGI PIB: 33 observaciones (serie 737375, base BIE-BISE); última 1T-26 = 0.002423; actualización BIE 18/06/2026 12:00:00 a. m..</t>
+          <t>• [RESERVAS] sin observaciones (estado: pendiente de token).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="62" t="inlineStr">
         <is>
-          <t>• INEGI IGAE: 101 observaciones (serie 737121, base BIE-BISE); última May 26 = 108.595752; actualización BIE 23/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI IMAI: 101 observaciones (serie 737233, base BIE-BISE); última May 26 = 101.629971; actualización BIE 23/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI IMAI: 101 observaciones (serie 737234, base BIE-BISE); última May 26 = -0.007713; actualización BIE 23/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI DESOCUP: 102 observaciones (serie 444603, base BIE-BISE); última Jun 26 = 0.028985; actualización BIE 24/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI INPC: 102 observaciones (serie 334360, base BIE-BISE); última Jun 26 = 3.365977; actualización BIE 10/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI INPC: 102 observaciones (serie 334452, base BIE-BISE); última Jun 26 = 4.03192; actualización BIE 10/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI BALANZA: 102 observaciones (serie 33223, base BIE-BISE); última Jun 26 = 72551.015; actualización BIE 27/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="62" t="inlineStr">
-        <is>
-          <t>• INEGI BALANZA: 102 observaciones (serie 33226, base BIE-BISE); última Jun 26 = 68461.119; actualización BIE 27/07/2026 12:00:00 a. m..</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="62" t="inlineStr">
-        <is>
-          <t>• [IMFBCF] sin observaciones (estado: pendiente de confirmar serie).</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="62" t="inlineStr">
-        <is>
-          <t>• [IOAE] sin observaciones (estado: pendiente de confirmar serie).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="62" t="inlineStr">
-        <is>
-          <t>• [EMIM] sin observaciones (estado: pendiente de confirmar serie).</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="62" t="inlineStr">
-        <is>
-          <t>• [TIPOCAMBIO] sin observaciones (estado: pendiente de token).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="62" t="inlineStr">
-        <is>
-          <t>• [TASA] sin observaciones (estado: pendiente de token).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="62" t="inlineStr">
-        <is>
-          <t>• [RESERVAS] sin observaciones (estado: pendiente de token).</t>
+          <t>• [EMIM] el último dato de la serie primaria es nulo.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10253,7 +10253,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 31/07/2026 15:13 UTC</t>
+          <t>Generado: 03/08/2026 15:37 UTC</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-07-31T15:13:20+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-03T15:37:44+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -12747,12 +12747,12 @@
       </c>
       <c r="K7" s="83" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L7" s="83" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M7" s="83" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10254,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 03/08/2026 15:32 UTC</t>
+          <t>Generado: 03/08/2026 15:49 UTC</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-03T15:31:49+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-03T15:49:34+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10254,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 03/08/2026 15:49 UTC</t>
+          <t>Generado: 03/08/2026 22:33 UTC</t>
         </is>
       </c>
     </row>
@@ -10350,10 +10350,10 @@
         </is>
       </c>
       <c r="E6" s="65" t="n">
-        <v>856921.087012258</v>
+        <v>797675.498</v>
       </c>
       <c r="F6" s="65" t="n">
-        <v>7750175.3189237</v>
+        <v>7621773.386</v>
       </c>
       <c r="G6" s="65" t="inlineStr">
         <is>
@@ -10642,13 +10642,15 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="E15" s="64" t="n"/>
+      <c r="E15" s="64" t="n">
+        <v>110.4</v>
+      </c>
       <c r="F15" s="64" t="n">
         <v>-0.006</v>
       </c>
       <c r="G15" s="64" t="inlineStr">
         <is>
-          <t>Índice</t>
+          <t>Índice base 2018=100</t>
         </is>
       </c>
     </row>
@@ -12279,7 +12281,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice · Estado: dato de respaldo vigente</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: actualizado automáticamente</t>
         </is>
       </c>
     </row>
@@ -12306,7 +12308,9 @@
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="B5" s="82" t="n"/>
+      <c r="B5" s="82" t="n">
+        <v>107.7</v>
+      </c>
       <c r="C5" s="82" t="n">
         <v>0.011</v>
       </c>
@@ -12317,7 +12321,9 @@
           <t>Dic 24</t>
         </is>
       </c>
-      <c r="B6" s="82" t="n"/>
+      <c r="B6" s="82" t="n">
+        <v>99.2</v>
+      </c>
       <c r="C6" s="82" t="n">
         <v>-0.015</v>
       </c>
@@ -12328,9 +12334,11 @@
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="B7" s="82" t="n"/>
+      <c r="B7" s="82" t="n">
+        <v>106</v>
+      </c>
       <c r="C7" s="82" t="n">
-        <v>-0.003</v>
+        <v>0.026</v>
       </c>
     </row>
     <row r="8">
@@ -12339,9 +12347,11 @@
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="B8" s="82" t="n"/>
+      <c r="B8" s="82" t="n">
+        <v>113.5</v>
+      </c>
       <c r="C8" s="82" t="n">
-        <v>-0.007</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="9">
@@ -12350,7 +12360,9 @@
           <t>Abr 25</t>
         </is>
       </c>
-      <c r="B9" s="82" t="n"/>
+      <c r="B9" s="82" t="n">
+        <v>108.9</v>
+      </c>
       <c r="C9" s="82" t="n">
         <v>-0.001</v>
       </c>
@@ -12361,7 +12373,9 @@
           <t>May 25</t>
         </is>
       </c>
-      <c r="B10" s="82" t="n"/>
+      <c r="B10" s="82" t="n">
+        <v>112.1</v>
+      </c>
       <c r="C10" s="82" t="n">
         <v>0.01</v>
       </c>
@@ -12372,9 +12386,11 @@
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="B11" s="82" t="n"/>
+      <c r="B11" s="82" t="n">
+        <v>110.2</v>
+      </c>
       <c r="C11" s="82" t="n">
-        <v>-0.002</v>
+        <v>-0.027</v>
       </c>
     </row>
     <row r="12">
@@ -12383,7 +12399,9 @@
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="B12" s="82" t="n"/>
+      <c r="B12" s="82" t="n">
+        <v>109.1</v>
+      </c>
       <c r="C12" s="82" t="n">
         <v>0.002</v>
       </c>
@@ -12394,7 +12412,9 @@
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="B13" s="82" t="n"/>
+      <c r="B13" s="82" t="n">
+        <v>112.9</v>
+      </c>
       <c r="C13" s="82" t="n">
         <v>0.003</v>
       </c>
@@ -12405,7 +12425,9 @@
           <t>Dic 25</t>
         </is>
       </c>
-      <c r="B14" s="82" t="n"/>
+      <c r="B14" s="82" t="n">
+        <v>103.5</v>
+      </c>
       <c r="C14" s="82" t="n">
         <v>-0.001</v>
       </c>
@@ -12416,9 +12438,11 @@
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="B15" s="82" t="n"/>
+      <c r="B15" s="82" t="n">
+        <v>107.1</v>
+      </c>
       <c r="C15" s="82" t="n">
-        <v>-0.003</v>
+        <v>0.034</v>
       </c>
     </row>
     <row r="16">
@@ -12427,9 +12451,11 @@
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="B16" s="82" t="n"/>
+      <c r="B16" s="82" t="n">
+        <v>115.4</v>
+      </c>
       <c r="C16" s="82" t="n">
-        <v>0</v>
+        <v>-0.011</v>
       </c>
     </row>
     <row r="17">
@@ -12438,7 +12464,9 @@
           <t>Abr 26</t>
         </is>
       </c>
-      <c r="B17" s="82" t="n"/>
+      <c r="B17" s="82" t="n">
+        <v>111.2</v>
+      </c>
       <c r="C17" s="82" t="n">
         <v>0.005</v>
       </c>
@@ -12449,7 +12477,9 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="B18" s="82" t="n"/>
+      <c r="B18" s="82" t="n">
+        <v>110.4</v>
+      </c>
       <c r="C18" s="82" t="n">
         <v>-0.006</v>
       </c>
@@ -12582,7 +12612,7 @@
       </c>
       <c r="C5" s="84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>735882, 735883, 735888</t>
         </is>
       </c>
       <c r="D5" s="84" t="inlineStr">
@@ -12602,12 +12632,12 @@
       </c>
       <c r="G5" s="84" t="inlineStr">
         <is>
-          <t>INEGI BIE API</t>
+          <t>INEGI BIE API / boletín PIBT</t>
         </is>
       </c>
       <c r="H5" s="84" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/pib/#informacion_general</t>
+          <t>https://www.inegi.org.mx/temas/pib/</t>
         </is>
       </c>
     </row>
@@ -12960,17 +12990,17 @@
       </c>
       <c r="C14" s="83" t="inlineStr">
         <is>
-          <t>EMIM_pdf</t>
+          <t>796224</t>
         </is>
       </c>
       <c r="D14" s="83" t="inlineStr">
         <is>
-          <t>Índice</t>
+          <t>Índice base 2018=100</t>
         </is>
       </c>
       <c r="E14" s="83" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>Serie original; variación mensual desestacionalizada</t>
         </is>
       </c>
       <c r="F14" s="83" t="inlineStr">
@@ -12980,12 +13010,12 @@
       </c>
       <c r="G14" s="83" t="inlineStr">
         <is>
-          <t>INEGI boletín PDF</t>
+          <t>INEGI BIE API / boletín PDF</t>
         </is>
       </c>
       <c r="H14" s="83" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/emim/emim2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=0&amp;t=562444#D796224</t>
         </is>
       </c>
     </row>
@@ -13164,7 +13194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13193,7 +13223,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-03T15:49:34+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-03T22:33:27+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13350,12 +13380,12 @@
       </c>
       <c r="C6" s="83" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D6" s="83" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E6" s="83" t="inlineStr">
@@ -13365,7 +13395,7 @@
       </c>
       <c r="F6" s="83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G6" s="83" t="inlineStr">
@@ -13390,12 +13420,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13962,12 +13992,12 @@
       </c>
       <c r="C15" s="84" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D15" s="84" t="inlineStr">
         <is>
-          <t>respaldo</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E15" s="84" t="inlineStr">
@@ -13977,7 +14007,7 @@
       </c>
       <c r="F15" s="84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G15" s="84" t="inlineStr">
@@ -14266,13 +14296,6 @@
       <c r="A25" s="62" t="inlineStr">
         <is>
           <t>• [RESERVAS] sin observaciones (estado: pendiente de token).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="62" t="inlineStr">
-        <is>
-          <t>• [EMIM] el último dato de la serie primaria es nulo.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10254,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 03/08/2026 22:33 UTC</t>
+          <t>Generado: 04/08/2026 00:50 UTC</t>
         </is>
       </c>
     </row>
@@ -12612,7 +12612,7 @@
       </c>
       <c r="C5" s="84" t="inlineStr">
         <is>
-          <t>735882, 735883, 735888</t>
+          <t>735888</t>
         </is>
       </c>
       <c r="D5" s="84" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="G5" s="84" t="inlineStr">
         <is>
-          <t>INEGI BIE API / boletín PIBT</t>
+          <t>INEGI BIE API</t>
         </is>
       </c>
       <c r="H5" s="84" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/temas/pib/</t>
+          <t>https://www.inegi.org.mx/app/indicadores/?tm=3&amp;t=600267#D735888</t>
         </is>
       </c>
     </row>
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G14" s="83" t="inlineStr">
         <is>
-          <t>INEGI BIE API / boletín PDF</t>
+          <t>INEGI BIE API</t>
         </is>
       </c>
       <c r="H14" s="83" t="inlineStr">
@@ -13223,7 +13223,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-03T22:33:27+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-04T00:50:46+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -833,14 +833,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -883,16 +883,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -934,10 +934,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -960,18 +960,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1001,7 +1001,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1188,7 +1188,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1199,7 +1199,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1236,23 +1236,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1450,8 +1450,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1463,9 +1463,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1501,7 +1501,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1515,7 +1515,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1530,9 +1530,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1555,16 +1555,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1589,16 +1589,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1651,16 +1651,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1689,16 +1689,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1723,10 +1723,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1741,14 +1741,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1771,16 +1771,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1821,7 +1821,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1833,10 +1833,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1848,10 +1848,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1862,11 +1862,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1905,18 +1905,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2048,7 +2048,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2060,10 +2060,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2082,18 +2082,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2225,7 +2225,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2237,10 +2237,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2272,18 +2272,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2319,18 +2319,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2462,7 +2462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2474,10 +2474,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2497,18 +2497,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2651,8 +2651,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2664,9 +2664,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2704,7 +2704,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2721,16 +2721,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2759,16 +2759,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2793,10 +2793,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2811,14 +2811,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2846,16 +2846,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2897,10 +2897,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3017,10 +3017,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3137,10 +3137,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3148,18 +3148,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3313,7 +3313,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3325,10 +3325,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3338,18 +3338,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3473,8 +3473,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3486,9 +3486,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3525,7 +3525,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3540,9 +3540,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3565,16 +3565,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3600,16 +3600,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3662,16 +3662,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3700,16 +3700,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3734,10 +3734,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3752,14 +3752,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3782,16 +3782,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3832,7 +3832,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3844,10 +3844,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3872,18 +3872,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3908,18 +3908,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3950,7 +3950,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4067,7 +4067,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4078,7 +4078,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4095,18 +4095,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4241,7 +4241,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4253,10 +4253,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4282,18 +4282,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4438,8 +4438,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4451,9 +4451,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4490,7 +4490,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4507,16 +4507,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4545,16 +4545,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4579,10 +4579,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4597,14 +4597,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4635,16 +4635,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4686,10 +4686,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4700,10 +4700,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4713,16 +4713,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4757,16 +4757,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4796,7 +4796,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4928,7 +4928,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4940,10 +4940,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4955,16 +4955,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5005,10 +5005,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5019,11 +5019,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5051,16 +5051,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5086,16 +5086,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5240,8 +5240,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5253,9 +5253,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5291,7 +5291,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5306,9 +5306,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5331,16 +5331,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5366,16 +5366,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5428,16 +5428,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5466,16 +5466,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5500,10 +5500,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5518,14 +5518,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5557,16 +5557,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5608,10 +5608,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5818,7 +5818,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5829,7 +5829,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5896,18 +5896,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6088,8 +6088,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6101,9 +6101,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6139,7 +6139,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6156,16 +6156,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6218,16 +6218,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6257,16 +6257,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6291,10 +6291,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6309,14 +6309,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6340,16 +6340,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6391,10 +6391,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6404,18 +6404,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6443,18 +6443,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6482,18 +6482,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6521,18 +6521,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6560,18 +6560,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6597,18 +6597,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6639,7 +6639,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6833,10 +6833,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7035,8 +7035,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7048,9 +7048,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7086,7 +7086,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7101,9 +7101,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7132,16 +7132,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7167,16 +7167,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7206,16 +7206,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7240,10 +7240,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7258,14 +7258,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7288,16 +7288,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7338,7 +7338,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
+            <a:pattFill prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7346,7 +7346,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7355,16 +7355,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7511,7 +7511,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7523,10 +7523,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7586,16 +7586,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7773,16 +7773,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7811,16 +7811,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7845,10 +7845,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7863,14 +7863,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7898,16 +7898,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7949,10 +7949,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8117,10 +8117,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8285,10 +8285,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8469,7 +8469,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8481,10 +8481,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8497,18 +8497,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8707,8 +8707,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8720,9 +8720,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8758,7 +8758,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8775,16 +8775,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8813,16 +8813,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8847,10 +8847,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8865,14 +8865,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8895,16 +8895,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8945,7 +8945,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8957,10 +8957,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9012,16 +9012,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9060,16 +9060,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9220,7 +9220,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9231,7 +9231,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9258,16 +9258,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9411,8 +9411,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9424,9 +9424,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9463,7 +9463,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9479,16 +9479,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9543,16 +9543,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9581,16 +9581,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9615,10 +9615,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9633,7 +9633,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9653,9 +9653,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9665,7 +9665,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9685,9 +9685,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9697,7 +9697,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9717,9 +9717,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9729,7 +9729,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9749,9 +9749,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9761,7 +9761,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9781,9 +9781,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9793,7 +9793,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9813,9 +9813,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9825,7 +9825,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9845,9 +9845,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9857,7 +9857,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9877,9 +9877,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9889,7 +9889,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9909,9 +9909,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9921,7 +9921,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9941,9 +9941,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10254,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/08/2026 00:50 UTC</t>
+          <t>Generado: 04/08/2026 15:15 UTC</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13223,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-04T00:50:46+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-04T15:15:58+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13352,12 +13352,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13420,12 +13420,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13488,12 +13488,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13552,12 +13552,12 @@
       </c>
       <c r="K8" s="85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L8" s="85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M8" s="85" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13692,12 +13692,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13756,12 +13756,12 @@
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -14032,12 +14032,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -833,14 +833,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -883,16 +883,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -934,10 +934,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -960,18 +960,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1001,7 +1001,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1188,7 +1188,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1199,7 +1199,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1236,23 +1236,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1450,8 +1450,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1463,9 +1463,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1501,7 +1501,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1515,7 +1515,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1530,9 +1530,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1555,16 +1555,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1589,16 +1589,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1651,16 +1651,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1689,16 +1689,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1723,10 +1723,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1741,14 +1741,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1771,16 +1771,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1821,7 +1821,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1833,10 +1833,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1848,10 +1848,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1862,11 +1862,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1905,18 +1905,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2048,7 +2048,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2060,10 +2060,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2082,18 +2082,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2225,7 +2225,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2237,10 +2237,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2272,18 +2272,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2319,18 +2319,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2462,7 +2462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2474,10 +2474,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2497,18 +2497,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2651,8 +2651,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2664,9 +2664,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2704,7 +2704,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2721,16 +2721,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2759,16 +2759,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2793,10 +2793,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2811,14 +2811,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2846,16 +2846,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2897,10 +2897,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3017,10 +3017,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3137,10 +3137,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3148,18 +3148,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3313,7 +3313,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3325,10 +3325,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3338,18 +3338,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3473,8 +3473,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3486,9 +3486,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3525,7 +3525,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3540,9 +3540,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3565,16 +3565,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3600,16 +3600,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3662,16 +3662,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3700,16 +3700,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3734,10 +3734,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3752,14 +3752,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3782,16 +3782,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3832,7 +3832,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3844,10 +3844,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="19050">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3872,18 +3872,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3908,18 +3908,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3950,7 +3950,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4067,7 +4067,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4078,7 +4078,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4095,18 +4095,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4241,7 +4241,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4253,10 +4253,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4282,18 +4282,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4438,8 +4438,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4451,9 +4451,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4490,7 +4490,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4507,16 +4507,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4545,16 +4545,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4579,10 +4579,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4597,14 +4597,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4635,16 +4635,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4686,10 +4686,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4700,10 +4700,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4713,16 +4713,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4757,16 +4757,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4796,7 +4796,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4928,7 +4928,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4940,10 +4940,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4955,16 +4955,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5005,10 +5005,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5019,11 +5019,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5051,16 +5051,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5086,16 +5086,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5240,8 +5240,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5253,9 +5253,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5291,7 +5291,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5306,9 +5306,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5331,16 +5331,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5366,16 +5366,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5428,16 +5428,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5466,16 +5466,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5500,10 +5500,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5518,14 +5518,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5557,16 +5557,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5608,10 +5608,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5818,7 +5818,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5829,7 +5829,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5896,18 +5896,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6088,8 +6088,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6101,9 +6101,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6139,7 +6139,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6156,16 +6156,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6218,16 +6218,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6257,16 +6257,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6291,10 +6291,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6309,14 +6309,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6340,16 +6340,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6391,10 +6391,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6404,18 +6404,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6443,18 +6443,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6482,18 +6482,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6521,18 +6521,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6560,18 +6560,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6597,18 +6597,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6639,7 +6639,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6833,10 +6833,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7035,8 +7035,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7048,9 +7048,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7086,7 +7086,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7101,9 +7101,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7132,16 +7132,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7167,16 +7167,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7206,16 +7206,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7240,10 +7240,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7258,14 +7258,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7288,16 +7288,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7338,7 +7338,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="pct20">
+            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7346,7 +7346,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln w="38100">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7355,16 +7355,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7511,7 +7511,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7523,10 +7523,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7586,16 +7586,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7773,16 +7773,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7811,16 +7811,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7845,10 +7845,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7863,14 +7863,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7898,16 +7898,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7949,10 +7949,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8117,10 +8117,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8285,10 +8285,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8469,7 +8469,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8481,10 +8481,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8497,18 +8497,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8707,8 +8707,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8720,9 +8720,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8758,7 +8758,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8775,16 +8775,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8813,16 +8813,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8847,10 +8847,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8865,14 +8865,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8895,16 +8895,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8945,7 +8945,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8957,10 +8957,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9012,16 +9012,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9060,16 +9060,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9220,7 +9220,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9231,7 +9231,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9258,16 +9258,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9411,8 +9411,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9424,9 +9424,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9463,7 +9463,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9479,16 +9479,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9543,16 +9543,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9581,16 +9581,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9615,10 +9615,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9633,7 +9633,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9653,9 +9653,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9665,7 +9665,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9685,9 +9685,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9697,7 +9697,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9717,9 +9717,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9729,7 +9729,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9749,9 +9749,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9761,7 +9761,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9781,9 +9781,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9793,7 +9793,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9813,9 +9813,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9825,7 +9825,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9845,9 +9845,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9857,7 +9857,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9877,9 +9877,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9889,7 +9889,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9909,9 +9909,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9921,7 +9921,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9941,9 +9941,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10254,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/08/2026 15:15 UTC</t>
+          <t>Generado: 04/08/2026 15:21 UTC</t>
         </is>
       </c>
     </row>
@@ -13223,7 +13223,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-04T15:15:58+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-04T15:21:26+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13824,12 +13824,12 @@
       </c>
       <c r="K12" s="85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L12" s="85" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M12" s="85" t="inlineStr">
@@ -13896,12 +13896,12 @@
       </c>
       <c r="K13" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L13" s="84" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M13" s="84" t="inlineStr">
@@ -13964,12 +13964,12 @@
       </c>
       <c r="K14" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L14" s="83" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M14" s="83" t="inlineStr">
@@ -14128,7 +14128,7 @@
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>pendiente de token</t>
+          <t>no disponible</t>
         </is>
       </c>
       <c r="D17" s="84" t="inlineStr">
@@ -14143,7 +14143,7 @@
       </c>
       <c r="F17" s="84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G17" s="84" t="n"/>
@@ -14180,7 +14180,7 @@
       </c>
       <c r="C18" s="83" t="inlineStr">
         <is>
-          <t>pendiente de token</t>
+          <t>no disponible</t>
         </is>
       </c>
       <c r="D18" s="83" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="F18" s="83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G18" s="83" t="n"/>
@@ -14232,7 +14232,7 @@
       </c>
       <c r="C19" s="84" t="inlineStr">
         <is>
-          <t>pendiente de token</t>
+          <t>no disponible</t>
         </is>
       </c>
       <c r="D19" s="84" t="inlineStr">
@@ -14247,7 +14247,7 @@
       </c>
       <c r="F19" s="84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="G19" s="84" t="n"/>
@@ -14281,21 +14281,21 @@
     <row r="23">
       <c r="A23" s="62" t="inlineStr">
         <is>
-          <t>• [TIPOCAMBIO] sin observaciones (estado: pendiente de token).</t>
+          <t>• [TIPOCAMBIO] sin observaciones (estado: no disponible).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="62" t="inlineStr">
         <is>
-          <t>• [TASA] sin observaciones (estado: pendiente de token).</t>
+          <t>• [TASA] sin observaciones (estado: no disponible).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="62" t="inlineStr">
         <is>
-          <t>• [RESERVAS] sin observaciones (estado: pendiente de token).</t>
+          <t>• [RESERVAS] sin observaciones (estado: no disponible).</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -833,14 +833,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -883,16 +883,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -934,10 +934,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -960,18 +960,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1001,7 +1001,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1188,7 +1188,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1199,7 +1199,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1236,23 +1236,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1450,8 +1450,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1463,9 +1463,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1501,7 +1501,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1515,7 +1515,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1530,9 +1530,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1555,16 +1555,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1589,16 +1589,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1651,16 +1651,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1689,16 +1689,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1723,10 +1723,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1741,14 +1741,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1771,16 +1771,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1821,7 +1821,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1833,10 +1833,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1848,10 +1848,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1862,11 +1862,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1905,18 +1905,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2048,7 +2048,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2060,10 +2060,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2082,18 +2082,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2225,7 +2225,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2237,10 +2237,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2272,18 +2272,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2319,18 +2319,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2462,7 +2462,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2474,10 +2474,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2497,18 +2497,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2651,8 +2651,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2664,9 +2664,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2704,7 +2704,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2721,16 +2721,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2759,16 +2759,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2793,10 +2793,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2811,14 +2811,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2846,16 +2846,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2897,10 +2897,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3017,10 +3017,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3137,10 +3137,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3148,18 +3148,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3313,7 +3313,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3325,10 +3325,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3338,18 +3338,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3473,8 +3473,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3486,9 +3486,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3525,7 +3525,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3540,9 +3540,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3565,16 +3565,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3600,16 +3600,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3662,16 +3662,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3700,16 +3700,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3734,10 +3734,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3752,14 +3752,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3782,16 +3782,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3832,7 +3832,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3844,10 +3844,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3872,18 +3872,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3908,18 +3908,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3950,7 +3950,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4067,7 +4067,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4078,7 +4078,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4095,18 +4095,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4241,7 +4241,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4253,10 +4253,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4282,18 +4282,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4438,8 +4438,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4451,9 +4451,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4490,7 +4490,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4507,16 +4507,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4545,16 +4545,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4579,10 +4579,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4597,14 +4597,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4635,16 +4635,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4686,10 +4686,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4700,10 +4700,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4713,16 +4713,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4757,16 +4757,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4796,7 +4796,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4928,7 +4928,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4940,10 +4940,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4955,16 +4955,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5005,10 +5005,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5019,11 +5019,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5051,16 +5051,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5086,16 +5086,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5240,8 +5240,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5253,9 +5253,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5291,7 +5291,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5306,9 +5306,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5331,16 +5331,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5366,16 +5366,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5428,16 +5428,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5466,16 +5466,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5500,10 +5500,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5518,14 +5518,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5557,16 +5557,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5608,10 +5608,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5818,7 +5818,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5829,7 +5829,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5896,18 +5896,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6088,8 +6088,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6101,9 +6101,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6139,7 +6139,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6156,16 +6156,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6218,16 +6218,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6257,16 +6257,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6291,10 +6291,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6309,14 +6309,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6340,16 +6340,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6391,10 +6391,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6404,18 +6404,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6443,18 +6443,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6482,18 +6482,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6521,18 +6521,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6560,18 +6560,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6597,18 +6597,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6639,7 +6639,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6833,10 +6833,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7035,8 +7035,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7048,9 +7048,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7086,7 +7086,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7101,9 +7101,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7132,16 +7132,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7167,16 +7167,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7206,16 +7206,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7240,10 +7240,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7258,14 +7258,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7288,16 +7288,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7338,7 +7338,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
+            <a:pattFill prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7346,7 +7346,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7355,16 +7355,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7511,7 +7511,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7523,10 +7523,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7586,16 +7586,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7773,16 +7773,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7811,16 +7811,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7845,10 +7845,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7863,14 +7863,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7898,16 +7898,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7949,10 +7949,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8117,10 +8117,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8285,10 +8285,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8469,7 +8469,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8481,10 +8481,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8497,18 +8497,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8707,8 +8707,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8720,9 +8720,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8758,7 +8758,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8775,16 +8775,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8813,16 +8813,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8847,10 +8847,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8865,14 +8865,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8895,16 +8895,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8945,7 +8945,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8957,10 +8957,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9012,16 +9012,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9060,16 +9060,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9220,7 +9220,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9231,7 +9231,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9258,16 +9258,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9411,8 +9411,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9424,9 +9424,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9463,7 +9463,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9479,16 +9479,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9543,16 +9543,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9581,16 +9581,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9615,10 +9615,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9633,7 +9633,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9653,9 +9653,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9665,7 +9665,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9685,9 +9685,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9697,7 +9697,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9717,9 +9717,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9729,7 +9729,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9749,9 +9749,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9761,7 +9761,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9781,9 +9781,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9793,7 +9793,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9813,9 +9813,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9825,7 +9825,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9845,9 +9845,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9857,7 +9857,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9877,9 +9877,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9889,7 +9889,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9909,9 +9909,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9921,7 +9921,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9941,9 +9941,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10254,7 +10254,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/08/2026 15:21 UTC</t>
+          <t>Generado: 04/08/2026 16:20 UTC</t>
         </is>
       </c>
     </row>
@@ -10690,21 +10690,27 @@
     <row r="17">
       <c r="A17" s="64" t="inlineStr">
         <is>
-          <t>Tipo de cambio FIX</t>
+          <t>Tipo de cambio FIX (pesos por dólar)</t>
         </is>
       </c>
       <c r="B17" s="64" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="C17" s="64" t="inlineStr">
         <is>
-          <t>Diaria</t>
-        </is>
-      </c>
-      <c r="D17" s="64" t="n"/>
-      <c r="E17" s="64" t="n"/>
+          <t>Diaria-&gt;mensual</t>
+        </is>
+      </c>
+      <c r="D17" s="64" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="E17" s="64" t="n">
+        <v>17.3317</v>
+      </c>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="inlineStr">
         <is>
@@ -10715,21 +10721,27 @@
     <row r="18">
       <c r="A18" s="65" t="inlineStr">
         <is>
-          <t>Tasa de interés objetivo</t>
+          <t>Tasa objetivo de Banco de México</t>
         </is>
       </c>
       <c r="B18" s="65" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="C18" s="65" t="inlineStr">
         <is>
-          <t>Por reunión</t>
-        </is>
-      </c>
-      <c r="D18" s="65" t="n"/>
-      <c r="E18" s="65" t="n"/>
+          <t>Diaria-&gt;mensual</t>
+        </is>
+      </c>
+      <c r="D18" s="65" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="E18" s="65" t="n">
+        <v>6.5</v>
+      </c>
       <c r="F18" s="65" t="n"/>
       <c r="G18" s="65" t="inlineStr">
         <is>
@@ -10745,16 +10757,22 @@
       </c>
       <c r="B19" s="64" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="C19" s="64" t="inlineStr">
         <is>
-          <t>Semanal</t>
-        </is>
-      </c>
-      <c r="D19" s="64" t="n"/>
-      <c r="E19" s="64" t="n"/>
+          <t>Semanal-&gt;mensual</t>
+        </is>
+      </c>
+      <c r="D19" s="64" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="E19" s="64" t="n">
+        <v>255498.1</v>
+      </c>
       <c r="F19" s="64" t="n"/>
       <c r="G19" s="64" t="inlineStr">
         <is>
@@ -13060,17 +13078,17 @@
     <row r="16">
       <c r="A16" s="83" t="inlineStr">
         <is>
-          <t>Tipo de cambio FIX</t>
+          <t>Tipo de cambio FIX (pesos por dólar)</t>
         </is>
       </c>
       <c r="B16" s="83" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="C16" s="83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SF43718</t>
         </is>
       </c>
       <c r="D16" s="83" t="inlineStr">
@@ -13085,7 +13103,7 @@
       </c>
       <c r="F16" s="83" t="inlineStr">
         <is>
-          <t>Diaria</t>
+          <t>Diaria-&gt;mensual</t>
         </is>
       </c>
       <c r="G16" s="83" t="inlineStr">
@@ -13102,17 +13120,17 @@
     <row r="17">
       <c r="A17" s="84" t="inlineStr">
         <is>
-          <t>Tasa de interés objetivo</t>
+          <t>Tasa objetivo de Banco de México</t>
         </is>
       </c>
       <c r="B17" s="84" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SF61745</t>
         </is>
       </c>
       <c r="D17" s="84" t="inlineStr">
@@ -13127,7 +13145,7 @@
       </c>
       <c r="F17" s="84" t="inlineStr">
         <is>
-          <t>Por reunión</t>
+          <t>Diaria-&gt;mensual</t>
         </is>
       </c>
       <c r="G17" s="84" t="inlineStr">
@@ -13149,12 +13167,12 @@
       </c>
       <c r="B18" s="83" t="inlineStr">
         <is>
-          <t>Banco de México</t>
+          <t>Banco de México (SIE)</t>
         </is>
       </c>
       <c r="C18" s="83" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SF43707</t>
         </is>
       </c>
       <c r="D18" s="83" t="inlineStr">
@@ -13169,7 +13187,7 @@
       </c>
       <c r="F18" s="83" t="inlineStr">
         <is>
-          <t>Semanal</t>
+          <t>Semanal-&gt;mensual</t>
         </is>
       </c>
       <c r="G18" s="83" t="inlineStr">
@@ -13194,7 +13212,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13223,7 +13241,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-04T15:21:26+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-04T16:20:24+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -14118,7 +14136,7 @@
     <row r="17">
       <c r="A17" s="84" t="inlineStr">
         <is>
-          <t>Tipo de cambio FIX</t>
+          <t>Tipo de cambio FIX (pesos por dólar)</t>
         </is>
       </c>
       <c r="B17" s="84" t="inlineStr">
@@ -14128,12 +14146,12 @@
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>no disponible</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D17" s="84" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E17" s="84" t="inlineStr">
@@ -14146,8 +14164,16 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G17" s="84" t="n"/>
-      <c r="H17" s="84" t="n"/>
+      <c r="G17" s="84" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="H17" s="84" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
       <c r="I17" s="84" t="inlineStr">
         <is>
           <t>Días hábiles</t>
@@ -14158,8 +14184,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="84" t="n"/>
-      <c r="L17" s="84" t="n"/>
+      <c r="K17" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L17" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="M17" s="84" t="inlineStr">
         <is>
           <t>No</t>
@@ -14170,7 +14204,7 @@
     <row r="18">
       <c r="A18" s="83" t="inlineStr">
         <is>
-          <t>Tasa de interés objetivo</t>
+          <t>Tasa objetivo de Banco de México</t>
         </is>
       </c>
       <c r="B18" s="83" t="inlineStr">
@@ -14180,12 +14214,12 @@
       </c>
       <c r="C18" s="83" t="inlineStr">
         <is>
-          <t>no disponible</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D18" s="83" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E18" s="83" t="inlineStr">
@@ -14198,8 +14232,16 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G18" s="83" t="n"/>
-      <c r="H18" s="83" t="n"/>
+      <c r="G18" s="83" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
+      <c r="H18" s="83" t="inlineStr">
+        <is>
+          <t>Ago 26</t>
+        </is>
+      </c>
       <c r="I18" s="83" t="inlineStr">
         <is>
           <t>Días de anuncio de política monetaria</t>
@@ -14210,8 +14252,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K18" s="83" t="n"/>
-      <c r="L18" s="83" t="n"/>
+      <c r="K18" s="83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L18" s="83" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="M18" s="83" t="inlineStr">
         <is>
           <t>No</t>
@@ -14232,12 +14282,12 @@
       </c>
       <c r="C19" s="84" t="inlineStr">
         <is>
-          <t>no disponible</t>
+          <t>actualizado automáticamente</t>
         </is>
       </c>
       <c r="D19" s="84" t="inlineStr">
         <is>
-          <t>pendiente</t>
+          <t>api</t>
         </is>
       </c>
       <c r="E19" s="84" t="inlineStr">
@@ -14250,8 +14300,16 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="G19" s="84" t="n"/>
-      <c r="H19" s="84" t="n"/>
+      <c r="G19" s="84" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="H19" s="84" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
       <c r="I19" s="84" t="inlineStr">
         <is>
           <t>Semanal (martes)</t>
@@ -14262,8 +14320,16 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="84" t="n"/>
-      <c r="L19" s="84" t="n"/>
+      <c r="K19" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="L19" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
       <c r="M19" s="84" t="inlineStr">
         <is>
           <t>No</t>
@@ -14275,27 +14341,6 @@
       <c r="A22" s="86" t="inlineStr">
         <is>
           <t>Advertencias del pipeline:</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="62" t="inlineStr">
-        <is>
-          <t>• [TIPOCAMBIO] sin observaciones (estado: no disponible).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="62" t="inlineStr">
-        <is>
-          <t>• [TASA] sin observaciones (estado: no disponible).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t>• [RESERVAS] sin observaciones (estado: no disponible).</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -169,7 +169,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -214,11 +214,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F5EF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6E2E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -475,7 +470,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -691,9 +686,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
@@ -833,14 +825,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -883,16 +875,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -934,10 +926,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -960,18 +952,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1001,7 +993,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1188,7 +1180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1199,7 +1191,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1236,23 +1228,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1450,8 +1442,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1463,9 +1455,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1501,7 +1493,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1515,7 +1507,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1530,9 +1522,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1555,16 +1547,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1589,16 +1581,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1651,16 +1643,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1689,16 +1681,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1723,10 +1715,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1741,14 +1733,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1771,16 +1763,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1821,7 +1813,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1833,10 +1825,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1848,10 +1840,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1862,11 +1854,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1905,18 +1897,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2048,7 +2040,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2060,10 +2052,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2082,18 +2074,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2225,7 +2217,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2237,10 +2229,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2272,18 +2264,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2319,18 +2311,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2462,7 +2454,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2474,10 +2466,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2497,18 +2489,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2651,8 +2643,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2664,9 +2656,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2704,7 +2696,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2721,16 +2713,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2759,16 +2751,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2793,10 +2785,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2811,14 +2803,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2846,16 +2838,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2897,10 +2889,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3017,10 +3009,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3137,10 +3129,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3148,18 +3140,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3313,7 +3305,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3325,10 +3317,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3338,18 +3330,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3473,8 +3465,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3486,9 +3478,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3525,7 +3517,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3540,9 +3532,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3565,16 +3557,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3600,16 +3592,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3662,16 +3654,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3700,16 +3692,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3734,10 +3726,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3752,14 +3744,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3782,16 +3774,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3832,7 +3824,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3844,10 +3836,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="19050">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3872,18 +3864,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3908,18 +3900,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3950,7 +3942,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4067,7 +4059,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4078,7 +4070,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4095,18 +4087,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4241,7 +4233,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4253,10 +4245,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4282,18 +4274,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4438,8 +4430,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4451,9 +4443,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4490,7 +4482,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4507,16 +4499,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4545,16 +4537,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4579,10 +4571,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4597,14 +4589,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4635,16 +4627,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4686,10 +4678,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4700,10 +4692,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4713,16 +4705,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4757,16 +4749,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4796,7 +4788,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4928,7 +4920,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4940,10 +4932,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4955,16 +4947,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5005,10 +4997,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5019,11 +5011,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5051,16 +5043,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5086,16 +5078,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5240,8 +5232,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5253,9 +5245,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5291,7 +5283,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5306,9 +5298,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5331,16 +5323,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5366,16 +5358,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5428,16 +5420,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5466,16 +5458,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5500,10 +5492,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5518,14 +5510,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5557,16 +5549,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5608,10 +5600,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5818,7 +5810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5829,7 +5821,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5896,18 +5888,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6088,8 +6080,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6101,9 +6093,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6139,7 +6131,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6156,16 +6148,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6218,16 +6210,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6257,16 +6249,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6291,10 +6283,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6309,14 +6301,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6340,16 +6332,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6391,10 +6383,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6404,18 +6396,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6443,18 +6435,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6482,18 +6474,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6521,18 +6513,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6560,18 +6552,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6597,18 +6589,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6639,7 +6631,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6833,10 +6825,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7035,8 +7027,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7048,9 +7040,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7086,7 +7078,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7101,9 +7093,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7132,16 +7124,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7167,16 +7159,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7206,16 +7198,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7240,10 +7232,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7258,14 +7250,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7288,16 +7280,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7338,7 +7330,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="pct20">
+            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7346,7 +7338,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln w="38100">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7355,16 +7347,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7511,7 +7503,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7523,10 +7515,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7586,16 +7578,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7773,16 +7765,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7811,16 +7803,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7845,10 +7837,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7863,14 +7855,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7898,16 +7890,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7949,10 +7941,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8117,10 +8109,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8285,10 +8277,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8469,7 +8461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8481,10 +8473,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8497,18 +8489,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8707,8 +8699,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8720,9 +8712,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8758,7 +8750,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8775,16 +8767,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8813,16 +8805,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8847,10 +8839,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8865,14 +8857,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8895,16 +8887,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8945,7 +8937,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8957,10 +8949,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9012,16 +9004,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9060,16 +9052,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9220,7 +9212,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9231,7 +9223,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9258,16 +9250,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9411,8 +9403,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9424,9 +9416,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9463,7 +9455,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9479,16 +9471,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9543,16 +9535,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9581,16 +9573,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9615,10 +9607,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9633,7 +9625,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9653,9 +9645,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9665,7 +9657,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9685,9 +9677,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9697,7 +9689,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9717,9 +9709,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9729,7 +9721,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9749,9 +9741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9761,7 +9753,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9781,9 +9773,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9793,7 +9785,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9813,9 +9805,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9825,7 +9817,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9845,9 +9837,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9857,7 +9849,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9877,9 +9869,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9889,7 +9881,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9909,9 +9901,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9921,7 +9913,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9941,9 +9933,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10254,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/08/2026 16:20 UTC</t>
+          <t>Generado: 04/08/2026 20:06 UTC</t>
         </is>
       </c>
     </row>
@@ -10709,7 +10701,7 @@
         </is>
       </c>
       <c r="E17" s="64" t="n">
-        <v>17.3317</v>
+        <v>17.2717</v>
       </c>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="inlineStr">
@@ -11608,12 +11600,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11646,6 +11639,11 @@
           <t>Var. mensual (%)</t>
         </is>
       </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Var. anual (%)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="82" t="inlineStr">
@@ -11659,6 +11657,7 @@
       <c r="C5" s="82" t="n">
         <v>0.001</v>
       </c>
+      <c r="D5" s="82" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
@@ -11672,6 +11671,9 @@
       <c r="C6" s="82" t="n">
         <v>0.001</v>
       </c>
+      <c r="D6" s="82" t="n">
+        <v>-0.003</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="82" t="inlineStr">
@@ -11685,6 +11687,9 @@
       <c r="C7" s="82" t="n">
         <v>-0.026</v>
       </c>
+      <c r="D7" s="82" t="n">
+        <v>-0.041</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="82" t="inlineStr">
@@ -11698,6 +11703,9 @@
       <c r="C8" s="82" t="n">
         <v>-0.015</v>
       </c>
+      <c r="D8" s="82" t="n">
+        <v>-0.059</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="82" t="inlineStr">
@@ -11711,6 +11719,9 @@
       <c r="C9" s="82" t="n">
         <v>0.001</v>
       </c>
+      <c r="D9" s="82" t="n">
+        <v>-0.06</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
@@ -11724,6 +11735,9 @@
       <c r="C10" s="82" t="n">
         <v>0.003</v>
       </c>
+      <c r="D10" s="82" t="n">
+        <v>-0.047</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="82" t="inlineStr">
@@ -11737,6 +11751,9 @@
       <c r="C11" s="82" t="n">
         <v>-0.017</v>
       </c>
+      <c r="D11" s="82" t="n">
+        <v>-0.077</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
@@ -11750,6 +11767,9 @@
       <c r="C12" s="82" t="n">
         <v>0.008999999999999999</v>
       </c>
+      <c r="D12" s="82" t="n">
+        <v>-0.067</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="82" t="inlineStr">
@@ -11763,6 +11783,9 @@
       <c r="C13" s="82" t="n">
         <v>-0.014</v>
       </c>
+      <c r="D13" s="82" t="n">
+        <v>-0.068</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="82" t="inlineStr">
@@ -11776,6 +11799,9 @@
       <c r="C14" s="82" t="n">
         <v>0.016</v>
       </c>
+      <c r="D14" s="82" t="n">
+        <v>-0.07199999999999999</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="82" t="inlineStr">
@@ -11789,6 +11815,9 @@
       <c r="C15" s="82" t="n">
         <v>-0.027</v>
       </c>
+      <c r="D15" s="82" t="n">
+        <v>-0.089</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="82" t="inlineStr">
@@ -11802,6 +11831,9 @@
       <c r="C16" s="82" t="n">
         <v>-0.003</v>
       </c>
+      <c r="D16" s="82" t="n">
+        <v>-0.08400000000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="82" t="inlineStr">
@@ -11815,6 +11847,9 @@
       <c r="C17" s="82" t="n">
         <v>0.008999999999999999</v>
       </c>
+      <c r="D17" s="82" t="n">
+        <v>-0.058</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="82" t="inlineStr">
@@ -11828,6 +11863,9 @@
       <c r="C18" s="82" t="n">
         <v>0.004</v>
       </c>
+      <c r="D18" s="82" t="n">
+        <v>-0.057</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="82" t="inlineStr">
@@ -11841,6 +11879,9 @@
       <c r="C19" s="82" t="n">
         <v>0.005</v>
       </c>
+      <c r="D19" s="82" t="n">
+        <v>-0.016</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="82" t="inlineStr">
@@ -11854,6 +11895,9 @@
       <c r="C20" s="82" t="n">
         <v>-0.011</v>
       </c>
+      <c r="D20" s="82" t="n">
+        <v>-0.022</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="82" t="inlineStr">
@@ -11867,6 +11911,9 @@
       <c r="C21" s="82" t="n">
         <v>-0.008</v>
       </c>
+      <c r="D21" s="82" t="n">
+        <v>-0.036</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="82" t="inlineStr">
@@ -11880,6 +11927,9 @@
       <c r="C22" s="82" t="n">
         <v>0.004</v>
       </c>
+      <c r="D22" s="82" t="n">
+        <v>-0.031</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="82" t="inlineStr">
@@ -11892,6 +11942,9 @@
       </c>
       <c r="C23" s="82" t="n">
         <v>0.04</v>
+      </c>
+      <c r="D23" s="82" t="n">
+        <v>0.051</v>
       </c>
     </row>
   </sheetData>
@@ -12598,7 +12651,7 @@
       </c>
       <c r="E4" s="83" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>Serie original; la variación trimestral y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
         </is>
       </c>
       <c r="F4" s="83" t="inlineStr">
@@ -12640,7 +12693,7 @@
       </c>
       <c r="E5" s="84" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>Serie original; la variación trimestral y anual de terciarias proviene de la serie desestacionalizada publicada por el INEGI</t>
         </is>
       </c>
       <c r="F5" s="84" t="inlineStr">
@@ -12682,7 +12735,7 @@
       </c>
       <c r="E6" s="83" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>Serie original; la variación mensual y anual proviene de la serie desestacionalizada publicada por el INEGI</t>
         </is>
       </c>
       <c r="F6" s="83" t="inlineStr">
@@ -12892,7 +12945,7 @@
       </c>
       <c r="E11" s="84" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
         </is>
       </c>
       <c r="F11" s="84" t="inlineStr">
@@ -12934,7 +12987,7 @@
       </c>
       <c r="E12" s="83" t="inlineStr">
         <is>
-          <t>Serie original</t>
+          <t>Serie desestacionalizada; índice y variaciones oficiales del boletín del INEGI</t>
         </is>
       </c>
       <c r="F12" s="83" t="inlineStr">
@@ -13241,7 +13294,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-04T16:20:24+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-04T20:06:32+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13522,72 +13575,68 @@
       <c r="N7" s="84" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="85" t="inlineStr">
+      <c r="A8" s="83" t="inlineStr">
         <is>
           <t>Indicador Mensual de la Actividad Industrial</t>
         </is>
       </c>
-      <c r="B8" s="85" t="inlineStr">
+      <c r="B8" s="83" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C8" s="85" t="inlineStr">
+      <c r="C8" s="83" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D8" s="85" t="inlineStr">
+      <c r="D8" s="83" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E8" s="85" t="inlineStr">
+      <c r="E8" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F8" s="85" t="inlineStr">
+      <c r="F8" s="83" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G8" s="85" t="inlineStr">
+      <c r="G8" s="83" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="H8" s="85" t="inlineStr">
+      <c r="H8" s="83" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="I8" s="85" t="n"/>
-      <c r="J8" s="85" t="inlineStr">
+      <c r="I8" s="83" t="n"/>
+      <c r="J8" s="83" t="inlineStr">
         <is>
           <t>11 de agosto de 2026 · Junio 2026</t>
         </is>
       </c>
-      <c r="K8" s="85" t="inlineStr">
+      <c r="K8" s="83" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="L8" s="85" t="inlineStr">
+      <c r="L8" s="83" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M8" s="85" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N8" s="85" t="inlineStr">
-        <is>
-          <t>Valor idéntico al de Consumo Privado (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
-        </is>
-      </c>
+      <c r="M8" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N8" s="83" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="84" t="inlineStr">
@@ -13790,76 +13839,72 @@
       <c r="N11" s="84" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="85" t="inlineStr">
+      <c r="A12" s="83" t="inlineStr">
         <is>
           <t>Indicador mensual del consumo privado</t>
         </is>
       </c>
-      <c r="B12" s="85" t="inlineStr">
+      <c r="B12" s="83" t="inlineStr">
         <is>
           <t>principal</t>
         </is>
       </c>
-      <c r="C12" s="85" t="inlineStr">
+      <c r="C12" s="83" t="inlineStr">
         <is>
           <t>actualizado automáticamente</t>
         </is>
       </c>
-      <c r="D12" s="85" t="inlineStr">
+      <c r="D12" s="83" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="E12" s="85" t="inlineStr">
+      <c r="E12" s="83" t="inlineStr">
         <is>
           <t>INEGI</t>
         </is>
       </c>
-      <c r="F12" s="85" t="inlineStr">
+      <c r="F12" s="83" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="G12" s="85" t="inlineStr">
+      <c r="G12" s="83" t="inlineStr">
         <is>
           <t>Abr 26</t>
         </is>
       </c>
-      <c r="H12" s="85" t="inlineStr">
+      <c r="H12" s="83" t="inlineStr">
         <is>
           <t>Abr 26</t>
         </is>
       </c>
-      <c r="I12" s="85" t="inlineStr">
+      <c r="I12" s="83" t="inlineStr">
         <is>
           <t>Aproximadamente 21 días después de haber concluido el mes</t>
         </is>
       </c>
-      <c r="J12" s="85" t="inlineStr">
+      <c r="J12" s="83" t="inlineStr">
         <is>
           <t>05 de agosto de 2026 · Mayo 2026</t>
         </is>
       </c>
-      <c r="K12" s="85" t="inlineStr">
+      <c r="K12" s="83" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="L12" s="85" t="inlineStr">
+      <c r="L12" s="83" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="M12" s="85" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="N12" s="85" t="inlineStr">
-        <is>
-          <t>Valor idéntico al de IMAI (104.4568568234) en el mismo mes: duplicado sospechoso entre series no relacionadas. Pendiente de verificación contra INEGI (BIE) una vez cargado INEGI_TOKEN.</t>
-        </is>
-      </c>
+      <c r="M12" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N12" s="83" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="84" t="inlineStr">
@@ -14338,7 +14383,7 @@
       <c r="N19" s="84" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="86" t="inlineStr">
+      <c r="A22" s="85" t="inlineStr">
         <is>
           <t>Advertencias del pipeline:</t>
         </is>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/08/2026 20:06 UTC</t>
+          <t>Generado: 04/08/2026 20:08 UTC</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-04T20:06:32+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-04T20:08:37+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -825,14 +825,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -875,16 +875,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -926,10 +926,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -952,18 +952,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -993,7 +993,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1180,7 +1180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1191,7 +1191,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1228,23 +1228,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1442,8 +1442,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1455,9 +1455,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1493,7 +1493,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1507,7 +1507,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1522,9 +1522,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1547,16 +1547,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1581,16 +1581,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1643,16 +1643,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1681,16 +1681,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1715,10 +1715,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1733,14 +1733,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1763,16 +1763,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1813,7 +1813,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1825,10 +1825,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1840,10 +1840,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1854,11 +1854,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1897,18 +1897,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2040,7 +2040,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2052,10 +2052,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2074,18 +2074,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2217,7 +2217,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2229,10 +2229,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2264,18 +2264,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2311,18 +2311,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2454,7 +2454,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2466,10 +2466,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2489,18 +2489,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2643,8 +2643,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2656,9 +2656,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2696,7 +2696,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2713,16 +2713,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2751,16 +2751,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2785,10 +2785,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2803,14 +2803,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2838,16 +2838,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2889,10 +2889,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3009,10 +3009,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3129,10 +3129,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3140,18 +3140,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3305,7 +3305,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3317,10 +3317,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3330,18 +3330,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3465,8 +3465,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3478,9 +3478,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3517,7 +3517,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3532,9 +3532,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3557,16 +3557,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3592,16 +3592,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3654,16 +3654,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3692,16 +3692,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3726,10 +3726,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3744,14 +3744,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3774,16 +3774,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3824,7 +3824,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3836,10 +3836,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3864,18 +3864,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3900,18 +3900,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3942,7 +3942,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4059,7 +4059,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4070,7 +4070,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4087,18 +4087,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4233,7 +4233,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4245,10 +4245,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4274,18 +4274,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4430,8 +4430,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4443,9 +4443,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4482,7 +4482,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4499,16 +4499,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4537,16 +4537,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4571,10 +4571,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4589,14 +4589,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4627,16 +4627,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4678,10 +4678,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4692,10 +4692,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4705,16 +4705,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4749,16 +4749,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4788,7 +4788,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4920,7 +4920,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4932,10 +4932,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4947,16 +4947,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4997,10 +4997,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5011,11 +5011,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5043,16 +5043,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5078,16 +5078,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5232,8 +5232,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5245,9 +5245,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5283,7 +5283,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5298,9 +5298,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5323,16 +5323,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5358,16 +5358,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5420,16 +5420,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5458,16 +5458,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5492,10 +5492,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5510,14 +5510,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5549,16 +5549,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5600,10 +5600,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5810,7 +5810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5821,7 +5821,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5888,18 +5888,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6080,8 +6080,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6093,9 +6093,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6131,7 +6131,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6148,16 +6148,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6210,16 +6210,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6249,16 +6249,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6283,10 +6283,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6301,14 +6301,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6332,16 +6332,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6383,10 +6383,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6396,18 +6396,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6435,18 +6435,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6474,18 +6474,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6513,18 +6513,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6552,18 +6552,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6589,18 +6589,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6631,7 +6631,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6825,10 +6825,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7027,8 +7027,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7040,9 +7040,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7078,7 +7078,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7093,9 +7093,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7124,16 +7124,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7159,16 +7159,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7198,16 +7198,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7232,10 +7232,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7250,14 +7250,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7280,16 +7280,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7330,7 +7330,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
+            <a:pattFill prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7338,7 +7338,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7347,16 +7347,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7503,7 +7503,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7515,10 +7515,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7578,16 +7578,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7765,16 +7765,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7803,16 +7803,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7837,10 +7837,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7855,14 +7855,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7890,16 +7890,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7941,10 +7941,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8109,10 +8109,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8277,10 +8277,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8461,7 +8461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8473,10 +8473,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8489,18 +8489,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8699,8 +8699,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8712,9 +8712,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8750,7 +8750,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8767,16 +8767,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8805,16 +8805,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8839,10 +8839,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8857,14 +8857,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8887,16 +8887,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8937,7 +8937,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8949,10 +8949,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9004,16 +9004,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9052,16 +9052,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9212,7 +9212,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9223,7 +9223,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9250,16 +9250,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9403,8 +9403,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9416,9 +9416,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9455,7 +9455,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9471,16 +9471,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9535,16 +9535,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9573,16 +9573,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9607,10 +9607,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9625,7 +9625,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9645,9 +9645,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9657,7 +9657,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9677,9 +9677,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9689,7 +9689,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9709,9 +9709,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9721,7 +9721,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9741,9 +9741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9753,7 +9753,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9773,9 +9773,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9785,7 +9785,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9805,9 +9805,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9817,7 +9817,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9837,9 +9837,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9849,7 +9849,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9869,9 +9869,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9901,9 +9901,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9913,7 +9913,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9933,9 +9933,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 04/08/2026 20:08 UTC</t>
+          <t>Generado: 05/08/2026 00:22 UTC</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-04T20:08:37+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-05T00:22:30+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13423,12 +13423,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13559,12 +13559,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13623,12 +13623,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13691,12 +13691,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13759,12 +13759,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13823,12 +13823,12 @@
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -13886,7 +13886,7 @@
       </c>
       <c r="J12" s="83" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026 · Mayo 2026</t>
+          <t>04 de septiembre de 2026 · Junio 2026</t>
         </is>
       </c>
       <c r="K12" s="83" t="inlineStr">
@@ -13954,7 +13954,7 @@
       </c>
       <c r="J13" s="84" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026 · Mayo 2026</t>
+          <t>04 de septiembre de 2026 · Junio 2026</t>
         </is>
       </c>
       <c r="K13" s="84" t="inlineStr">
@@ -14095,12 +14095,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14231,12 +14231,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14299,12 +14299,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14367,12 +14367,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -825,14 +825,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -875,16 +875,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -926,10 +926,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -952,18 +952,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -993,7 +993,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1180,7 +1180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1191,7 +1191,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1228,23 +1228,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1442,8 +1442,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1455,9 +1455,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1493,7 +1493,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1507,7 +1507,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1522,9 +1522,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1547,16 +1547,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1581,16 +1581,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1643,16 +1643,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1681,16 +1681,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1715,10 +1715,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1733,14 +1733,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1763,16 +1763,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1813,7 +1813,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1825,10 +1825,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1840,10 +1840,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1854,11 +1854,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1897,18 +1897,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2040,7 +2040,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2052,10 +2052,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2074,18 +2074,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2217,7 +2217,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2229,10 +2229,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2264,18 +2264,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2311,18 +2311,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2454,7 +2454,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2466,10 +2466,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2489,18 +2489,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2643,8 +2643,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2656,9 +2656,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2696,7 +2696,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2713,16 +2713,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2751,16 +2751,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2785,10 +2785,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2803,14 +2803,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2838,16 +2838,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2889,10 +2889,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3009,10 +3009,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3129,10 +3129,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3140,18 +3140,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3305,7 +3305,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3317,10 +3317,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3330,18 +3330,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3465,8 +3465,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3478,9 +3478,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3517,7 +3517,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3532,9 +3532,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3557,16 +3557,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3592,16 +3592,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3654,16 +3654,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3692,16 +3692,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3726,10 +3726,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3744,14 +3744,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3774,16 +3774,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3824,7 +3824,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3836,10 +3836,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="19050">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3864,18 +3864,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3900,18 +3900,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3942,7 +3942,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4059,7 +4059,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4070,7 +4070,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4087,18 +4087,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4233,7 +4233,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4245,10 +4245,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4274,18 +4274,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4430,8 +4430,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4443,9 +4443,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4482,7 +4482,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4499,16 +4499,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4537,16 +4537,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4571,10 +4571,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4589,14 +4589,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4627,16 +4627,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4678,10 +4678,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4692,10 +4692,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4705,16 +4705,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4749,16 +4749,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4788,7 +4788,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4920,7 +4920,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4932,10 +4932,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4947,16 +4947,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4997,10 +4997,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5011,11 +5011,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5043,16 +5043,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5078,16 +5078,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5232,8 +5232,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5245,9 +5245,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5283,7 +5283,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5298,9 +5298,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5323,16 +5323,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5358,16 +5358,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5420,16 +5420,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5458,16 +5458,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5492,10 +5492,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5510,14 +5510,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5549,16 +5549,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5600,10 +5600,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5810,7 +5810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5821,7 +5821,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5888,18 +5888,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6080,8 +6080,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6093,9 +6093,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6131,7 +6131,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6148,16 +6148,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6210,16 +6210,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6249,16 +6249,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6283,10 +6283,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6301,14 +6301,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6332,16 +6332,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6383,10 +6383,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6396,18 +6396,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6435,18 +6435,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6474,18 +6474,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6513,18 +6513,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6552,18 +6552,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6589,18 +6589,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6631,7 +6631,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6825,10 +6825,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7027,8 +7027,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7040,9 +7040,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7078,7 +7078,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7093,9 +7093,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7124,16 +7124,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7159,16 +7159,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7198,16 +7198,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7232,10 +7232,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7250,14 +7250,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7280,16 +7280,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7330,7 +7330,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="pct20">
+            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7338,7 +7338,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln w="38100">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7347,16 +7347,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7503,7 +7503,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7515,10 +7515,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7578,16 +7578,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7765,16 +7765,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7803,16 +7803,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7837,10 +7837,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7855,14 +7855,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7890,16 +7890,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7941,10 +7941,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8109,10 +8109,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8277,10 +8277,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8461,7 +8461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8473,10 +8473,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8489,18 +8489,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8699,8 +8699,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8712,9 +8712,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8750,7 +8750,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8767,16 +8767,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8805,16 +8805,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8839,10 +8839,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8857,14 +8857,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8887,16 +8887,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8937,7 +8937,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8949,10 +8949,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9004,16 +9004,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9052,16 +9052,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9212,7 +9212,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9223,7 +9223,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9250,16 +9250,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9403,8 +9403,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9416,9 +9416,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9455,7 +9455,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9471,16 +9471,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9535,16 +9535,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9573,16 +9573,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9607,10 +9607,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9625,7 +9625,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9645,9 +9645,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9657,7 +9657,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9677,9 +9677,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9689,7 +9689,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9709,9 +9709,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9721,7 +9721,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9741,9 +9741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9753,7 +9753,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9773,9 +9773,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9785,7 +9785,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9805,9 +9805,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9817,7 +9817,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9837,9 +9837,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9849,7 +9849,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9869,9 +9869,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9901,9 +9901,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9913,7 +9913,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9933,9 +9933,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/08/2026 00:22 UTC</t>
+          <t>Generado: 05/08/2026 01:10 UTC</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10605,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" s="65" t="n">
-        <v>-1</v>
+        <v>1.7</v>
       </c>
       <c r="G14" s="65" t="inlineStr">
         <is>
@@ -11958,13 +11958,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11989,15 +11990,20 @@
       </c>
       <c r="B4" s="63" t="inlineStr">
         <is>
-          <t>Estimación puntual (%)</t>
+          <t>Estimación mensual (%)</t>
         </is>
       </c>
       <c r="C4" s="63" t="inlineStr">
         <is>
+          <t>Estimación anual (%)</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
           <t>Límite inferior (%)</t>
         </is>
       </c>
-      <c r="D4" s="63" t="inlineStr">
+      <c r="E4" s="63" t="inlineStr">
         <is>
           <t>Límite superior (%)</t>
         </is>
@@ -12012,10 +12018,11 @@
       <c r="B5" s="82" t="n">
         <v>0.2</v>
       </c>
-      <c r="C5" s="82" t="n">
+      <c r="C5" s="82" t="n"/>
+      <c r="D5" s="82" t="n">
         <v>-0.9</v>
       </c>
-      <c r="D5" s="82" t="n">
+      <c r="E5" s="82" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -12028,10 +12035,11 @@
       <c r="B6" s="82" t="n">
         <v>-0.3</v>
       </c>
-      <c r="C6" s="82" t="n">
+      <c r="C6" s="82" t="n"/>
+      <c r="D6" s="82" t="n">
         <v>-1.2</v>
       </c>
-      <c r="D6" s="82" t="n">
+      <c r="E6" s="82" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -12045,10 +12053,13 @@
         <v>0.1</v>
       </c>
       <c r="C7" s="82" t="n">
-        <v>-1</v>
+        <v>1.8</v>
       </c>
       <c r="D7" s="82" t="n">
-        <v>1.2</v>
+        <v>-0.8</v>
+      </c>
+      <c r="E7" s="82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -12058,13 +12069,16 @@
         </is>
       </c>
       <c r="B8" s="82" t="n">
-        <v>1.1</v>
+        <v>0.2</v>
       </c>
       <c r="C8" s="82" t="n">
-        <v>0.1</v>
+        <v>-0.7</v>
       </c>
       <c r="D8" s="82" t="n">
-        <v>2.2</v>
+        <v>-1</v>
+      </c>
+      <c r="E8" s="82" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="9">
@@ -12074,13 +12088,16 @@
         </is>
       </c>
       <c r="B9" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="82" t="n">
         <v>-0.2</v>
       </c>
-      <c r="C9" s="82" t="n">
+      <c r="D9" s="82" t="n">
         <v>-1.2</v>
       </c>
-      <c r="D9" s="82" t="n">
-        <v>0.7</v>
+      <c r="E9" s="82" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="10">
@@ -12090,13 +12107,16 @@
         </is>
       </c>
       <c r="B10" s="82" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C10" s="82" t="n">
-        <v>-1.3</v>
+        <v>0.7</v>
       </c>
       <c r="D10" s="82" t="n">
-        <v>0.8</v>
+        <v>-1.4</v>
+      </c>
+      <c r="E10" s="82" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
@@ -12106,13 +12126,16 @@
         </is>
       </c>
       <c r="B11" s="82" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C11" s="82" t="n">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="D11" s="82" t="n">
-        <v>1.4</v>
+        <v>-1</v>
+      </c>
+      <c r="E11" s="82" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="12">
@@ -12125,10 +12148,13 @@
         <v>0.2</v>
       </c>
       <c r="C12" s="82" t="n">
-        <v>-0.8</v>
+        <v>1.3</v>
       </c>
       <c r="D12" s="82" t="n">
-        <v>1.1</v>
+        <v>-0.9</v>
+      </c>
+      <c r="E12" s="82" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="13">
@@ -12138,13 +12164,16 @@
         </is>
       </c>
       <c r="B13" s="82" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="C13" s="82" t="n">
-        <v>-1.6</v>
+        <v>0.1</v>
       </c>
       <c r="D13" s="82" t="n">
-        <v>0.6</v>
+        <v>-1</v>
+      </c>
+      <c r="E13" s="82" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="14">
@@ -12157,10 +12186,13 @@
         <v>0.1</v>
       </c>
       <c r="C14" s="82" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="D14" s="82" t="n">
-        <v>1.2</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E14" s="82" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="15">
@@ -12170,13 +12202,16 @@
         </is>
       </c>
       <c r="B15" s="82" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C15" s="82" t="n">
-        <v>-1.4</v>
+        <v>-0.6</v>
       </c>
       <c r="D15" s="82" t="n">
-        <v>0.5</v>
+        <v>-1</v>
+      </c>
+      <c r="E15" s="82" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="16">
@@ -12186,13 +12221,16 @@
         </is>
       </c>
       <c r="B16" s="82" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C16" s="82" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="D16" s="82" t="n">
-        <v>1.6</v>
+        <v>-0.9</v>
+      </c>
+      <c r="E16" s="82" t="n">
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
@@ -12202,13 +12240,16 @@
         </is>
       </c>
       <c r="B17" s="82" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C17" s="82" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="82" t="n">
-        <v>1.2</v>
+        <v>-1.3</v>
+      </c>
+      <c r="E17" s="82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -12221,10 +12262,13 @@
         <v>0.2</v>
       </c>
       <c r="C18" s="82" t="n">
-        <v>-0.7</v>
+        <v>2.3</v>
       </c>
       <c r="D18" s="82" t="n">
-        <v>1.2</v>
+        <v>-1</v>
+      </c>
+      <c r="E18" s="82" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
@@ -12234,13 +12278,16 @@
         </is>
       </c>
       <c r="B19" s="82" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="82" t="n">
-        <v>-1.3</v>
+        <v>2.3</v>
       </c>
       <c r="D19" s="82" t="n">
-        <v>0.9</v>
+        <v>-0.6</v>
+      </c>
+      <c r="E19" s="82" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -12250,13 +12297,16 @@
         </is>
       </c>
       <c r="B20" s="82" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="C20" s="82" t="n">
-        <v>-0.6</v>
+        <v>1.2</v>
       </c>
       <c r="D20" s="82" t="n">
-        <v>1.6</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E20" s="82" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="21">
@@ -12266,13 +12316,16 @@
         </is>
       </c>
       <c r="B21" s="82" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="82" t="n">
-        <v>-0.9</v>
+        <v>0.5</v>
       </c>
       <c r="D21" s="82" t="n">
-        <v>1</v>
+        <v>-1.2</v>
+      </c>
+      <c r="E21" s="82" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="22">
@@ -12282,13 +12335,16 @@
         </is>
       </c>
       <c r="B22" s="82" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="C22" s="82" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="82" t="n">
-        <v>2.1</v>
+        <v>-0.6</v>
+      </c>
+      <c r="E22" s="82" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="23">
@@ -12298,13 +12354,16 @@
         </is>
       </c>
       <c r="B23" s="82" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
       <c r="C23" s="82" t="n">
-        <v>-1.4</v>
+        <v>1.1</v>
       </c>
       <c r="D23" s="82" t="n">
-        <v>0.8</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E23" s="82" t="n">
+        <v>1.2</v>
       </c>
     </row>
     <row r="24">
@@ -12317,9 +12376,12 @@
         <v>0.2</v>
       </c>
       <c r="C24" s="82" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D24" s="82" t="n">
         <v>-1</v>
       </c>
-      <c r="D24" s="82" t="n">
+      <c r="E24" s="82" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -13294,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-05T00:22:30+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-05T01:10:35+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13423,12 +13485,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13491,12 +13553,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13559,12 +13621,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13623,12 +13685,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13691,12 +13753,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13759,12 +13821,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13823,12 +13885,12 @@
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -13886,7 +13948,7 @@
       </c>
       <c r="J12" s="83" t="inlineStr">
         <is>
-          <t>04 de septiembre de 2026 · Junio 2026</t>
+          <t>05 de agosto de 2026 · Mayo 2026</t>
         </is>
       </c>
       <c r="K12" s="83" t="inlineStr">
@@ -13954,7 +14016,7 @@
       </c>
       <c r="J13" s="84" t="inlineStr">
         <is>
-          <t>04 de septiembre de 2026 · Junio 2026</t>
+          <t>05 de agosto de 2026 · Mayo 2026</t>
         </is>
       </c>
       <c r="K13" s="84" t="inlineStr">
@@ -14095,12 +14157,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14231,12 +14293,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14299,12 +14361,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14367,12 +14429,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -825,14 +825,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -875,16 +875,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -926,10 +926,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -952,18 +952,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -993,7 +993,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1180,7 +1180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1191,7 +1191,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1228,23 +1228,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1442,8 +1442,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1455,9 +1455,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1493,7 +1493,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1507,7 +1507,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1522,9 +1522,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1547,16 +1547,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1581,16 +1581,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1643,16 +1643,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1681,16 +1681,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1715,10 +1715,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1733,14 +1733,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1763,16 +1763,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1813,7 +1813,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1825,10 +1825,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1840,10 +1840,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1854,11 +1854,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1897,18 +1897,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2040,7 +2040,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2052,10 +2052,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2074,18 +2074,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2217,7 +2217,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2229,10 +2229,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2264,18 +2264,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2311,18 +2311,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2454,7 +2454,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2466,10 +2466,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2489,18 +2489,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2643,8 +2643,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2656,9 +2656,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2696,7 +2696,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2713,16 +2713,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2751,16 +2751,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2785,10 +2785,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2803,14 +2803,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2838,16 +2838,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2889,10 +2889,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3009,10 +3009,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3129,10 +3129,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3140,18 +3140,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3305,7 +3305,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3317,10 +3317,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3330,18 +3330,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3465,8 +3465,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3478,9 +3478,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3517,7 +3517,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3532,9 +3532,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3557,16 +3557,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3592,16 +3592,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3654,16 +3654,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3692,16 +3692,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3726,10 +3726,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3744,14 +3744,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3774,16 +3774,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3824,7 +3824,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3836,10 +3836,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:ln w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3864,18 +3864,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3900,18 +3900,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3942,7 +3942,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4059,7 +4059,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4070,7 +4070,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4087,18 +4087,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4233,7 +4233,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4245,10 +4245,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4274,18 +4274,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4430,8 +4430,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4443,9 +4443,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4482,7 +4482,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4499,16 +4499,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4537,16 +4537,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4571,10 +4571,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4589,14 +4589,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4627,16 +4627,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4678,10 +4678,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4692,10 +4692,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4705,16 +4705,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4749,16 +4749,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4788,7 +4788,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4920,7 +4920,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4932,10 +4932,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4947,16 +4947,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4997,10 +4997,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:ln>
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5011,11 +5011,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5043,16 +5043,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5078,16 +5078,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5232,8 +5232,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5245,9 +5245,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5283,7 +5283,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5298,9 +5298,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5323,16 +5323,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5358,16 +5358,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5420,16 +5420,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5458,16 +5458,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5492,10 +5492,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5510,14 +5510,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5549,16 +5549,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5600,10 +5600,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5810,7 +5810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
+            <a:ln w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5821,7 +5821,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5888,18 +5888,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6080,8 +6080,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6093,9 +6093,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6131,7 +6131,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6148,16 +6148,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6210,16 +6210,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6249,16 +6249,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6283,10 +6283,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6301,14 +6301,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6332,16 +6332,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6383,10 +6383,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6396,18 +6396,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6435,18 +6435,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6474,18 +6474,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6513,18 +6513,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6552,18 +6552,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6589,18 +6589,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6631,7 +6631,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
+              <a:ln w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6825,10 +6825,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7027,8 +7027,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7040,9 +7040,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7078,7 +7078,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7093,9 +7093,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7124,16 +7124,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7159,16 +7159,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7198,16 +7198,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7232,10 +7232,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7250,14 +7250,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7280,16 +7280,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7330,7 +7330,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
+            <a:pattFill prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7338,7 +7338,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
+            <a:ln w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7347,16 +7347,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7503,7 +7503,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7515,10 +7515,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7578,16 +7578,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7765,16 +7765,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7803,16 +7803,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7837,10 +7837,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7855,14 +7855,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7890,16 +7890,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7941,10 +7941,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8109,10 +8109,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8277,10 +8277,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8461,7 +8461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8473,10 +8473,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8489,18 +8489,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8699,8 +8699,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8712,9 +8712,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8750,7 +8750,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8767,16 +8767,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8805,16 +8805,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8839,10 +8839,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8857,14 +8857,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8887,16 +8887,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8937,7 +8937,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8949,10 +8949,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:ln w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9004,16 +9004,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:ln>
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9052,16 +9052,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9212,7 +9212,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+            <a:ln w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9223,7 +9223,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:ln>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9250,16 +9250,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:noFill/>
+              <a:ln>
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9403,8 +9403,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9416,9 +9416,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9455,7 +9455,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9471,16 +9471,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9535,16 +9535,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:ln>
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9573,16 +9573,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:noFill/>
+        <a:ln>
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9607,10 +9607,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+    <a:solidFill>
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9625,7 +9625,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9645,9 +9645,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9657,7 +9657,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9677,9 +9677,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9689,7 +9689,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9709,9 +9709,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9721,7 +9721,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9741,9 +9741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9753,7 +9753,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9773,9 +9773,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9785,7 +9785,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9805,9 +9805,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9817,7 +9817,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9837,9 +9837,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9849,7 +9849,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9869,9 +9869,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9901,9 +9901,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9913,7 +9913,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9933,9 +9933,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/08/2026 01:10 UTC</t>
+          <t>Generado: 05/08/2026 01:19 UTC</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-05T01:10:35+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-05T01:19:21+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13621,12 +13621,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13685,12 +13685,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -13948,7 +13948,7 @@
       </c>
       <c r="J12" s="83" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026 · Mayo 2026</t>
+          <t>04 de septiembre de 2026 · Junio 2026</t>
         </is>
       </c>
       <c r="K12" s="83" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="J13" s="84" t="inlineStr">
         <is>
-          <t>05 de agosto de 2026 · Mayo 2026</t>
+          <t>04 de septiembre de 2026 · Junio 2026</t>
         </is>
       </c>
       <c r="K13" s="84" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/08/2026 01:19 UTC</t>
+          <t>Generado: 05/08/2026 15:08 UTC</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-05T01:19:21+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-05T15:08:07+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="PIB" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -825,14 +825,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -875,16 +875,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1800" b="1" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
               <a:solidFill>
@@ -926,10 +926,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -952,18 +952,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="800" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -993,7 +993,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -1180,7 +1180,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -1191,7 +1191,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -1228,23 +1228,23 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:sysClr val="windowText" lastClr="000000">
                   <a:lumOff val="85000"/>
                   <a:lumMod val="15000"/>
                 </a:sysClr>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -1442,8 +1442,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -1455,9 +1455,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" spc="0" normalizeH="0" baseline="0">
                 <a:solidFill>
@@ -1493,7 +1493,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -1507,7 +1507,7 @@
         </majorGridlines>
         <minorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="5000"/>
@@ -1522,9 +1522,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                     <a:solidFill>
@@ -1547,16 +1547,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" cap="all" baseline="0">
                   <a:solidFill>
@@ -1581,16 +1581,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1643,16 +1643,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -1681,16 +1681,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -1715,10 +1715,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -1733,14 +1733,14 @@
 </file>
 
 <file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -1763,16 +1763,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -1813,7 +1813,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -1825,10 +1825,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -1840,10 +1840,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -1854,11 +1854,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -1897,18 +1897,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2040,7 +2040,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -2052,10 +2052,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -2074,18 +2074,18 @@
               <idx val="10"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2217,7 +2217,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -2229,10 +2229,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -2264,18 +2264,18 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -2311,18 +2311,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2454,7 +2454,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -2466,10 +2466,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="0070C0"/>
                 </a:solidFill>
@@ -2489,18 +2489,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -2643,8 +2643,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -2656,9 +2656,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2696,7 +2696,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -2713,16 +2713,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -2751,16 +2751,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -2785,10 +2785,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -2803,14 +2803,14 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -2838,16 +2838,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -2889,10 +2889,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3009,10 +3009,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3129,10 +3129,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -3140,18 +3140,18 @@
           <invertIfNegative val="0"/>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3305,7 +3305,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -3317,10 +3317,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -3330,18 +3330,18 @@
           </marker>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3465,8 +3465,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -3478,9 +3478,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3517,7 +3517,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -3532,9 +3532,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3557,16 +3557,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -3592,16 +3592,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3654,16 +3654,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -3692,16 +3692,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -3726,10 +3726,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -3744,14 +3744,14 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -3774,16 +3774,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -3824,7 +3824,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -3836,10 +3836,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="19050">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -3864,18 +3864,18 @@
             <dLbl>
               <idx val="11"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -3900,18 +3900,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -3942,7 +3942,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4059,7 +4059,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4070,7 +4070,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -4087,18 +4087,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4233,7 +4233,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
@@ -4245,10 +4245,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="9C2348"/>
                 </a:solidFill>
@@ -4274,18 +4274,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4430,8 +4430,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -4443,9 +4443,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4482,7 +4482,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -4499,16 +4499,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -4537,16 +4537,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -4571,10 +4571,10 @@
     <dispBlanksAs val="zero"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -4589,14 +4589,14 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -4627,16 +4627,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -4678,10 +4678,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4692,10 +4692,10 @@
             <invertIfNegative val="0"/>
             <bubble3D val="0"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="9C2348"/>
               </a:solidFill>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4705,16 +4705,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4749,16 +4749,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -4788,7 +4788,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -4920,7 +4920,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -4932,10 +4932,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -4947,16 +4947,16 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -4997,10 +4997,10 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:solidFill>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:sysClr val="window" lastClr="FFFFFF"/>
                 </a:solidFill>
-                <a:ln>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:solidFill>
                     <a:sysClr val="windowText" lastClr="000000">
                       <a:lumOff val="75000"/>
@@ -5011,11 +5011,11 @@
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5043,16 +5043,16 @@
             <dLbl>
               <idx val="10"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -5078,16 +5078,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5232,8 +5232,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -5245,9 +5245,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5283,7 +5283,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -5298,9 +5298,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -5323,16 +5323,16 @@
           </tx>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -5358,16 +5358,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5420,16 +5420,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -5458,16 +5458,16 @@
       <legendPos val="b"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -5492,10 +5492,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -5510,14 +5510,14 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -5549,16 +5549,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -5600,10 +5600,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -5810,7 +5810,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="38100" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -5821,7 +5821,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -5888,18 +5888,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6080,8 +6080,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -6093,9 +6093,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6131,7 +6131,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -6148,16 +6148,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6210,16 +6210,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -6249,16 +6249,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -6283,10 +6283,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -6301,14 +6301,14 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -6332,16 +6332,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -6383,10 +6383,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -6396,18 +6396,18 @@
             <dLbl>
               <idx val="1"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6435,18 +6435,18 @@
             <dLbl>
               <idx val="2"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6474,18 +6474,18 @@
             <dLbl>
               <idx val="3"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6513,18 +6513,18 @@
             <dLbl>
               <idx val="7"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6552,18 +6552,18 @@
             <dLbl>
               <idx val="8"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                   <a:spAutoFit/>
                 </a:bodyPr>
-                <a:lstStyle/>
-                <a:p>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -6589,18 +6589,18 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -6631,7 +6631,7 @@
           </dLbls>
           <trendline>
             <spPr>
-              <a:ln w="19050" cap="rnd">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
                 <a:solidFill>
                   <a:schemeClr val="accent1"/>
                 </a:solidFill>
@@ -6825,10 +6825,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -7027,8 +7027,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -7040,9 +7040,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7078,7 +7078,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -7093,9 +7093,9 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7124,16 +7124,16 @@
           <layout/>
           <overlay val="0"/>
           <spPr>
-            <a:noFill/>
-            <a:ln>
+            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
+            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:pPr>
                 <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
@@ -7159,16 +7159,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7198,16 +7198,16 @@
       <layout/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7232,10 +7232,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7250,14 +7250,14 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7280,16 +7280,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7330,7 +7330,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:pattFill prst="pct20">
+            <a:pattFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="pct20">
               <a:fgClr>
                 <a:srgbClr val="1E5B4F"/>
               </a:fgClr>
@@ -7338,7 +7338,7 @@
                 <a:schemeClr val="bg1"/>
               </a:bgClr>
             </a:pattFill>
-            <a:ln w="38100">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -7347,16 +7347,16 @@
           </spPr>
           <dLbls>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7503,7 +7503,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -7515,10 +7515,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -7578,16 +7578,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -7765,16 +7765,16 @@
         <majorTickMark val="out"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -7803,16 +7803,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -7837,10 +7837,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -7855,14 +7855,14 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -7890,16 +7890,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -7941,10 +7941,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="002F2A"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8109,10 +8109,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="1E5B4F"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8277,10 +8277,10 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="9C2348"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:noFill/>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -8461,7 +8461,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
@@ -8473,10 +8473,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="A6802D"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="A6802D"/>
                 </a:solidFill>
@@ -8489,18 +8489,18 @@
               <idx val="18"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -8699,8 +8699,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -8712,9 +8712,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8750,7 +8750,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -8767,16 +8767,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="800" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -8805,16 +8805,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -8839,10 +8839,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -8857,14 +8857,14 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
@@ -8887,16 +8887,16 @@
       </tx>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
@@ -8937,7 +8937,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
@@ -8949,10 +8949,10 @@
             <symbol val="circle"/>
             <size val="5"/>
             <spPr>
-              <a:solidFill>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:srgbClr val="1E5B4F"/>
               </a:solidFill>
-              <a:ln w="9525">
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
                 <a:solidFill>
                   <a:srgbClr val="1E5B4F"/>
                 </a:solidFill>
@@ -9004,16 +9004,16 @@
             <dLbl>
               <idx val="9"/>
               <spPr>
-                <a:noFill/>
-                <a:ln>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:noFill/>
                   <a:prstDash val="solid"/>
                 </a:ln>
               </spPr>
               <txPr>
-                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-                <a:lstStyle/>
-                <a:p>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                   <a:pPr>
                     <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
@@ -9052,16 +9052,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9212,7 +9212,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln w="28575" cap="rnd">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
               <a:solidFill>
                 <a:srgbClr val="0070C0"/>
               </a:solidFill>
@@ -9223,7 +9223,7 @@
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
@@ -9250,16 +9250,16 @@
               <showBubbleSize val="0"/>
             </dLbl>
             <spPr>
-              <a:noFill/>
-              <a:ln>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:noFill/>
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
             <txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
@@ -9403,8 +9403,8 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
               <a:schemeClr val="tx1">
                 <a:lumMod val="15000"/>
@@ -9416,9 +9416,9 @@
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9455,7 +9455,7 @@
         <axPos val="l"/>
         <majorGridlines>
           <spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="15000"/>
@@ -9471,16 +9471,16 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9535,16 +9535,16 @@
         <minorTickMark val="none"/>
         <tickLblPos val="nextTo"/>
         <spPr>
-          <a:noFill/>
-          <a:ln>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:noFill/>
             <a:prstDash val="solid"/>
           </a:ln>
         </spPr>
         <txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
@@ -9573,16 +9573,16 @@
       <legendPos val="t"/>
       <overlay val="0"/>
       <spPr>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
       <txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
@@ -9607,10 +9607,10 @@
     <dispBlanksAs val="gap"/>
   </chart>
   <spPr>
-    <a:solidFill>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
       <a:schemeClr val="bg1"/>
     </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
         <a:schemeClr val="tx1">
           <a:lumMod val="15000"/>
@@ -9625,7 +9625,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9645,9 +9645,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9657,7 +9657,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9677,9 +9677,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9689,7 +9689,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9709,9 +9709,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9721,7 +9721,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>6</col>
@@ -9741,9 +9741,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9753,7 +9753,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9773,9 +9773,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9785,7 +9785,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>4</col>
@@ -9805,9 +9805,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9817,7 +9817,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9837,9 +9837,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9849,7 +9849,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9869,9 +9869,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9881,7 +9881,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>7</col>
@@ -9901,9 +9901,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -9913,7 +9913,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
       <col>5</col>
@@ -9933,9 +9933,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 10/08/2026 14:13 UTC</t>
+          <t>Generado: 05/08/2026 17:00 UTC</t>
         </is>
       </c>
     </row>
@@ -10499,14 +10499,14 @@
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="E11" s="64" t="n">
-        <v>3.11763</v>
+        <v>3.365977</v>
       </c>
       <c r="F11" s="64" t="n">
-        <v>3.948334</v>
+        <v>4.03192</v>
       </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="E17" s="64" t="n">
-        <v>17.1387</v>
+        <v>17.2717</v>
       </c>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="inlineStr">
@@ -11619,7 +11619,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: actualizado automáticamente</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: REZAGADO</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: actualizado automáticamente</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Variación mensual estimada (%) · Estado: ACTUALIZADO</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12414,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: actualizado automáticamente</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: ACTUALIZADO</t>
         </is>
       </c>
     </row>
@@ -13327,7 +13327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13356,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-10T14:13:35+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-05T17:00:42+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13445,7 +13445,7 @@
       </c>
       <c r="C5" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>REZAGADO</t>
         </is>
       </c>
       <c r="D5" s="84" t="inlineStr">
@@ -13475,7 +13475,7 @@
       </c>
       <c r="I5" s="84" t="inlineStr">
         <is>
-          <t>Aproximadamente 50 días después de haber concluido el trimestre</t>
+          <t>30 de julio de 2026</t>
         </is>
       </c>
       <c r="J5" s="84" t="inlineStr">
@@ -13485,12 +13485,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13513,7 +13513,7 @@
       </c>
       <c r="C6" s="83" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>PUBLICACIÓN PENDIENTE</t>
         </is>
       </c>
       <c r="D6" s="83" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13581,7 +13581,7 @@
       </c>
       <c r="C7" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D7" s="84" t="inlineStr">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="I7" s="84" t="inlineStr">
         <is>
-          <t>Aproximadamente 55 días después de haber concluido el mes</t>
+          <t>23 de julio de 2026</t>
         </is>
       </c>
       <c r="J7" s="84" t="inlineStr">
@@ -13621,12 +13621,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13649,7 +13649,7 @@
       </c>
       <c r="C8" s="83" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D8" s="83" t="inlineStr">
@@ -13677,7 +13677,11 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="I8" s="83" t="n"/>
+      <c r="I8" s="83" t="inlineStr">
+        <is>
+          <t>10 de julio de 2026</t>
+        </is>
+      </c>
       <c r="J8" s="83" t="inlineStr">
         <is>
           <t>11 de agosto de 2026 · Junio 2026</t>
@@ -13685,12 +13689,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13713,7 +13717,7 @@
       </c>
       <c r="C9" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D9" s="84" t="inlineStr">
@@ -13743,7 +13747,7 @@
       </c>
       <c r="I9" s="84" t="inlineStr">
         <is>
-          <t>Aproximadamente 30 a 45 días posteriores al cierre del mes</t>
+          <t>27 de julio de 2026</t>
         </is>
       </c>
       <c r="J9" s="84" t="inlineStr">
@@ -13753,12 +13757,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13781,7 +13785,7 @@
       </c>
       <c r="C10" s="83" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D10" s="83" t="inlineStr">
@@ -13811,7 +13815,7 @@
       </c>
       <c r="I10" s="83" t="inlineStr">
         <is>
-          <t>Aproximadamente 25-30 días después de haber concluido el mes</t>
+          <t>24 de julio de 2026</t>
         </is>
       </c>
       <c r="J10" s="83" t="inlineStr">
@@ -13821,12 +13825,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13849,7 +13853,7 @@
       </c>
       <c r="C11" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D11" s="84" t="inlineStr">
@@ -13869,28 +13873,32 @@
       </c>
       <c r="G11" s="84" t="inlineStr">
         <is>
-          <t>Jul 26</t>
+          <t>Jun 26</t>
         </is>
       </c>
       <c r="H11" s="84" t="inlineStr">
         <is>
-          <t>Jul 26</t>
-        </is>
-      </c>
-      <c r="I11" s="84" t="n"/>
+          <t>Jun 26</t>
+        </is>
+      </c>
+      <c r="I11" s="84" t="inlineStr">
+        <is>
+          <t>09 de julio de 2026</t>
+        </is>
+      </c>
       <c r="J11" s="84" t="inlineStr">
         <is>
-          <t>09 de septiembre de 2026 · Agosto 2026</t>
+          <t>07 de agosto de 2026 · Julio 2026</t>
         </is>
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -13913,7 +13921,7 @@
       </c>
       <c r="C12" s="83" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>REZAGADO</t>
         </is>
       </c>
       <c r="D12" s="83" t="inlineStr">
@@ -13943,7 +13951,7 @@
       </c>
       <c r="I12" s="83" t="inlineStr">
         <is>
-          <t>Aproximadamente 21 días después de haber concluido el mes</t>
+          <t>05 de agosto de 2026</t>
         </is>
       </c>
       <c r="J12" s="83" t="inlineStr">
@@ -13981,7 +13989,7 @@
       </c>
       <c r="C13" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>REZAGADO</t>
         </is>
       </c>
       <c r="D13" s="84" t="inlineStr">
@@ -14011,7 +14019,7 @@
       </c>
       <c r="I13" s="84" t="inlineStr">
         <is>
-          <t>Aproximadamente 55 días tras el cierre del mes</t>
+          <t>05 de agosto de 2026</t>
         </is>
       </c>
       <c r="J13" s="84" t="inlineStr">
@@ -14049,7 +14057,7 @@
       </c>
       <c r="C14" s="83" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D14" s="83" t="inlineStr">
@@ -14079,7 +14087,7 @@
       </c>
       <c r="I14" s="83" t="inlineStr">
         <is>
-          <t>Fin de mes del periodo estimado</t>
+          <t>21 de julio de 2026</t>
         </is>
       </c>
       <c r="J14" s="83" t="inlineStr">
@@ -14117,7 +14125,7 @@
       </c>
       <c r="C15" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D15" s="84" t="inlineStr">
@@ -14147,7 +14155,7 @@
       </c>
       <c r="I15" s="84" t="inlineStr">
         <is>
-          <t>Aproximadamente 40 días tras el cierre del mes</t>
+          <t>16 de julio de 2026</t>
         </is>
       </c>
       <c r="J15" s="84" t="inlineStr">
@@ -14157,12 +14165,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14185,7 +14193,7 @@
       </c>
       <c r="C16" s="83" t="inlineStr">
         <is>
-          <t>dato de respaldo vigente</t>
+          <t>PUBLICACIÓN PENDIENTE</t>
         </is>
       </c>
       <c r="D16" s="83" t="inlineStr">
@@ -14253,7 +14261,7 @@
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>PUBLICACIÓN PENDIENTE</t>
         </is>
       </c>
       <c r="D17" s="84" t="inlineStr">
@@ -14293,12 +14301,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14321,7 +14329,7 @@
       </c>
       <c r="C18" s="83" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>PUBLICACIÓN PENDIENTE</t>
         </is>
       </c>
       <c r="D18" s="83" t="inlineStr">
@@ -14361,12 +14369,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14389,7 +14397,7 @@
       </c>
       <c r="C19" s="84" t="inlineStr">
         <is>
-          <t>actualizado automáticamente</t>
+          <t>PUBLICACIÓN PENDIENTE</t>
         </is>
       </c>
       <c r="D19" s="84" t="inlineStr">
@@ -14429,12 +14437,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">
@@ -14448,6 +14456,27 @@
       <c r="A22" s="85" t="inlineStr">
         <is>
           <t>Advertencias del pipeline:</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="62" t="inlineStr">
+        <is>
+          <t>• PIB: REZAGADO – El calendario indica que ya se publicó 2° trimestre 2026, pero el dashboard aún muestra 1T-26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="62" t="inlineStr">
+        <is>
+          <t>• CONSUMO: REZAGADO – El calendario indica que ya se publicó Mayo 2026, pero el dashboard aún muestra Abr 26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>• IMFBCF: REZAGADO – El calendario indica que ya se publicó Mayo 2026, pero el dashboard aún muestra Abr 26.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/08/2026 17:00 UTC</t>
+          <t>Generado: 05/08/2026 17:06 UTC</t>
         </is>
       </c>
     </row>
@@ -10308,11 +10308,15 @@
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="E5" s="64" t="n">
-        <v>24973976.071</v>
-      </c>
-      <c r="F5" s="64" t="n">
-        <v>0.002423</v>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>24.97 billones de pesos de 2018</t>
+        </is>
+      </c>
+      <c r="F5" s="64" t="inlineStr">
+        <is>
+          <t>+0.4%</t>
+        </is>
       </c>
       <c r="G5" s="64" t="inlineStr">
         <is>
@@ -10341,11 +10345,15 @@
           <t>1T-26 P</t>
         </is>
       </c>
-      <c r="E6" s="65" t="n">
-        <v>797675.498</v>
-      </c>
-      <c r="F6" s="65" t="n">
-        <v>7621773.386</v>
+      <c r="E6" s="65" t="inlineStr">
+        <is>
+          <t>23,553,779</t>
+        </is>
+      </c>
+      <c r="F6" s="65" t="inlineStr">
+        <is>
+          <t>-0.4%</t>
+        </is>
       </c>
       <c r="G6" s="65" t="inlineStr">
         <is>
@@ -10374,10 +10382,16 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="E7" s="64" t="n">
-        <v>108.595752</v>
-      </c>
-      <c r="F7" s="64" t="n"/>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>108.6</t>
+        </is>
+      </c>
+      <c r="F7" s="64" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="G7" s="64" t="inlineStr">
         <is>
           <t>Índice base 2018=100</t>
@@ -10405,11 +10419,15 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="E8" s="65" t="n">
-        <v>101.629971</v>
-      </c>
-      <c r="F8" s="65" t="n">
-        <v>-0.007713</v>
+      <c r="E8" s="65" t="inlineStr">
+        <is>
+          <t>101.6</t>
+        </is>
+      </c>
+      <c r="F8" s="65" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
       </c>
       <c r="G8" s="65" t="inlineStr">
         <is>
@@ -10438,11 +10456,15 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="E9" s="64" t="n">
-        <v>72551.015</v>
-      </c>
-      <c r="F9" s="64" t="n">
-        <v>68461.11900000001</v>
+      <c r="E9" s="64" t="inlineStr">
+        <is>
+          <t>4,090</t>
+        </is>
+      </c>
+      <c r="F9" s="64" t="inlineStr">
+        <is>
+          <t>+1,831 mdd</t>
+        </is>
       </c>
       <c r="G9" s="64" t="inlineStr">
         <is>
@@ -10471,10 +10493,16 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="E10" s="65" t="n">
-        <v>0.028985</v>
-      </c>
-      <c r="F10" s="65" t="n"/>
+      <c r="E10" s="65" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="F10" s="65" t="inlineStr">
+        <is>
+          <t>+0.1 pp</t>
+        </is>
+      </c>
       <c r="G10" s="65" t="inlineStr">
         <is>
           <t>Porcentaje de la PEA</t>
@@ -10502,11 +10530,15 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="E11" s="64" t="n">
-        <v>3.365977</v>
-      </c>
-      <c r="F11" s="64" t="n">
-        <v>4.03192</v>
+      <c r="E11" s="64" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="64" t="inlineStr">
+        <is>
+          <t>-0.6 puntos porcentuales</t>
+        </is>
       </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
@@ -10535,11 +10567,15 @@
           <t>Abr 26</t>
         </is>
       </c>
-      <c r="E12" s="65" t="n">
-        <v>113.7</v>
-      </c>
-      <c r="F12" s="65" t="n">
-        <v>0.001</v>
+      <c r="E12" s="65" t="inlineStr">
+        <is>
+          <t>113.7</t>
+        </is>
+      </c>
+      <c r="F12" s="65" t="inlineStr">
+        <is>
+          <t>+0.1%</t>
+        </is>
       </c>
       <c r="G12" s="65" t="inlineStr">
         <is>
@@ -10568,11 +10604,15 @@
           <t>Abr 26</t>
         </is>
       </c>
-      <c r="E13" s="64" t="n">
-        <v>107.4</v>
-      </c>
-      <c r="F13" s="64" t="n">
-        <v>0.04</v>
+      <c r="E13" s="64" t="inlineStr">
+        <is>
+          <t>107.4</t>
+        </is>
+      </c>
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>+4.0%</t>
+        </is>
       </c>
       <c r="G13" s="64" t="inlineStr">
         <is>
@@ -10601,11 +10641,15 @@
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="E14" s="65" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F14" s="65" t="n">
-        <v>1.7</v>
+      <c r="E14" s="65" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="F14" s="65" t="inlineStr">
+        <is>
+          <t>+0.2%</t>
+        </is>
       </c>
       <c r="G14" s="65" t="inlineStr">
         <is>
@@ -10634,11 +10678,15 @@
           <t>May 26</t>
         </is>
       </c>
-      <c r="E15" s="64" t="n">
-        <v>110.4</v>
-      </c>
-      <c r="F15" s="64" t="n">
-        <v>-0.006</v>
+      <c r="E15" s="64" t="inlineStr">
+        <is>
+          <t>110.4</t>
+        </is>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
       </c>
       <c r="G15" s="64" t="inlineStr">
         <is>
@@ -10667,11 +10715,15 @@
           <t>1T-26</t>
         </is>
       </c>
-      <c r="E16" s="65" t="n">
-        <v>23590.62204554513</v>
-      </c>
-      <c r="F16" s="65" t="n">
-        <v>1705.227100742525</v>
+      <c r="E16" s="65" t="inlineStr">
+        <is>
+          <t>23,591</t>
+        </is>
+      </c>
+      <c r="F16" s="65" t="inlineStr">
+        <is>
+          <t>+10.4%</t>
+        </is>
       </c>
       <c r="G16" s="65" t="inlineStr">
         <is>
@@ -10700,10 +10752,16 @@
           <t>Ago 26</t>
         </is>
       </c>
-      <c r="E17" s="64" t="n">
-        <v>17.2717</v>
-      </c>
-      <c r="F17" s="64" t="n"/>
+      <c r="E17" s="64" t="inlineStr">
+        <is>
+          <t>$17.27</t>
+        </is>
+      </c>
+      <c r="F17" s="64" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="G17" s="64" t="inlineStr">
         <is>
           <t>Pesos por dólar</t>
@@ -10731,10 +10789,16 @@
           <t>Ago 26</t>
         </is>
       </c>
-      <c r="E18" s="65" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F18" s="65" t="n"/>
+      <c r="E18" s="65" t="inlineStr">
+        <is>
+          <t>6.5%</t>
+        </is>
+      </c>
+      <c r="F18" s="65" t="inlineStr">
+        <is>
+          <t>+0.0 pp</t>
+        </is>
+      </c>
       <c r="G18" s="65" t="inlineStr">
         <is>
           <t>Porcentaje anual</t>
@@ -10762,10 +10826,16 @@
           <t>Jul 26</t>
         </is>
       </c>
-      <c r="E19" s="64" t="n">
-        <v>255498.1</v>
-      </c>
-      <c r="F19" s="64" t="n"/>
+      <c r="E19" s="64" t="inlineStr">
+        <is>
+          <t>255,498</t>
+        </is>
+      </c>
+      <c r="F19" s="64" t="inlineStr">
+        <is>
+          <t>+317 mdd</t>
+        </is>
+      </c>
       <c r="G19" s="64" t="inlineStr">
         <is>
           <t>Millones de dólares</t>
@@ -13356,7 +13426,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-05T17:00:42+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-05T17:06:20+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/08/2026 17:06 UTC</t>
+          <t>Generado: 10/08/2026 17:10 UTC</t>
         </is>
       </c>
     </row>
@@ -10527,17 +10527,17 @@
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="E11" s="64" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F11" s="64" t="inlineStr">
         <is>
-          <t>-0.6 puntos porcentuales</t>
+          <t>-0.2 puntos porcentuales</t>
         </is>
       </c>
       <c r="G11" s="64" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="D12" s="65" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="E12" s="65" t="inlineStr">
         <is>
-          <t>113.7</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="F12" s="65" t="inlineStr">
@@ -10601,17 +10601,17 @@
       </c>
       <c r="D13" s="64" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="E13" s="64" t="inlineStr">
         <is>
-          <t>107.4</t>
+          <t>107.1</t>
         </is>
       </c>
       <c r="F13" s="64" t="inlineStr">
         <is>
-          <t>+4.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="G13" s="64" t="inlineStr">
@@ -10754,12 +10754,12 @@
       </c>
       <c r="E17" s="64" t="inlineStr">
         <is>
-          <t>$17.27</t>
+          <t>$17.14</t>
         </is>
       </c>
       <c r="F17" s="64" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="G17" s="64" t="inlineStr">
@@ -11670,7 +11670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11689,7 +11689,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: REZAGADO</t>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Índice base 2018=100 · Estado: ACTUALIZADO</t>
         </is>
       </c>
     </row>
@@ -12015,6 +12015,22 @@
       </c>
       <c r="D23" s="82" t="n">
         <v>0.051</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="C24" s="82" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="D24" s="82" t="n">
+        <v>0.024</v>
       </c>
     </row>
   </sheetData>
@@ -13092,7 +13108,7 @@
       </c>
       <c r="H11" s="84" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/imcp/imcpmi2026_08.pdf</t>
         </is>
       </c>
     </row>
@@ -13134,7 +13150,7 @@
       </c>
       <c r="H12" s="83" t="inlineStr">
         <is>
-          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_07.pdf</t>
+          <t>https://www.inegi.org.mx/contenidos/saladeprensa/boletines/2026/ifb/imfbcf2026_08.pdf</t>
         </is>
       </c>
     </row>
@@ -13397,7 +13413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13426,7 +13442,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-05T17:06:20+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-10T17:10:14+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13555,12 +13571,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13623,12 +13639,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13691,12 +13707,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13759,12 +13775,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13827,12 +13843,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13895,12 +13911,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13943,32 +13959,32 @@
       </c>
       <c r="G11" s="84" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="H11" s="84" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="I11" s="84" t="inlineStr">
         <is>
-          <t>09 de julio de 2026</t>
+          <t>07 de agosto de 2026</t>
         </is>
       </c>
       <c r="J11" s="84" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026 · Julio 2026</t>
+          <t>09 de septiembre de 2026 · Agosto 2026</t>
         </is>
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -13991,7 +14007,7 @@
       </c>
       <c r="C12" s="83" t="inlineStr">
         <is>
-          <t>REZAGADO</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D12" s="83" t="inlineStr">
@@ -14011,12 +14027,12 @@
       </c>
       <c r="G12" s="83" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="H12" s="83" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="I12" s="83" t="inlineStr">
@@ -14031,12 +14047,12 @@
       </c>
       <c r="K12" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L12" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M12" s="83" t="inlineStr">
@@ -14059,7 +14075,7 @@
       </c>
       <c r="C13" s="84" t="inlineStr">
         <is>
-          <t>REZAGADO</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D13" s="84" t="inlineStr">
@@ -14079,12 +14095,12 @@
       </c>
       <c r="G13" s="84" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="H13" s="84" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>May 26</t>
         </is>
       </c>
       <c r="I13" s="84" t="inlineStr">
@@ -14099,12 +14115,12 @@
       </c>
       <c r="K13" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L13" s="84" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M13" s="84" t="inlineStr">
@@ -14167,12 +14183,12 @@
       </c>
       <c r="K14" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L14" s="83" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M14" s="83" t="inlineStr">
@@ -14235,12 +14251,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14371,12 +14387,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14439,12 +14455,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14507,12 +14523,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">
@@ -14533,20 +14549,6 @@
       <c r="A23" s="62" t="inlineStr">
         <is>
           <t>• PIB: REZAGADO – El calendario indica que ya se publicó 2° trimestre 2026, pero el dashboard aún muestra 1T-26.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="62" t="inlineStr">
-        <is>
-          <t>• CONSUMO: REZAGADO – El calendario indica que ya se publicó Mayo 2026, pero el dashboard aún muestra Abr 26.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="62" t="inlineStr">
-        <is>
-          <t>• IMFBCF: REZAGADO – El calendario indica que ya se publicó Mayo 2026, pero el dashboard aún muestra Abr 26.</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 05/08/2026 15:08 UTC</t>
+          <t>Generado: 06/08/2026 15:07 UTC</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="E17" s="64" t="n">
-        <v>17.2717</v>
+        <v>17.2317</v>
       </c>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="inlineStr">
@@ -13356,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-05T15:08:07+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-06T15:07:06+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13621,12 +13621,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13685,12 +13685,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 06/08/2026 15:07 UTC</t>
+          <t>Generado: 07/08/2026 14:06 UTC</t>
         </is>
       </c>
     </row>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="E17" s="64" t="n">
-        <v>17.2317</v>
+        <v>17.2195</v>
       </c>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="inlineStr">
@@ -13356,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-06T15:07:06+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-07T14:06:58+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13621,12 +13621,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13685,12 +13685,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13880,17 +13880,17 @@
       <c r="I11" s="84" t="n"/>
       <c r="J11" s="84" t="inlineStr">
         <is>
-          <t>07 de agosto de 2026 · Julio 2026</t>
+          <t>09 de septiembre de 2026 · Agosto 2026</t>
         </is>
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 07/08/2026 14:06 UTC</t>
+          <t>Generado: 10/08/2026 14:13 UTC</t>
         </is>
       </c>
     </row>
@@ -10499,14 +10499,14 @@
       </c>
       <c r="D11" s="64" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="E11" s="64" t="n">
-        <v>3.365977</v>
+        <v>3.11763</v>
       </c>
       <c r="F11" s="64" t="n">
-        <v>4.03192</v>
+        <v>3.948334</v>
       </c>
       <c r="G11" s="64" t="inlineStr">
         <is>
@@ -10701,7 +10701,7 @@
         </is>
       </c>
       <c r="E17" s="64" t="n">
-        <v>17.2195</v>
+        <v>17.1387</v>
       </c>
       <c r="F17" s="64" t="n"/>
       <c r="G17" s="64" t="inlineStr">
@@ -13356,7 +13356,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-07T14:06:58+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-10T14:13:35+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13485,12 +13485,12 @@
       </c>
       <c r="K5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L5" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M5" s="84" t="inlineStr">
@@ -13553,12 +13553,12 @@
       </c>
       <c r="K6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L6" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M6" s="83" t="inlineStr">
@@ -13621,12 +13621,12 @@
       </c>
       <c r="K7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L7" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M7" s="84" t="inlineStr">
@@ -13685,12 +13685,12 @@
       </c>
       <c r="K8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L8" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M8" s="83" t="inlineStr">
@@ -13753,12 +13753,12 @@
       </c>
       <c r="K9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L9" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M9" s="84" t="inlineStr">
@@ -13821,12 +13821,12 @@
       </c>
       <c r="K10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L10" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M10" s="83" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="G11" s="84" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="H11" s="84" t="inlineStr">
         <is>
-          <t>Jun 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="I11" s="84" t="n"/>
@@ -13885,12 +13885,12 @@
       </c>
       <c r="K11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L11" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M11" s="84" t="inlineStr">
@@ -14157,12 +14157,12 @@
       </c>
       <c r="K15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L15" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M15" s="84" t="inlineStr">
@@ -14293,12 +14293,12 @@
       </c>
       <c r="K17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L17" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M17" s="84" t="inlineStr">
@@ -14361,12 +14361,12 @@
       </c>
       <c r="K18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L18" s="83" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M18" s="83" t="inlineStr">
@@ -14429,12 +14429,12 @@
       </c>
       <c r="K19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="L19" s="84" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="M19" s="84" t="inlineStr">

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 10/08/2026 17:10 UTC</t>
+          <t>Generado: 10/08/2026 17:30 UTC</t>
         </is>
       </c>
     </row>
@@ -13442,7 +13442,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-10T17:10:14+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-10T17:30:39+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -10224,7 +10224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10246,7 +10246,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 10/08/2026 17:30 UTC</t>
+          <t>Generado: 10/08/2026 18:31 UTC</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="F15" s="64" t="inlineStr">
         <is>
-          <t>-0.6%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="G15" s="64" t="inlineStr">
@@ -10842,17 +10842,67 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="65" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de Opinión Empresarial</t>
+        </is>
+      </c>
+      <c r="B20" s="65" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C20" s="65" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="D20" s="65" t="n"/>
+      <c r="E20" s="65" t="n"/>
+      <c r="F20" s="65" t="n"/>
+      <c r="G20" s="65" t="inlineStr">
+        <is>
+          <t>Puntos</t>
+        </is>
+      </c>
+    </row>
     <row r="21">
-      <c r="A21" s="66" t="inlineStr">
+      <c r="A21" s="64" t="inlineStr">
+        <is>
+          <t>Balanza Comercial de Mercancías de México</t>
+        </is>
+      </c>
+      <c r="B21" s="64" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C21" s="64" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="D21" s="64" t="n"/>
+      <c r="E21" s="64" t="n"/>
+      <c r="F21" s="64" t="n"/>
+      <c r="G21" s="64" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="66" t="inlineStr">
         <is>
           <t>Nota: cifras oficiales sujetas a revisión. Análisis por reglas deterministas; no se atribuye causalidad. La fuente de la tasa de desocupación es INEGI/ENOE. Los indicadores en estado 'pendiente de token' o 'dato de respaldo' no se presentan como actualización automática (ver 'Control de actualizaciones').</t>
         </is>
       </c>
     </row>
-    <row r="22"/>
+    <row r="24"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A21:G22"/>
+    <mergeCell ref="A23:G24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11727,7 +11777,9 @@
       <c r="C5" s="82" t="n">
         <v>0.001</v>
       </c>
-      <c r="D5" s="82" t="n"/>
+      <c r="D5" s="82" t="n">
+        <v>-0.045</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
@@ -12044,7 +12096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12098,184 +12150,186 @@
     <row r="5">
       <c r="A5" s="82" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="B5" s="82" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C5" s="82" t="n"/>
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="82" t="n">
+        <v>2.4</v>
+      </c>
       <c r="D5" s="82" t="n">
         <v>-0.9</v>
       </c>
       <c r="E5" s="82" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="B6" s="82" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="C6" s="82" t="n"/>
+        <v>0.2</v>
+      </c>
+      <c r="C6" s="82" t="n">
+        <v>2.1</v>
+      </c>
       <c r="D6" s="82" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="E6" s="82" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="82" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>Jun 24</t>
         </is>
       </c>
       <c r="B7" s="82" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C7" s="82" t="n">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="D7" s="82" t="n">
-        <v>-0.8</v>
+        <v>-1.2</v>
       </c>
       <c r="E7" s="82" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="82" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B8" s="82" t="n">
         <v>0.2</v>
       </c>
-      <c r="C8" s="82" t="n">
-        <v>-0.7</v>
-      </c>
+      <c r="C8" s="82" t="n"/>
       <c r="D8" s="82" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="E8" s="82" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="82" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B9" s="82" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C9" s="82" t="n">
-        <v>-0.2</v>
+        <v>1.1</v>
       </c>
       <c r="D9" s="82" t="n">
-        <v>-1.2</v>
+        <v>-0.8</v>
       </c>
       <c r="E9" s="82" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B10" s="82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C10" s="82" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="D10" s="82" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="E10" s="82" t="n">
-        <v>1.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="82" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B11" s="82" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C11" s="82" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
       <c r="D11" s="82" t="n">
         <v>-1</v>
       </c>
       <c r="E11" s="82" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B12" s="82" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C12" s="82" t="n">
-        <v>1.3</v>
+        <v>-0.2</v>
       </c>
       <c r="D12" s="82" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="E12" s="82" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="82" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Abr 25</t>
         </is>
       </c>
       <c r="B13" s="82" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C13" s="82" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="D13" s="82" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="E13" s="82" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="82" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B14" s="82" t="n">
         <v>0.1</v>
       </c>
       <c r="C14" s="82" t="n">
-        <v>0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="D14" s="82" t="n">
-        <v>-1.1</v>
+        <v>-1</v>
       </c>
       <c r="E14" s="82" t="n">
         <v>1.3</v>
@@ -12284,36 +12338,36 @@
     <row r="15">
       <c r="A15" s="82" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B15" s="82" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C15" s="82" t="n">
-        <v>-0.6</v>
+        <v>1.3</v>
       </c>
       <c r="D15" s="82" t="n">
-        <v>-1</v>
+        <v>-0.9</v>
       </c>
       <c r="E15" s="82" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="82" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B16" s="82" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="C16" s="82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D16" s="82" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="E16" s="82" t="n">
         <v>0.9</v>
@@ -12322,109 +12376,109 @@
     <row r="17">
       <c r="A17" s="82" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B17" s="82" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C17" s="82" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="D17" s="82" t="n">
-        <v>-1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="E17" s="82" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="82" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B18" s="82" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C18" s="82" t="n">
-        <v>2.3</v>
+        <v>-0.6</v>
       </c>
       <c r="D18" s="82" t="n">
         <v>-1</v>
       </c>
       <c r="E18" s="82" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="82" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B19" s="82" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="C19" s="82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="D19" s="82" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
       <c r="E19" s="82" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="82" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B20" s="82" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="C20" s="82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D20" s="82" t="n">
-        <v>-1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="E20" s="82" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="82" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B21" s="82" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C21" s="82" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="D21" s="82" t="n">
-        <v>-1.2</v>
+        <v>-1</v>
       </c>
       <c r="E21" s="82" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="82" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B22" s="82" t="n">
         <v>0.3</v>
       </c>
       <c r="C22" s="82" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="D22" s="82" t="n">
         <v>-0.6</v>
@@ -12436,38 +12490,95 @@
     <row r="23">
       <c r="A23" s="82" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Feb 26</t>
         </is>
       </c>
       <c r="B23" s="82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="C23" s="82" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="D23" s="82" t="n">
         <v>-1.1</v>
       </c>
       <c r="E23" s="82" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="82" t="inlineStr">
         <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D24" s="82" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E24" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B25" s="82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C25" s="82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D25" s="82" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E25" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B26" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="82" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D26" s="82" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E26" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="82" t="inlineStr">
+        <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B24" s="82" t="n">
+      <c r="B27" s="82" t="n">
         <v>0.2</v>
       </c>
-      <c r="C24" s="82" t="n">
+      <c r="C27" s="82" t="n">
         <v>1.7</v>
       </c>
-      <c r="D24" s="82" t="n">
+      <c r="D27" s="82" t="n">
         <v>-1</v>
       </c>
-      <c r="E24" s="82" t="n">
+      <c r="E27" s="82" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -12482,7 +12593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12524,183 +12635,1314 @@
     <row r="5">
       <c r="A5" s="82" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Ene 18</t>
         </is>
       </c>
       <c r="B5" s="82" t="n">
-        <v>107.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="C5" s="82" t="n">
-        <v>0.011</v>
+        <v>0.064481</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Feb 18</t>
         </is>
       </c>
       <c r="B6" s="82" t="n">
-        <v>99.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="C6" s="82" t="n">
-        <v>-0.015</v>
+        <v>-0.030801</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="82" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Mar 18</t>
         </is>
       </c>
       <c r="B7" s="82" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C7" s="82" t="n">
-        <v>0.026</v>
+        <v>0.091102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="82" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Abr 18</t>
         </is>
       </c>
       <c r="B8" s="82" t="n">
-        <v>113.5</v>
+        <v>100.7</v>
       </c>
       <c r="C8" s="82" t="n">
-        <v>-0.02</v>
+        <v>-0.02233</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="82" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>May 18</t>
         </is>
       </c>
       <c r="B9" s="82" t="n">
-        <v>108.9</v>
+        <v>106.2</v>
       </c>
       <c r="C9" s="82" t="n">
-        <v>-0.001</v>
+        <v>0.054618</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Jun 18</t>
         </is>
       </c>
       <c r="B10" s="82" t="n">
-        <v>112.1</v>
+        <v>102.1</v>
       </c>
       <c r="C10" s="82" t="n">
-        <v>0.01</v>
+        <v>-0.038606</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="82" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Jul 18</t>
         </is>
       </c>
       <c r="B11" s="82" t="n">
-        <v>110.2</v>
+        <v>99</v>
       </c>
       <c r="C11" s="82" t="n">
-        <v>-0.027</v>
+        <v>-0.030362</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>Ago 18</t>
         </is>
       </c>
       <c r="B12" s="82" t="n">
-        <v>109.1</v>
+        <v>105.8</v>
       </c>
       <c r="C12" s="82" t="n">
-        <v>0.002</v>
+        <v>0.068687</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="82" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Sep 18</t>
         </is>
       </c>
       <c r="B13" s="82" t="n">
-        <v>112.9</v>
+        <v>98</v>
       </c>
       <c r="C13" s="82" t="n">
-        <v>0.003</v>
+        <v>-0.073724</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="82" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Oct 18</t>
         </is>
       </c>
       <c r="B14" s="82" t="n">
-        <v>103.5</v>
+        <v>103.1</v>
       </c>
       <c r="C14" s="82" t="n">
-        <v>-0.001</v>
+        <v>0.052041</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="82" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Nov 18</t>
         </is>
       </c>
       <c r="B15" s="82" t="n">
-        <v>107.1</v>
+        <v>100.4</v>
       </c>
       <c r="C15" s="82" t="n">
-        <v>0.034</v>
+        <v>-0.026188</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="82" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Dic 18</t>
         </is>
       </c>
       <c r="B16" s="82" t="n">
-        <v>115.4</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="C16" s="82" t="n">
-        <v>-0.011</v>
+        <v>-0.104582</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="82" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Ene 19</t>
         </is>
       </c>
       <c r="B17" s="82" t="n">
-        <v>111.2</v>
+        <v>97.3</v>
       </c>
       <c r="C17" s="82" t="n">
-        <v>0.005</v>
+        <v>0.082314</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="82" t="inlineStr">
         <is>
+          <t>Feb 19</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="C18" s="82" t="n">
+        <v>-0.012333</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>Mar 19</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>103.4</v>
+      </c>
+      <c r="C19" s="82" t="n">
+        <v>0.075963</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>Abr 19</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="n">
+        <v>98.90000000000001</v>
+      </c>
+      <c r="C20" s="82" t="n">
+        <v>-0.04352</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="C21" s="82" t="n">
+        <v>0.066734</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
+        <is>
+          <t>Jun 19</t>
+        </is>
+      </c>
+      <c r="B22" s="82" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="C22" s="82" t="n">
+        <v>-0.034123</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>Jul 19</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="n">
+        <v>101.9</v>
+      </c>
+      <c r="C23" s="82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>Ago 19</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="C24" s="82" t="n">
+        <v>0.019627</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="inlineStr">
+        <is>
+          <t>Sep 19</t>
+        </is>
+      </c>
+      <c r="B25" s="82" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="C25" s="82" t="n">
+        <v>-0.049086</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="82" t="inlineStr">
+        <is>
+          <t>Oct 19</t>
+        </is>
+      </c>
+      <c r="B26" s="82" t="n">
+        <v>100</v>
+      </c>
+      <c r="C26" s="82" t="n">
+        <v>0.012146</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="82" t="inlineStr">
+        <is>
+          <t>Nov 19</t>
+        </is>
+      </c>
+      <c r="B27" s="82" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="C27" s="82" t="n">
+        <v>-0.023</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="82" t="inlineStr">
+        <is>
+          <t>Dic 19</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="n">
+        <v>89.3</v>
+      </c>
+      <c r="C28" s="82" t="n">
+        <v>-0.085977</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="82" t="inlineStr">
+        <is>
+          <t>Ene 20</t>
+        </is>
+      </c>
+      <c r="B29" s="82" t="n">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="C29" s="82" t="n">
+        <v>0.101904</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="82" t="inlineStr">
+        <is>
+          <t>Feb 20</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="n">
+        <v>96.09999999999999</v>
+      </c>
+      <c r="C30" s="82" t="n">
+        <v>-0.023374</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="82" t="inlineStr">
+        <is>
+          <t>Mar 20</t>
+        </is>
+      </c>
+      <c r="B31" s="82" t="n">
+        <v>97.3</v>
+      </c>
+      <c r="C31" s="82" t="n">
+        <v>0.012487</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="82" t="inlineStr">
+        <is>
+          <t>Abr 20</t>
+        </is>
+      </c>
+      <c r="B32" s="82" t="n">
+        <v>64</v>
+      </c>
+      <c r="C32" s="82" t="n">
+        <v>-0.34224</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="82" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="B33" s="82" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="C33" s="82" t="n">
+        <v>0.026563</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="82" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="B34" s="82" t="n">
+        <v>88.40000000000001</v>
+      </c>
+      <c r="C34" s="82" t="n">
+        <v>0.34551</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="82" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="C35" s="82" t="n">
+        <v>0.049774</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="82" t="inlineStr">
+        <is>
+          <t>Ago 20</t>
+        </is>
+      </c>
+      <c r="B36" s="82" t="n">
+        <v>94.7</v>
+      </c>
+      <c r="C36" s="82" t="n">
+        <v>0.020474</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="82" t="inlineStr">
+        <is>
+          <t>Sep 20</t>
+        </is>
+      </c>
+      <c r="B37" s="82" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="C37" s="82" t="n">
+        <v>0.038015</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="82" t="inlineStr">
+        <is>
+          <t>Oct 20</t>
+        </is>
+      </c>
+      <c r="B38" s="82" t="n">
+        <v>102.6</v>
+      </c>
+      <c r="C38" s="82" t="n">
+        <v>0.043744</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="82" t="inlineStr">
+        <is>
+          <t>Nov 20</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="n">
+        <v>97.2</v>
+      </c>
+      <c r="C39" s="82" t="n">
+        <v>-0.052632</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="82" t="inlineStr">
+        <is>
+          <t>Dic 20</t>
+        </is>
+      </c>
+      <c r="B40" s="82" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="C40" s="82" t="n">
+        <v>-0.014403</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="82" t="inlineStr">
+        <is>
+          <t>Ene 21</t>
+        </is>
+      </c>
+      <c r="B41" s="82" t="n">
+        <v>98</v>
+      </c>
+      <c r="C41" s="82" t="n">
+        <v>0.022965</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="82" t="inlineStr">
+        <is>
+          <t>Feb 21</t>
+        </is>
+      </c>
+      <c r="B42" s="82" t="n">
+        <v>93</v>
+      </c>
+      <c r="C42" s="82" t="n">
+        <v>-0.05102</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="82" t="inlineStr">
+        <is>
+          <t>Mar 21</t>
+        </is>
+      </c>
+      <c r="B43" s="82" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="C43" s="82" t="n">
+        <v>0.177419</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="82" t="inlineStr">
+        <is>
+          <t>Abr 21</t>
+        </is>
+      </c>
+      <c r="B44" s="82" t="n">
+        <v>99.8</v>
+      </c>
+      <c r="C44" s="82" t="n">
+        <v>-0.088584</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="82" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="B45" s="82" t="n">
+        <v>99.3</v>
+      </c>
+      <c r="C45" s="82" t="n">
+        <v>-0.00501</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="82" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B46" s="82" t="n">
+        <v>101</v>
+      </c>
+      <c r="C46" s="82" t="n">
+        <v>0.01712</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="82" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B47" s="82" t="n">
+        <v>98.8</v>
+      </c>
+      <c r="C47" s="82" t="n">
+        <v>-0.021782</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="82" t="inlineStr">
+        <is>
+          <t>Ago 21</t>
+        </is>
+      </c>
+      <c r="B48" s="82" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="C48" s="82" t="n">
+        <v>0.013158</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="82" t="inlineStr">
+        <is>
+          <t>Sep 21</t>
+        </is>
+      </c>
+      <c r="B49" s="82" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="C49" s="82" t="n">
+        <v>-0.032967</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="82" t="inlineStr">
+        <is>
+          <t>Oct 21</t>
+        </is>
+      </c>
+      <c r="B50" s="82" t="n">
+        <v>101</v>
+      </c>
+      <c r="C50" s="82" t="n">
+        <v>0.043388</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="82" t="inlineStr">
+        <is>
+          <t>Nov 21</t>
+        </is>
+      </c>
+      <c r="B51" s="82" t="n">
+        <v>100.6</v>
+      </c>
+      <c r="C51" s="82" t="n">
+        <v>-0.00396</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="82" t="inlineStr">
+        <is>
+          <t>Dic 21</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C52" s="82" t="n">
+        <v>-0.009939999999999999</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="82" t="inlineStr">
+        <is>
+          <t>Ene 22</t>
+        </is>
+      </c>
+      <c r="B53" s="82" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="C53" s="82" t="n">
+        <v>0.031124</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="82" t="inlineStr">
+        <is>
+          <t>Feb 22</t>
+        </is>
+      </c>
+      <c r="B54" s="82" t="n">
+        <v>100.9</v>
+      </c>
+      <c r="C54" s="82" t="n">
+        <v>-0.017527</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="82" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="B55" s="82" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="C55" s="82" t="n">
+        <v>0.122894</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="82" t="inlineStr">
+        <is>
+          <t>Abr 22</t>
+        </is>
+      </c>
+      <c r="B56" s="82" t="n">
+        <v>105.1</v>
+      </c>
+      <c r="C56" s="82" t="n">
+        <v>-0.07237399999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="82" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="B57" s="82" t="n">
+        <v>108.1</v>
+      </c>
+      <c r="C57" s="82" t="n">
+        <v>0.028544</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="82" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B58" s="82" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="C58" s="82" t="n">
+        <v>-0.032377</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="82" t="inlineStr">
+        <is>
+          <t>Jul 22</t>
+        </is>
+      </c>
+      <c r="B59" s="82" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="C59" s="82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="82" t="inlineStr">
+        <is>
+          <t>Ago 22</t>
+        </is>
+      </c>
+      <c r="B60" s="82" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="C60" s="82" t="n">
+        <v>0.054493</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="82" t="inlineStr">
+        <is>
+          <t>Sep 22</t>
+        </is>
+      </c>
+      <c r="B61" s="82" t="n">
+        <v>105</v>
+      </c>
+      <c r="C61" s="82" t="n">
+        <v>-0.048051</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="82" t="inlineStr">
+        <is>
+          <t>Oct 22</t>
+        </is>
+      </c>
+      <c r="B62" s="82" t="n">
+        <v>108.4</v>
+      </c>
+      <c r="C62" s="82" t="n">
+        <v>0.032381</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="82" t="inlineStr">
+        <is>
+          <t>Nov 22</t>
+        </is>
+      </c>
+      <c r="B63" s="82" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="C63" s="82" t="n">
+        <v>-0.009225000000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="82" t="inlineStr">
+        <is>
+          <t>Dic 22</t>
+        </is>
+      </c>
+      <c r="B64" s="82" t="n">
+        <v>103.3</v>
+      </c>
+      <c r="C64" s="82" t="n">
+        <v>-0.038175</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="82" t="inlineStr">
+        <is>
+          <t>Ene 23</t>
+        </is>
+      </c>
+      <c r="B65" s="82" t="n">
+        <v>106.8</v>
+      </c>
+      <c r="C65" s="82" t="n">
+        <v>0.033882</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="82" t="inlineStr">
+        <is>
+          <t>Feb 23</t>
+        </is>
+      </c>
+      <c r="B66" s="82" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="C66" s="82" t="n">
+        <v>-0.040262</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="82" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="B67" s="82" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="C67" s="82" t="n">
+        <v>0.126829</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="82" t="inlineStr">
+        <is>
+          <t>Abr 23</t>
+        </is>
+      </c>
+      <c r="B68" s="82" t="n">
+        <v>107.3</v>
+      </c>
+      <c r="C68" s="82" t="n">
+        <v>-0.070996</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="82" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="B69" s="82" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="C69" s="82" t="n">
+        <v>0.039143</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="82" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B70" s="82" t="n">
+        <v>108.7</v>
+      </c>
+      <c r="C70" s="82" t="n">
+        <v>-0.025112</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="82" t="inlineStr">
+        <is>
+          <t>Jul 23</t>
+        </is>
+      </c>
+      <c r="B71" s="82" t="n">
+        <v>106.4</v>
+      </c>
+      <c r="C71" s="82" t="n">
+        <v>-0.021159</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="82" t="inlineStr">
+        <is>
+          <t>Ago 23</t>
+        </is>
+      </c>
+      <c r="B72" s="82" t="n">
+        <v>110</v>
+      </c>
+      <c r="C72" s="82" t="n">
+        <v>0.033835</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="82" t="inlineStr">
+        <is>
+          <t>Sep 23</t>
+        </is>
+      </c>
+      <c r="B73" s="82" t="n">
+        <v>107.2</v>
+      </c>
+      <c r="C73" s="82" t="n">
+        <v>-0.025455</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="82" t="inlineStr">
+        <is>
+          <t>Oct 23</t>
+        </is>
+      </c>
+      <c r="B74" s="82" t="n">
+        <v>109</v>
+      </c>
+      <c r="C74" s="82" t="n">
+        <v>0.016791</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="82" t="inlineStr">
+        <is>
+          <t>Nov 23</t>
+        </is>
+      </c>
+      <c r="B75" s="82" t="n">
+        <v>107</v>
+      </c>
+      <c r="C75" s="82" t="n">
+        <v>-0.018349</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>Dic 23</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="n">
+        <v>99.59999999999999</v>
+      </c>
+      <c r="C76" s="82" t="n">
+        <v>-0.069159</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="82" t="inlineStr">
+        <is>
+          <t>Ene 24</t>
+        </is>
+      </c>
+      <c r="B77" s="82" t="n">
+        <v>108.8</v>
+      </c>
+      <c r="C77" s="82" t="n">
+        <v>0.09236900000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="82" t="inlineStr">
+        <is>
+          <t>Feb 24</t>
+        </is>
+      </c>
+      <c r="B78" s="82" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="C78" s="82" t="n">
+        <v>-0.011949</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="82" t="inlineStr">
+        <is>
+          <t>Mar 24</t>
+        </is>
+      </c>
+      <c r="B79" s="82" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="C79" s="82" t="n">
+        <v>0.034419</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="82" t="inlineStr">
+        <is>
+          <t>Abr 24</t>
+        </is>
+      </c>
+      <c r="B80" s="82" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="C80" s="82" t="n">
+        <v>0.017986</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="82" t="inlineStr">
+        <is>
+          <t>May 24</t>
+        </is>
+      </c>
+      <c r="B81" s="82" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="C81" s="82" t="n">
+        <v>-0.015018</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="82" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B82" s="82" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="C82" s="82" t="n">
+        <v>-0.026906</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="82" t="inlineStr">
+        <is>
+          <t>Jul 24</t>
+        </is>
+      </c>
+      <c r="B83" s="82" t="n">
+        <v>110.3</v>
+      </c>
+      <c r="C83" s="82" t="n">
+        <v>0.01659</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="82" t="inlineStr">
+        <is>
+          <t>Ago 24</t>
+        </is>
+      </c>
+      <c r="B84" s="82" t="n">
+        <v>112.8</v>
+      </c>
+      <c r="C84" s="82" t="n">
+        <v>0.022665</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="82" t="inlineStr">
+        <is>
+          <t>Sep 24</t>
+        </is>
+      </c>
+      <c r="B85" s="82" t="n">
+        <v>109.9</v>
+      </c>
+      <c r="C85" s="82" t="n">
+        <v>-0.025709</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="82" t="inlineStr">
+        <is>
+          <t>Oct 24</t>
+        </is>
+      </c>
+      <c r="B86" s="82" t="n">
+        <v>112</v>
+      </c>
+      <c r="C86" s="82" t="n">
+        <v>0.019108</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="82" t="inlineStr">
+        <is>
+          <t>Nov 24</t>
+        </is>
+      </c>
+      <c r="B87" s="82" t="n">
+        <v>107.7</v>
+      </c>
+      <c r="C87" s="82" t="n">
+        <v>-0.038393</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="82" t="inlineStr">
+        <is>
+          <t>Dic 24</t>
+        </is>
+      </c>
+      <c r="B88" s="82" t="n">
+        <v>99.2</v>
+      </c>
+      <c r="C88" s="82" t="n">
+        <v>-0.07892299999999999</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="82" t="inlineStr">
+        <is>
+          <t>Ene 25</t>
+        </is>
+      </c>
+      <c r="B89" s="82" t="n">
+        <v>107.4</v>
+      </c>
+      <c r="C89" s="82" t="n">
+        <v>0.082661</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="82" t="inlineStr">
+        <is>
+          <t>Feb 25</t>
+        </is>
+      </c>
+      <c r="B90" s="82" t="n">
+        <v>106</v>
+      </c>
+      <c r="C90" s="82" t="n">
+        <v>-0.013035</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="82" t="inlineStr">
+        <is>
+          <t>Mar 25</t>
+        </is>
+      </c>
+      <c r="B91" s="82" t="n">
+        <v>113.5</v>
+      </c>
+      <c r="C91" s="82" t="n">
+        <v>0.070755</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="82" t="inlineStr">
+        <is>
+          <t>Abr 25</t>
+        </is>
+      </c>
+      <c r="B92" s="82" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="C92" s="82" t="n">
+        <v>-0.040529</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="82" t="inlineStr">
+        <is>
+          <t>May 25</t>
+        </is>
+      </c>
+      <c r="B93" s="82" t="n">
+        <v>112.1</v>
+      </c>
+      <c r="C93" s="82" t="n">
+        <v>0.029385</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="82" t="inlineStr">
+        <is>
+          <t>Jun 25</t>
+        </is>
+      </c>
+      <c r="B94" s="82" t="n">
+        <v>111.9</v>
+      </c>
+      <c r="C94" s="82" t="n">
+        <v>-0.001784</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="82" t="inlineStr">
+        <is>
+          <t>Jul 25</t>
+        </is>
+      </c>
+      <c r="B95" s="82" t="n">
+        <v>110.2</v>
+      </c>
+      <c r="C95" s="82" t="n">
+        <v>-0.015192</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="82" t="inlineStr">
+        <is>
+          <t>Ago 25</t>
+        </is>
+      </c>
+      <c r="B96" s="82" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="C96" s="82" t="n">
+        <v>-0.00726</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="82" t="inlineStr">
+        <is>
+          <t>Sep 25</t>
+        </is>
+      </c>
+      <c r="B97" s="82" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="C97" s="82" t="n">
+        <v>-0.002742</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="82" t="inlineStr">
+        <is>
+          <t>Oct 25</t>
+        </is>
+      </c>
+      <c r="B98" s="82" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="C98" s="82" t="n">
+        <v>0.03483</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="82" t="inlineStr">
+        <is>
+          <t>Nov 25</t>
+        </is>
+      </c>
+      <c r="B99" s="82" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="C99" s="82" t="n">
+        <v>-0.045173</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="82" t="inlineStr">
+        <is>
+          <t>Dic 25</t>
+        </is>
+      </c>
+      <c r="B100" s="82" t="n">
+        <v>103.5</v>
+      </c>
+      <c r="C100" s="82" t="n">
+        <v>-0.039889</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="82" t="inlineStr">
+        <is>
+          <t>Ene 26</t>
+        </is>
+      </c>
+      <c r="B101" s="82" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="C101" s="82" t="n">
+        <v>0.022222</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="82" t="inlineStr">
+        <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B102" s="82" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="C102" s="82" t="n">
+        <v>0.012287</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="82" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B103" s="82" t="n">
+        <v>115.4</v>
+      </c>
+      <c r="C103" s="82" t="n">
+        <v>0.077498</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="82" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B104" s="82" t="n">
+        <v>111.2</v>
+      </c>
+      <c r="C104" s="82" t="n">
+        <v>-0.036395</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="82" t="inlineStr">
+        <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="B18" s="82" t="n">
+      <c r="B105" s="82" t="n">
         <v>110.4</v>
       </c>
-      <c r="C18" s="82" t="n">
-        <v>-0.006</v>
+      <c r="C105" s="82" t="n">
+        <v>-0.007194</v>
       </c>
     </row>
   </sheetData>
@@ -12714,7 +13956,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13402,6 +14644,90 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="84" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de Opinión Empresarial</t>
+        </is>
+      </c>
+      <c r="B19" s="84" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C19" s="84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="84" t="inlineStr">
+        <is>
+          <t>Puntos</t>
+        </is>
+      </c>
+      <c r="E19" s="84" t="inlineStr">
+        <is>
+          <t>Serie desestacionalizada</t>
+        </is>
+      </c>
+      <c r="F19" s="84" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G19" s="84" t="inlineStr">
+        <is>
+          <t>INEGI BIE API</t>
+        </is>
+      </c>
+      <c r="H19" s="84" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/temas/emoe/</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="inlineStr">
+        <is>
+          <t>Balanza Comercial de Mercancías de México</t>
+        </is>
+      </c>
+      <c r="B20" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="C20" s="83" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="83" t="inlineStr">
+        <is>
+          <t>Millones de dólares</t>
+        </is>
+      </c>
+      <c r="E20" s="83" t="inlineStr">
+        <is>
+          <t>Serie original</t>
+        </is>
+      </c>
+      <c r="F20" s="83" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+      <c r="G20" s="83" t="inlineStr">
+        <is>
+          <t>INEGI BIE API</t>
+        </is>
+      </c>
+      <c r="H20" s="83" t="inlineStr">
+        <is>
+          <t>https://www.inegi.org.mx/temas/balanza/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13413,7 +14739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -13442,7 +14768,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Última corrida del pipeline: 2026-08-10T17:30:39+00:00 · resultado: OK · modo: offline</t>
+          <t>Última corrida del pipeline: 2026-08-10T18:31:08+00:00 · resultado: OK · modo: offline</t>
         </is>
       </c>
     </row>
@@ -13599,7 +14925,7 @@
       </c>
       <c r="C6" s="83" t="inlineStr">
         <is>
-          <t>PUBLICACIÓN PENDIENTE</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D6" s="83" t="inlineStr">
@@ -14279,7 +15605,7 @@
       </c>
       <c r="C16" s="83" t="inlineStr">
         <is>
-          <t>PUBLICACIÓN PENDIENTE</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D16" s="83" t="inlineStr">
@@ -14347,7 +15673,7 @@
       </c>
       <c r="C17" s="84" t="inlineStr">
         <is>
-          <t>PUBLICACIÓN PENDIENTE</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D17" s="84" t="inlineStr">
@@ -14415,7 +15741,7 @@
       </c>
       <c r="C18" s="83" t="inlineStr">
         <is>
-          <t>PUBLICACIÓN PENDIENTE</t>
+          <t>ACTUALIZADO</t>
         </is>
       </c>
       <c r="D18" s="83" t="inlineStr">
@@ -14483,72 +15809,295 @@
       </c>
       <c r="C19" s="84" t="inlineStr">
         <is>
+          <t>REZAGADO</t>
+        </is>
+      </c>
+      <c r="D19" s="84" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="E19" s="84" t="inlineStr">
+        <is>
+          <t>BANXICO</t>
+        </is>
+      </c>
+      <c r="F19" s="84" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G19" s="84" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="H19" s="84" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="I19" s="84" t="inlineStr">
+        <is>
+          <t>Semanal (martes)</t>
+        </is>
+      </c>
+      <c r="J19" s="84" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K19" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="L19" s="84" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="M19" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N19" s="84" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="83" t="inlineStr">
+        <is>
+          <t>Encuesta Mensual de Opinión Empresarial</t>
+        </is>
+      </c>
+      <c r="B20" s="83" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C20" s="83" t="inlineStr">
+        <is>
           <t>PUBLICACIÓN PENDIENTE</t>
         </is>
       </c>
-      <c r="D19" s="84" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="E19" s="84" t="inlineStr">
-        <is>
-          <t>BANXICO</t>
-        </is>
-      </c>
-      <c r="F19" s="84" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G19" s="84" t="inlineStr">
-        <is>
-          <t>Jul 26</t>
-        </is>
-      </c>
-      <c r="H19" s="84" t="inlineStr">
-        <is>
-          <t>Jul 26</t>
-        </is>
-      </c>
-      <c r="I19" s="84" t="inlineStr">
-        <is>
-          <t>Semanal (martes)</t>
-        </is>
-      </c>
-      <c r="J19" s="84" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K19" s="84" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="L19" s="84" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="M19" s="84" t="inlineStr">
+      <c r="D20" s="83" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E20" s="83" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F20" s="83" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="N19" s="84" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="85" t="inlineStr">
+      <c r="G20" s="83" t="n"/>
+      <c r="H20" s="83" t="n"/>
+      <c r="I20" s="83" t="inlineStr">
+        <is>
+          <t>3 de agosto de 2026</t>
+        </is>
+      </c>
+      <c r="J20" s="83" t="inlineStr">
+        <is>
+          <t>1 de septiembre de 2026 · Agosto 2026</t>
+        </is>
+      </c>
+      <c r="K20" s="83" t="n"/>
+      <c r="L20" s="83" t="n"/>
+      <c r="M20" s="83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N20" s="83" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="84" t="inlineStr">
+        <is>
+          <t>Balanza Comercial de Mercancías de México</t>
+        </is>
+      </c>
+      <c r="B21" s="84" t="inlineStr">
+        <is>
+          <t>complementario</t>
+        </is>
+      </c>
+      <c r="C21" s="84" t="inlineStr">
+        <is>
+          <t>PUBLICACIÓN PENDIENTE</t>
+        </is>
+      </c>
+      <c r="D21" s="84" t="inlineStr">
+        <is>
+          <t>pendiente</t>
+        </is>
+      </c>
+      <c r="E21" s="84" t="inlineStr">
+        <is>
+          <t>INEGI</t>
+        </is>
+      </c>
+      <c r="F21" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" s="84" t="n"/>
+      <c r="H21" s="84" t="n"/>
+      <c r="I21" s="84" t="inlineStr">
+        <is>
+          <t>27 de julio de 2026</t>
+        </is>
+      </c>
+      <c r="J21" s="84" t="inlineStr">
+        <is>
+          <t>27 de agosto de 2026 · Julio 2026</t>
+        </is>
+      </c>
+      <c r="K21" s="84" t="n"/>
+      <c r="L21" s="84" t="n"/>
+      <c r="M21" s="84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N21" s="84" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="85" t="inlineStr">
         <is>
           <t>Advertencias del pipeline:</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="62" t="inlineStr">
-        <is>
-          <t>• PIB: REZAGADO – El calendario indica que ya se publicó 2° trimestre 2026, pero el dashboard aún muestra 1T-26.</t>
+    <row r="25">
+      <c r="A25" s="62" t="inlineStr">
+        <is>
+          <t>• PIB: REZAGADO – El periodo esperado es 2° trimestre 2026, pero el dashboard aún muestra 1T-26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>• RESERVAS: REZAGADO – El periodo esperado es Ago 26, pero el dashboard aún muestra Jul 26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="62" t="inlineStr">
+        <is>
+          <t>• [EMOE] sin observaciones (estado: PUBLICACIÓN PENDIENTE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>• [BCMM] sin observaciones (estado: PUBLICACIÓN PENDIENTE).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-18: 14350827.278 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-18: 14313691.858 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-19: 14270949.004 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-19: 14322078.244 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-20: 11664084.703 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-20: 13054858.82 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-21: 14063214.857 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-21: 13810362.579 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-22: 14325766.844 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-22: 14421864.812 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-23: 14833956.646 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="62" t="inlineStr">
+        <is>
+          <t>• [PIBSEC] valor fuera de rango plausible en 1T-23: 14924452.582 (esperado (15000000, 35000000)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="62" t="inlineStr">
+        <is>
+          <t>• [IMAI] valor fuera de rango plausible en Abr 20: 69.864321 (esperado (70, 130)).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="62" t="inlineStr">
+        <is>
+          <t>• [IMAI] valor fuera de rango plausible en May 20: 69.771418 (esperado (70, 130)).</t>
         </is>
       </c>
     </row>

--- a/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
+++ b/downloads/Indicadores_Macroeconomicos_Mexico_Actualizado.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="6" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18465" tabRatio="600" firstSheet="1" activeTab="5" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Síntesis de coyuntura" sheetId="1" state="visible" r:id="rId1"/>
@@ -11,17 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PIB Sectorial" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IGAE" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IMAI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exportaciones" sheetId="6" state="hidden" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumo Privado" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IED" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasa de desocupación" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INPC (Inflación)" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formación bruta capital fijo" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IOAE" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EMIM (Manufactura)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balanza comercial" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metodología y fuentes" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control de actualizaciones" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -169,7 +168,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -214,6 +213,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F5EF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6E2E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -470,7 +474,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -684,6 +688,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1702,1076 +1709,6 @@
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart10.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-MX" sz="1600" b="1"/>
-              <a:t xml:space="preserve">Inflación (porcentual) </a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'INPC (Inflación)'!$C$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Inflación</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="1E5B4F"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="1E5B4F"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="1E5B4F"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLbl>
-              <idx val="9"/>
-              <spPr>
-                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:sysClr val="window" lastClr="FFFFFF"/>
-                </a:solidFill>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000">
-                      <a:lumOff val="75000"/>
-                      <a:lumMod val="25000"/>
-                    </a:sysClr>
-                  </a:solidFill>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="65000"/>
-                          <a:lumOff val="35000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="t"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="11"/>
-              <dLblPos val="b"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="1E5B4F"/>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>'INPC (Inflación)'!$B$10:$B$21</f>
-              <strCache>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="3">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="4">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="5">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="6">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="7">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="8">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="9">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="10">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="11">
-                  <v>May 26</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'INPC (Inflación)'!$C$10:$C$21</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>4.32</v>
-                </pt>
-                <pt idx="1">
-                  <v>3.51</v>
-                </pt>
-                <pt idx="2">
-                  <v>3.57</v>
-                </pt>
-                <pt idx="3">
-                  <v>3.76</v>
-                </pt>
-                <pt idx="4">
-                  <v>3.57</v>
-                </pt>
-                <pt idx="5">
-                  <v>3.8</v>
-                </pt>
-                <pt idx="6">
-                  <v>3.69</v>
-                </pt>
-                <pt idx="7">
-                  <v>3.79</v>
-                </pt>
-                <pt idx="8">
-                  <v>4.02</v>
-                </pt>
-                <pt idx="9">
-                  <v>4.59</v>
-                </pt>
-                <pt idx="10">
-                  <v>4.45</v>
-                </pt>
-                <pt idx="11">
-                  <v>3.94</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'INPC (Inflación)'!$D$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Subyacente</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="9C2348"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="9C2348"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="9C2348"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="9"/>
-            </dLbl>
-            <dLbl>
-              <idx val="10"/>
-            </dLbl>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="9C2348"/>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>'INPC (Inflación)'!$B$10:$B$21</f>
-              <strCache>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="3">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="4">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="5">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="6">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="7">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="8">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="9">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="10">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="11">
-                  <v>May 26</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'INPC (Inflación)'!$D$10:$D$21</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>4.24</v>
-                </pt>
-                <pt idx="1">
-                  <v>4.23</v>
-                </pt>
-                <pt idx="2">
-                  <v>4.23</v>
-                </pt>
-                <pt idx="3">
-                  <v>4.28</v>
-                </pt>
-                <pt idx="4">
-                  <v>4.28</v>
-                </pt>
-                <pt idx="5">
-                  <v>4.43</v>
-                </pt>
-                <pt idx="6">
-                  <v>4.33</v>
-                </pt>
-                <pt idx="7">
-                  <v>4.52</v>
-                </pt>
-                <pt idx="8">
-                  <v>4.5</v>
-                </pt>
-                <pt idx="9">
-                  <v>4.45</v>
-                </pt>
-                <pt idx="10">
-                  <v>4.26</v>
-                </pt>
-                <pt idx="11">
-                  <v>4.19</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'INPC (Inflación)'!$E$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>No subyacente</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="A6802D"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="A6802D"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="A6802D"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <dLblPos val="l"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="8"/>
-              <dLblPos val="l"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="10"/>
-              <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="A6802D"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="t"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="11"/>
-              <dLblPos val="b"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="A6802D"/>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>'INPC (Inflación)'!$B$10:$B$21</f>
-              <strCache>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="3">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="4">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="5">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="6">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="7">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="8">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="9">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="10">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="11">
-                  <v>May 26</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'INPC (Inflación)'!$E$10:$E$21</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>4.33</v>
-                </pt>
-                <pt idx="1">
-                  <v>1.14</v>
-                </pt>
-                <pt idx="2">
-                  <v>1.38</v>
-                </pt>
-                <pt idx="3">
-                  <v>2.02</v>
-                </pt>
-                <pt idx="4">
-                  <v>1.18</v>
-                </pt>
-                <pt idx="5">
-                  <v>1.73</v>
-                </pt>
-                <pt idx="6">
-                  <v>1.61</v>
-                </pt>
-                <pt idx="7">
-                  <v>1.39</v>
-                </pt>
-                <pt idx="8">
-                  <v>2.44</v>
-                </pt>
-                <pt idx="9">
-                  <v>5.05</v>
-                </pt>
-                <pt idx="10">
-                  <v>5.08</v>
-                </pt>
-                <pt idx="11">
-                  <v>3.1</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <ser>
-          <idx val="3"/>
-          <order val="3"/>
-          <tx>
-            <strRef>
-              <f>'INPC (Inflación)'!$F$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Banxico</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="circle"/>
-            <size val="5"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="0070C0"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
-                <a:solidFill>
-                  <a:srgbClr val="0070C0"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLbl>
-              <idx val="0"/>
-              <dLblPos val="t"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </txPr>
-            <showLegendKey val="0"/>
-            <showVal val="0"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>'INPC (Inflación)'!$B$10:$B$21</f>
-              <strCache>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="2">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="3">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="4">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="5">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="6">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="7">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="8">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="9">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="10">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="11">
-                  <v>May 26</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'INPC (Inflación)'!$F$10:$F$21</f>
-              <numCache>
-                <formatCode>General</formatCode>
-                <ptCount val="12"/>
-                <pt idx="0">
-                  <v>3</v>
-                </pt>
-                <pt idx="1">
-                  <v>3</v>
-                </pt>
-                <pt idx="2">
-                  <v>3</v>
-                </pt>
-                <pt idx="3">
-                  <v>3</v>
-                </pt>
-                <pt idx="4">
-                  <v>3</v>
-                </pt>
-                <pt idx="5">
-                  <v>3</v>
-                </pt>
-                <pt idx="6">
-                  <v>3</v>
-                </pt>
-                <pt idx="7">
-                  <v>3</v>
-                </pt>
-                <pt idx="8">
-                  <v>3</v>
-                </pt>
-                <pt idx="9">
-                  <v>3</v>
-                </pt>
-                <pt idx="10">
-                  <v>3</v>
-                </pt>
-                <pt idx="11">
-                  <v>3</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <marker val="1"/>
-        <smooth val="0"/>
-        <axId val="1771803888"/>
-        <axId val="1771804720"/>
-      </lineChart>
-      <catAx>
-        <axId val="1771803888"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="1771804720"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="1771804720"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="5.5"/>
-          <min val="0"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="1771803888"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="t"/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:r>
@@ -5519,1746 +4456,6 @@
           <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
           <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-MX"/>
-              <a:t>Exportaciones 2024</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="es-MX" baseline="0"/>
-              <a:t xml:space="preserve"> - 2026, millones de dólares</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="es-MX"/>
-              <a:t> </a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <layout/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>Exportaciones!$C$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Exportaciones</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1E5B4F"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:solidFill>
-                <a:srgbClr val="1E5B4F"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <strRef>
-              <f>Exportaciones!$B$10:$B$34</f>
-              <strCache>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>May 24</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jun 24</v>
-                </pt>
-                <pt idx="2">
-                  <v>Jul 24</v>
-                </pt>
-                <pt idx="3">
-                  <v>Ago 24</v>
-                </pt>
-                <pt idx="4">
-                  <v>Sep 24</v>
-                </pt>
-                <pt idx="5">
-                  <v>Oct 24</v>
-                </pt>
-                <pt idx="6">
-                  <v>Nov 24</v>
-                </pt>
-                <pt idx="7">
-                  <v>Dic 24</v>
-                </pt>
-                <pt idx="8">
-                  <v>Ene 25</v>
-                </pt>
-                <pt idx="9">
-                  <v>Feb 25</v>
-                </pt>
-                <pt idx="10">
-                  <v>Mar 25</v>
-                </pt>
-                <pt idx="11">
-                  <v>Abr 25</v>
-                </pt>
-                <pt idx="12">
-                  <v>May 25</v>
-                </pt>
-                <pt idx="13">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="14">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="15">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="16">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="17">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="18">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="19">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="20">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="21">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="22">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="23">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="24">
-                  <v>May 26 O</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Exportaciones!$C$10:$C$34</f>
-              <numCache>
-                <formatCode>_-"$"* #,##0_-;\-"$"* #,##0_-;_-"$"* "-"??_-;_-@_-</formatCode>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>55754.041</v>
-                </pt>
-                <pt idx="1">
-                  <v>48824.268</v>
-                </pt>
-                <pt idx="2">
-                  <v>54550.711</v>
-                </pt>
-                <pt idx="3">
-                  <v>51902.528</v>
-                </pt>
-                <pt idx="4">
-                  <v>49629.743</v>
-                </pt>
-                <pt idx="5">
-                  <v>57897.71</v>
-                </pt>
-                <pt idx="6">
-                  <v>52264.794</v>
-                </pt>
-                <pt idx="7">
-                  <v>51754.359</v>
-                </pt>
-                <pt idx="8">
-                  <v>44398.267</v>
-                </pt>
-                <pt idx="9">
-                  <v>49098.535</v>
-                </pt>
-                <pt idx="10">
-                  <v>55404.972</v>
-                </pt>
-                <pt idx="11">
-                  <v>54347.764</v>
-                </pt>
-                <pt idx="12">
-                  <v>55476.735</v>
-                </pt>
-                <pt idx="13">
-                  <v>54001.827</v>
-                </pt>
-                <pt idx="14">
-                  <v>56707.774</v>
-                </pt>
-                <pt idx="15">
-                  <v>55718.184</v>
-                </pt>
-                <pt idx="16">
-                  <v>56487.938</v>
-                </pt>
-                <pt idx="17">
-                  <v>66132.55100000001</v>
-                </pt>
-                <pt idx="18">
-                  <v>56411.894</v>
-                </pt>
-                <pt idx="19">
-                  <v>60650.727</v>
-                </pt>
-                <pt idx="20">
-                  <v>48007.823</v>
-                </pt>
-                <pt idx="21">
-                  <v>56851.119</v>
-                </pt>
-                <pt idx="22">
-                  <v>70727.019</v>
-                </pt>
-                <pt idx="23">
-                  <v>72041.829</v>
-                </pt>
-                <pt idx="24">
-                  <v>69544.49099999999</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="100"/>
-        <overlap val="-27"/>
-        <axId val="477923072"/>
-        <axId val="477921280"/>
-      </barChart>
-      <lineChart>
-        <grouping val="standard"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>Exportaciones!$D$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v xml:space="preserve">Var. Anual </v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="38100" cap="rnd">
-              <a:solidFill>
-                <a:srgbClr val="A6802D"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <dLbls>
-            <dLbl>
-              <idx val="14"/>
-              <dLblPos val="b"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="15"/>
-              <dLblPos val="r"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="18"/>
-              <dLblPos val="b"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="20"/>
-              <dLblPos val="b"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="21"/>
-              <dLblPos val="r"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="24"/>
-              <dLblPos val="b"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="A6802D"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="t"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <cat>
-            <strRef>
-              <f>Exportaciones!$B$10:$B$34</f>
-              <strCache>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>May 24</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jun 24</v>
-                </pt>
-                <pt idx="2">
-                  <v>Jul 24</v>
-                </pt>
-                <pt idx="3">
-                  <v>Ago 24</v>
-                </pt>
-                <pt idx="4">
-                  <v>Sep 24</v>
-                </pt>
-                <pt idx="5">
-                  <v>Oct 24</v>
-                </pt>
-                <pt idx="6">
-                  <v>Nov 24</v>
-                </pt>
-                <pt idx="7">
-                  <v>Dic 24</v>
-                </pt>
-                <pt idx="8">
-                  <v>Ene 25</v>
-                </pt>
-                <pt idx="9">
-                  <v>Feb 25</v>
-                </pt>
-                <pt idx="10">
-                  <v>Mar 25</v>
-                </pt>
-                <pt idx="11">
-                  <v>Abr 25</v>
-                </pt>
-                <pt idx="12">
-                  <v>May 25</v>
-                </pt>
-                <pt idx="13">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="14">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="15">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="16">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="17">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="18">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="19">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="20">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="21">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="22">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="23">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="24">
-                  <v>May 26 O</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>Exportaciones!$D$10:$D$34</f>
-              <numCache>
-                <formatCode>0.0%</formatCode>
-                <ptCount val="25"/>
-                <pt idx="13">
-                  <v>0.1060447849417836</v>
-                </pt>
-                <pt idx="14">
-                  <v>0.03954234437017679</v>
-                </pt>
-                <pt idx="15">
-                  <v>0.07351580254433854</v>
-                </pt>
-                <pt idx="16">
-                  <v>0.1381871955291003</v>
-                </pt>
-                <pt idx="17">
-                  <v>0.1422308585261836</v>
-                </pt>
-                <pt idx="18">
-                  <v>0.0793478684714608</v>
-                </pt>
-                <pt idx="19">
-                  <v>0.1718960136285332</v>
-                </pt>
-                <pt idx="20">
-                  <v>0.08129947954950567</v>
-                </pt>
-                <pt idx="21">
-                  <v>0.1578984790483056</v>
-                </pt>
-                <pt idx="22">
-                  <v>0.2765464261943855</v>
-                </pt>
-                <pt idx="23">
-                  <v>0.3255711679325022</v>
-                </pt>
-                <pt idx="24">
-                  <v>0.2535793788152816</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <marker val="1"/>
-        <smooth val="0"/>
-        <axId val="477931584"/>
-        <axId val="477932032"/>
-      </lineChart>
-      <catAx>
-        <axId val="477923072"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="477921280"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="477921280"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <numFmt formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="477923072"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-      <catAx>
-        <axId val="477931584"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="1"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <crossAx val="477932032"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="477932032"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="r"/>
-        <numFmt formatCode="0.0%" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="477931584"/>
-        <crosses val="max"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="t"/>
-      <layout/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-MX" b="1"/>
-              <a:t xml:space="preserve">Exportaciones e importaciones de México (valores absolutos, mdd) </a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-      <layout/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="1400" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </txPr>
-    </title>
-    <plotArea>
-      <layout/>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <varyColors val="0"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Balanza comercial'!$C$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Exportaciones</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="9C2348"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <dLbls>
-            <dLbl>
-              <idx val="1"/>
-              <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="1E5B4F"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="outEnd"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="2"/>
-              <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="1E5B4F"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="outEnd"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="3"/>
-              <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="1E5B4F"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="outEnd"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="7"/>
-              <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="1E5B4F"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="outEnd"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <dLbl>
-              <idx val="8"/>
-              <spPr>
-                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:noFill/>
-                  <a:prstDash val="solid"/>
-                </a:ln>
-              </spPr>
-              <txPr>
-                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                  <a:spAutoFit/>
-                </a:bodyPr>
-                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                  <a:pPr>
-                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
-                      <a:solidFill>
-                        <a:srgbClr val="1E5B4F"/>
-                      </a:solidFill>
-                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    </a:defRPr>
-                  </a:pPr>
-                  <a:r>
-                    <a:t/>
-                  </a:r>
-                  <a:endParaRPr lang="es-MX"/>
-                </a:p>
-              </txPr>
-              <dLblPos val="outEnd"/>
-              <showLegendKey val="0"/>
-              <showVal val="1"/>
-              <showCatName val="0"/>
-              <showSerName val="0"/>
-              <showPercent val="0"/>
-              <showBubbleSize val="0"/>
-            </dLbl>
-            <spPr>
-              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:noFill/>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-            <txPr>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:t/>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </txPr>
-            <dLblPos val="outEnd"/>
-            <showLegendKey val="0"/>
-            <showVal val="1"/>
-            <showCatName val="0"/>
-            <showSerName val="0"/>
-            <showPercent val="0"/>
-            <showBubbleSize val="0"/>
-            <showLeaderLines val="0"/>
-          </dLbls>
-          <trendline>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050" cap="rnd">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-            </spPr>
-            <trendlineType val="linear"/>
-            <dispRSqr val="0"/>
-            <dispEq val="0"/>
-          </trendline>
-          <cat>
-            <strRef>
-              <f>'Balanza comercial'!$B$10:$B$34</f>
-              <strCache>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>May 24</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jun 24</v>
-                </pt>
-                <pt idx="2">
-                  <v>Jul 24</v>
-                </pt>
-                <pt idx="3">
-                  <v>Ago 24</v>
-                </pt>
-                <pt idx="4">
-                  <v>Sep 24</v>
-                </pt>
-                <pt idx="5">
-                  <v>Oct 24</v>
-                </pt>
-                <pt idx="6">
-                  <v>Nov 24</v>
-                </pt>
-                <pt idx="7">
-                  <v>Dic 24</v>
-                </pt>
-                <pt idx="8">
-                  <v>Ene 25</v>
-                </pt>
-                <pt idx="9">
-                  <v>Feb 25</v>
-                </pt>
-                <pt idx="10">
-                  <v>Mar 25</v>
-                </pt>
-                <pt idx="11">
-                  <v>Abr 25</v>
-                </pt>
-                <pt idx="12">
-                  <v>May 25</v>
-                </pt>
-                <pt idx="13">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="14">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="15">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="16">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="17">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="18">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="19">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="20">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="21">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="22">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="23">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="24">
-                  <v>May 26 O</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Balanza comercial'!$C$10:$C$34</f>
-              <numCache>
-                <formatCode>_-"$"* #,##0_-;\-"$"* #,##0_-;_-"$"* "-"??_-;_-@_-</formatCode>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>55754.041</v>
-                </pt>
-                <pt idx="1">
-                  <v>48824.268</v>
-                </pt>
-                <pt idx="2">
-                  <v>54550.711</v>
-                </pt>
-                <pt idx="3">
-                  <v>51902.528</v>
-                </pt>
-                <pt idx="4">
-                  <v>49629.743</v>
-                </pt>
-                <pt idx="5">
-                  <v>57897.71</v>
-                </pt>
-                <pt idx="6">
-                  <v>52264.794</v>
-                </pt>
-                <pt idx="7">
-                  <v>51754.359</v>
-                </pt>
-                <pt idx="8">
-                  <v>44398.267</v>
-                </pt>
-                <pt idx="9">
-                  <v>49098.535</v>
-                </pt>
-                <pt idx="10">
-                  <v>55404.972</v>
-                </pt>
-                <pt idx="11">
-                  <v>54347.764</v>
-                </pt>
-                <pt idx="12">
-                  <v>55476.735</v>
-                </pt>
-                <pt idx="13">
-                  <v>54001.827</v>
-                </pt>
-                <pt idx="14">
-                  <v>56707.774</v>
-                </pt>
-                <pt idx="15">
-                  <v>55718.184</v>
-                </pt>
-                <pt idx="16">
-                  <v>56487.938</v>
-                </pt>
-                <pt idx="17">
-                  <v>66132.55100000001</v>
-                </pt>
-                <pt idx="18">
-                  <v>56411.894</v>
-                </pt>
-                <pt idx="19">
-                  <v>60650.727</v>
-                </pt>
-                <pt idx="20">
-                  <v>48007.823</v>
-                </pt>
-                <pt idx="21">
-                  <v>56851.119</v>
-                </pt>
-                <pt idx="22">
-                  <v>70727.019</v>
-                </pt>
-                <pt idx="23">
-                  <v>72041.829</v>
-                </pt>
-                <pt idx="24">
-                  <v>69544.49099999999</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'Balanza comercial'!$E$9</f>
-              <strCache>
-                <ptCount val="1"/>
-                <pt idx="0">
-                  <v>Importaciones</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1E5B4F"/>
-            </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <invertIfNegative val="0"/>
-          <cat>
-            <strRef>
-              <f>'Balanza comercial'!$B$10:$B$34</f>
-              <strCache>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>May 24</v>
-                </pt>
-                <pt idx="1">
-                  <v>Jun 24</v>
-                </pt>
-                <pt idx="2">
-                  <v>Jul 24</v>
-                </pt>
-                <pt idx="3">
-                  <v>Ago 24</v>
-                </pt>
-                <pt idx="4">
-                  <v>Sep 24</v>
-                </pt>
-                <pt idx="5">
-                  <v>Oct 24</v>
-                </pt>
-                <pt idx="6">
-                  <v>Nov 24</v>
-                </pt>
-                <pt idx="7">
-                  <v>Dic 24</v>
-                </pt>
-                <pt idx="8">
-                  <v>Ene 25</v>
-                </pt>
-                <pt idx="9">
-                  <v>Feb 25</v>
-                </pt>
-                <pt idx="10">
-                  <v>Mar 25</v>
-                </pt>
-                <pt idx="11">
-                  <v>Abr 25</v>
-                </pt>
-                <pt idx="12">
-                  <v>May 25</v>
-                </pt>
-                <pt idx="13">
-                  <v>Jun 25</v>
-                </pt>
-                <pt idx="14">
-                  <v>Jul 25</v>
-                </pt>
-                <pt idx="15">
-                  <v>Ago 25</v>
-                </pt>
-                <pt idx="16">
-                  <v>Sep 25</v>
-                </pt>
-                <pt idx="17">
-                  <v>Oct 25</v>
-                </pt>
-                <pt idx="18">
-                  <v>Nov 25</v>
-                </pt>
-                <pt idx="19">
-                  <v>Dic 25</v>
-                </pt>
-                <pt idx="20">
-                  <v>Ene 26</v>
-                </pt>
-                <pt idx="21">
-                  <v>Feb 26</v>
-                </pt>
-                <pt idx="22">
-                  <v>Mar 26</v>
-                </pt>
-                <pt idx="23">
-                  <v>Abr 26</v>
-                </pt>
-                <pt idx="24">
-                  <v>May 26 O</v>
-                </pt>
-              </strCache>
-            </strRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Balanza comercial'!$E$10:$E$34</f>
-              <numCache>
-                <formatCode>_-"$"* #,##0_-;\-"$"* #,##0_-;_-"$"* "-"??_-;_-@_-</formatCode>
-                <ptCount val="25"/>
-                <pt idx="0">
-                  <v>54863.065</v>
-                </pt>
-                <pt idx="1">
-                  <v>51230.591</v>
-                </pt>
-                <pt idx="2">
-                  <v>55771.222</v>
-                </pt>
-                <pt idx="3">
-                  <v>57747.196</v>
-                </pt>
-                <pt idx="4">
-                  <v>51120.789</v>
-                </pt>
-                <pt idx="5">
-                  <v>58109.034</v>
-                </pt>
-                <pt idx="6">
-                  <v>52971.031</v>
-                </pt>
-                <pt idx="7">
-                  <v>49905.838</v>
-                </pt>
-                <pt idx="8">
-                  <v>49611.476</v>
-                </pt>
-                <pt idx="9">
-                  <v>47444.307</v>
-                </pt>
-                <pt idx="10">
-                  <v>52115.201</v>
-                </pt>
-                <pt idx="11">
-                  <v>54392.226</v>
-                </pt>
-                <pt idx="12">
-                  <v>54244.911</v>
-                </pt>
-                <pt idx="13">
-                  <v>53487.398</v>
-                </pt>
-                <pt idx="14">
-                  <v>56724.468</v>
-                </pt>
-                <pt idx="15">
-                  <v>57662.068</v>
-                </pt>
-                <pt idx="16">
-                  <v>58887.475</v>
-                </pt>
-                <pt idx="17">
-                  <v>65526.483</v>
-                </pt>
-                <pt idx="18">
-                  <v>55749.102</v>
-                </pt>
-                <pt idx="19">
-                  <v>58221.107</v>
-                </pt>
-                <pt idx="20">
-                  <v>54488.877</v>
-                </pt>
-                <pt idx="21">
-                  <v>57313.897</v>
-                </pt>
-                <pt idx="22">
-                  <v>64795.021</v>
-                </pt>
-                <pt idx="23">
-                  <v>67521.798</v>
-                </pt>
-                <pt idx="24">
-                  <v>67285.323</v>
-                </pt>
-              </numCache>
-            </numRef>
-          </val>
-        </ser>
-        <dLbls>
-          <showLegendKey val="0"/>
-          <showVal val="0"/>
-          <showCatName val="0"/>
-          <showSerName val="0"/>
-          <showPercent val="0"/>
-          <showBubbleSize val="0"/>
-        </dLbls>
-        <gapWidth val="100"/>
-        <overlap val="-27"/>
-        <axId val="1259334848"/>
-        <axId val="1259336096"/>
-      </barChart>
-      <catAx>
-        <axId val="1259334848"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="b"/>
-        <numFmt formatCode="General" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="1259336096"/>
-        <crosses val="autoZero"/>
-        <auto val="1"/>
-        <lblAlgn val="ctr"/>
-        <lblOffset val="100"/>
-        <noMultiLvlLbl val="0"/>
-      </catAx>
-      <valAx>
-        <axId val="1259336096"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-              <a:round/>
-            </a:ln>
-          </spPr>
-        </majorGridlines>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="es-MX"/>
-                  <a:t xml:space="preserve"> Millones</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="es-MX" baseline="0"/>
-                  <a:t xml:space="preserve"> de dólares</a:t>
-                </a:r>
-                <a:endParaRPr lang="es-MX"/>
-              </a:p>
-            </rich>
-          </tx>
-          <layout/>
-          <overlay val="0"/>
-          <spPr>
-            <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <txPr>
-            <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-            <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                  <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:r>
-                <a:t/>
-              </a:r>
-              <a:endParaRPr lang="es-MX"/>
-            </a:p>
-          </txPr>
-        </title>
-        <numFmt formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <tickLblPos val="nextTo"/>
-        <spPr>
-          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:noFill/>
-            <a:prstDash val="solid"/>
-          </a:ln>
-        </spPr>
-        <txPr>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr lang="es-MX"/>
-          </a:p>
-        </txPr>
-        <crossAx val="1259334848"/>
-        <crosses val="autoZero"/>
-        <crossBetween val="between"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="t"/>
-      <layout/>
-      <overlay val="0"/>
-      <spPr>
-        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:noFill/>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-      <txPr>
-        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-              <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:r>
-            <a:t/>
-          </a:r>
-          <a:endParaRPr lang="es-MX"/>
-        </a:p>
-      </txPr>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-  <spPr>
-    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:prstDash val="solid"/>
-      <a:round/>
-    </a:ln>
-  </spPr>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
               <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
@@ -7854,7 +5051,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -8856,7 +6053,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
@@ -9624,6 +6821,1076 @@
 </chartSpace>
 </file>
 
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="es-MX" sz="1600" b="1"/>
+              <a:t xml:space="preserve">Inflación (porcentual) </a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </txPr>
+    </title>
+    <plotArea>
+      <layout/>
+      <lineChart>
+        <grouping val="standard"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'INPC (Inflación)'!$C$9</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Inflación</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="1E5B4F"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="1E5B4F"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="1E5B4F"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="9"/>
+              <spPr>
+                <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:sysClr val="window" lastClr="FFFFFF"/>
+                </a:solidFill>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumOff val="75000"/>
+                      <a:lumMod val="25000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="dk1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr lang="es-MX"/>
+                </a:p>
+              </txPr>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="11"/>
+              <dLblPos val="b"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="1E5B4F"/>
+                    </a:solidFill>
+                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+            <showLeaderLines val="0"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>'INPC (Inflación)'!$B$10:$B$21</f>
+              <strCache>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>Jun 25</v>
+                </pt>
+                <pt idx="1">
+                  <v>Jul 25</v>
+                </pt>
+                <pt idx="2">
+                  <v>Ago 25</v>
+                </pt>
+                <pt idx="3">
+                  <v>Sep 25</v>
+                </pt>
+                <pt idx="4">
+                  <v>Oct 25</v>
+                </pt>
+                <pt idx="5">
+                  <v>Nov 25</v>
+                </pt>
+                <pt idx="6">
+                  <v>Dic 25</v>
+                </pt>
+                <pt idx="7">
+                  <v>Ene 26</v>
+                </pt>
+                <pt idx="8">
+                  <v>Feb 26</v>
+                </pt>
+                <pt idx="9">
+                  <v>Mar 26</v>
+                </pt>
+                <pt idx="10">
+                  <v>Abr 26</v>
+                </pt>
+                <pt idx="11">
+                  <v>May 26</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'INPC (Inflación)'!$C$10:$C$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>4.32</v>
+                </pt>
+                <pt idx="1">
+                  <v>3.51</v>
+                </pt>
+                <pt idx="2">
+                  <v>3.57</v>
+                </pt>
+                <pt idx="3">
+                  <v>3.76</v>
+                </pt>
+                <pt idx="4">
+                  <v>3.57</v>
+                </pt>
+                <pt idx="5">
+                  <v>3.8</v>
+                </pt>
+                <pt idx="6">
+                  <v>3.69</v>
+                </pt>
+                <pt idx="7">
+                  <v>3.79</v>
+                </pt>
+                <pt idx="8">
+                  <v>4.02</v>
+                </pt>
+                <pt idx="9">
+                  <v>4.59</v>
+                </pt>
+                <pt idx="10">
+                  <v>4.45</v>
+                </pt>
+                <pt idx="11">
+                  <v>3.94</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'INPC (Inflación)'!$D$9</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Subyacente</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="9C2348"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="9C2348"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="9C2348"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="9"/>
+            </dLbl>
+            <dLbl>
+              <idx val="10"/>
+            </dLbl>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="9C2348"/>
+                    </a:solidFill>
+                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+            <showLeaderLines val="0"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>'INPC (Inflación)'!$B$10:$B$21</f>
+              <strCache>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>Jun 25</v>
+                </pt>
+                <pt idx="1">
+                  <v>Jul 25</v>
+                </pt>
+                <pt idx="2">
+                  <v>Ago 25</v>
+                </pt>
+                <pt idx="3">
+                  <v>Sep 25</v>
+                </pt>
+                <pt idx="4">
+                  <v>Oct 25</v>
+                </pt>
+                <pt idx="5">
+                  <v>Nov 25</v>
+                </pt>
+                <pt idx="6">
+                  <v>Dic 25</v>
+                </pt>
+                <pt idx="7">
+                  <v>Ene 26</v>
+                </pt>
+                <pt idx="8">
+                  <v>Feb 26</v>
+                </pt>
+                <pt idx="9">
+                  <v>Mar 26</v>
+                </pt>
+                <pt idx="10">
+                  <v>Abr 26</v>
+                </pt>
+                <pt idx="11">
+                  <v>May 26</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'INPC (Inflación)'!$D$10:$D$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>4.24</v>
+                </pt>
+                <pt idx="1">
+                  <v>4.23</v>
+                </pt>
+                <pt idx="2">
+                  <v>4.23</v>
+                </pt>
+                <pt idx="3">
+                  <v>4.28</v>
+                </pt>
+                <pt idx="4">
+                  <v>4.28</v>
+                </pt>
+                <pt idx="5">
+                  <v>4.43</v>
+                </pt>
+                <pt idx="6">
+                  <v>4.33</v>
+                </pt>
+                <pt idx="7">
+                  <v>4.52</v>
+                </pt>
+                <pt idx="8">
+                  <v>4.5</v>
+                </pt>
+                <pt idx="9">
+                  <v>4.45</v>
+                </pt>
+                <pt idx="10">
+                  <v>4.26</v>
+                </pt>
+                <pt idx="11">
+                  <v>4.19</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'INPC (Inflación)'!$E$9</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>No subyacente</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="A6802D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="A6802D"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="A6802D"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="8"/>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="10"/>
+              <spPr>
+                <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:noFill/>
+                  <a:prstDash val="solid"/>
+                </a:ln>
+              </spPr>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                  <a:spAutoFit/>
+                </a:bodyPr>
+                <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:srgbClr val="A6802D"/>
+                      </a:solidFill>
+                      <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                      <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                      <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr lang="es-MX"/>
+                </a:p>
+              </txPr>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <dLbl>
+              <idx val="11"/>
+              <dLblPos val="b"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="A6802D"/>
+                    </a:solidFill>
+                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </txPr>
+            <dLblPos val="t"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+            <showLeaderLines val="0"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>'INPC (Inflación)'!$B$10:$B$21</f>
+              <strCache>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>Jun 25</v>
+                </pt>
+                <pt idx="1">
+                  <v>Jul 25</v>
+                </pt>
+                <pt idx="2">
+                  <v>Ago 25</v>
+                </pt>
+                <pt idx="3">
+                  <v>Sep 25</v>
+                </pt>
+                <pt idx="4">
+                  <v>Oct 25</v>
+                </pt>
+                <pt idx="5">
+                  <v>Nov 25</v>
+                </pt>
+                <pt idx="6">
+                  <v>Dic 25</v>
+                </pt>
+                <pt idx="7">
+                  <v>Ene 26</v>
+                </pt>
+                <pt idx="8">
+                  <v>Feb 26</v>
+                </pt>
+                <pt idx="9">
+                  <v>Mar 26</v>
+                </pt>
+                <pt idx="10">
+                  <v>Abr 26</v>
+                </pt>
+                <pt idx="11">
+                  <v>May 26</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'INPC (Inflación)'!$E$10:$E$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>4.33</v>
+                </pt>
+                <pt idx="1">
+                  <v>1.14</v>
+                </pt>
+                <pt idx="2">
+                  <v>1.38</v>
+                </pt>
+                <pt idx="3">
+                  <v>2.02</v>
+                </pt>
+                <pt idx="4">
+                  <v>1.18</v>
+                </pt>
+                <pt idx="5">
+                  <v>1.73</v>
+                </pt>
+                <pt idx="6">
+                  <v>1.61</v>
+                </pt>
+                <pt idx="7">
+                  <v>1.39</v>
+                </pt>
+                <pt idx="8">
+                  <v>2.44</v>
+                </pt>
+                <pt idx="9">
+                  <v>5.05</v>
+                </pt>
+                <pt idx="10">
+                  <v>5.08</v>
+                </pt>
+                <pt idx="11">
+                  <v>3.1</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'INPC (Inflación)'!$F$9</f>
+              <strCache>
+                <ptCount val="1"/>
+                <pt idx="0">
+                  <v>Banxico</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="28575" cap="rnd">
+              <a:solidFill>
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="circle"/>
+            <size val="5"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="0070C0"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+                <a:solidFill>
+                  <a:srgbClr val="0070C0"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="0"/>
+              <dLblPos val="t"/>
+              <showLegendKey val="0"/>
+              <showVal val="1"/>
+              <showCatName val="0"/>
+              <showSerName val="0"/>
+              <showPercent val="0"/>
+              <showBubbleSize val="0"/>
+            </dLbl>
+            <spPr>
+              <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:noFill/>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+            <txPr>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:t/>
+                </a:r>
+                <a:endParaRPr lang="es-MX"/>
+              </a:p>
+            </txPr>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+            <showBubbleSize val="0"/>
+          </dLbls>
+          <cat>
+            <strRef>
+              <f>'INPC (Inflación)'!$B$10:$B$21</f>
+              <strCache>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>Jun 25</v>
+                </pt>
+                <pt idx="1">
+                  <v>Jul 25</v>
+                </pt>
+                <pt idx="2">
+                  <v>Ago 25</v>
+                </pt>
+                <pt idx="3">
+                  <v>Sep 25</v>
+                </pt>
+                <pt idx="4">
+                  <v>Oct 25</v>
+                </pt>
+                <pt idx="5">
+                  <v>Nov 25</v>
+                </pt>
+                <pt idx="6">
+                  <v>Dic 25</v>
+                </pt>
+                <pt idx="7">
+                  <v>Ene 26</v>
+                </pt>
+                <pt idx="8">
+                  <v>Feb 26</v>
+                </pt>
+                <pt idx="9">
+                  <v>Mar 26</v>
+                </pt>
+                <pt idx="10">
+                  <v>Abr 26</v>
+                </pt>
+                <pt idx="11">
+                  <v>May 26</v>
+                </pt>
+              </strCache>
+            </strRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'INPC (Inflación)'!$F$10:$F$21</f>
+              <numCache>
+                <formatCode>General</formatCode>
+                <ptCount val="12"/>
+                <pt idx="0">
+                  <v>3</v>
+                </pt>
+                <pt idx="1">
+                  <v>3</v>
+                </pt>
+                <pt idx="2">
+                  <v>3</v>
+                </pt>
+                <pt idx="3">
+                  <v>3</v>
+                </pt>
+                <pt idx="4">
+                  <v>3</v>
+                </pt>
+                <pt idx="5">
+                  <v>3</v>
+                </pt>
+                <pt idx="6">
+                  <v>3</v>
+                </pt>
+                <pt idx="7">
+                  <v>3</v>
+                </pt>
+                <pt idx="8">
+                  <v>3</v>
+                </pt>
+                <pt idx="9">
+                  <v>3</v>
+                </pt>
+                <pt idx="10">
+                  <v>3</v>
+                </pt>
+                <pt idx="11">
+                  <v>3</v>
+                </pt>
+              </numCache>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
+        </dLbls>
+        <marker val="1"/>
+        <smooth val="0"/>
+        <axId val="1771803888"/>
+        <axId val="1771804720"/>
+      </lineChart>
+      <catAx>
+        <axId val="1771803888"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </txPr>
+        <crossAx val="1771804720"/>
+        <crosses val="autoZero"/>
+        <auto val="1"/>
+        <lblAlgn val="ctr"/>
+        <lblOffset val="100"/>
+        <noMultiLvlLbl val="0"/>
+      </catAx>
+      <valAx>
+        <axId val="1771804720"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="5.5"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+              <a:round/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
+        <numFmt formatCode="General" sourceLinked="1"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <spPr>
+          <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:noFill/>
+            <a:prstDash val="solid"/>
+          </a:ln>
+        </spPr>
+        <txPr>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr lang="es-MX"/>
+          </a:p>
+        </txPr>
+        <crossAx val="1771803888"/>
+        <crosses val="autoZero"/>
+        <crossBetween val="between"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="t"/>
+      <overlay val="0"/>
+      <spPr>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+      <txPr>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Noto Sans" panose="020B0502040504020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr lang="es-MX"/>
+        </a:p>
+      </txPr>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+  <spPr>
+    <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+      <a:round/>
+    </a:ln>
+  </spPr>
+</chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
@@ -9638,38 +7905,6 @@
       <colOff>9524</colOff>
       <row>33</row>
       <rowOff>0</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>7</col>
-      <colOff>4762</colOff>
-      <row>7</row>
-      <rowOff>247649</rowOff>
-    </from>
-    <to>
-      <col>17</col>
-      <colOff>742950</colOff>
-      <row>29</row>
-      <rowOff>190499</rowOff>
     </to>
     <graphicFrame>
       <nvGraphicFramePr>
@@ -9788,70 +8023,6 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
-      <col>4</col>
-      <colOff>430893</colOff>
-      <row>8</row>
-      <rowOff>379185</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>181428</colOff>
-      <row>34</row>
-      <rowOff>9071</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>380999</colOff>
-      <row>8</row>
-      <rowOff>9524</rowOff>
-    </from>
-    <to>
-      <col>17</col>
-      <colOff>752474</colOff>
-      <row>29</row>
-      <rowOff>180974</rowOff>
-    </to>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </twoCellAnchor>
-</wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <twoCellAnchor>
-    <from>
       <col>5</col>
       <colOff>4761</colOff>
       <row>8</row>
@@ -9880,7 +8051,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
@@ -9912,7 +8083,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor>
     <from>
@@ -9926,6 +8097,38 @@
       <colOff>761999</colOff>
       <row>33</row>
       <rowOff>85725</rowOff>
+    </to>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor>
+    <from>
+      <col>7</col>
+      <colOff>4762</colOff>
+      <row>7</row>
+      <rowOff>247649</rowOff>
+    </from>
+    <to>
+      <col>17</col>
+      <colOff>742950</colOff>
+      <row>29</row>
+      <rowOff>190499</rowOff>
     </to>
     <graphicFrame>
       <nvGraphicFramePr>
@@ -10224,7 +8427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -10246,7 +8449,7 @@
     <row r="2">
       <c r="A2" s="62" t="inlineStr">
         <is>
-          <t>Generado: 10/08/2026 18:31 UTC</t>
+          <t>Generado: 11/08/2026 03:06 UTC</t>
         </is>
       </c>
     </row>
@@ -10438,7 +8641,7 @@
     <row r="9">
       <c r="A9" s="64" t="inlineStr">
         <is>
-          <t>Balanza comercial</t>
+          <t>Balanza Comercial de Mercancías de México</t>
         </is>
       </c>
       <c r="B9" s="64" t="inlineStr">
@@ -10749,17 +8952,17 @@
       </c>
       <c r="D17" s="64" t="inlineStr">
         <is>
-          <t>Ago 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="E17" s="64" t="inlineStr">
         <is>
-          <t>$17.14</t>
+          <t>$17.33</t>
         </is>
       </c>
       <c r="F17" s="64" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-0.8%</t>
         </is>
       </c>
       <c r="G17" s="64" t="inlineStr">
@@ -10786,7 +8989,7 @@
       </c>
       <c r="D18" s="65" t="inlineStr">
         <is>
-          <t>Ago 26</t>
+          <t>Jul 26</t>
         </is>
       </c>
       <c r="E18" s="65" t="inlineStr">
@@ -10845,7 +9048,7 @@
     <row r="20">
       <c r="A20" s="65" t="inlineStr">
         <is>
-          <t>Encuesta Mensual de Opinión Empresarial</t>
+          <t>Confianza empresarial (EMOE)</t>
         </is>
       </c>
       <c r="B20" s="65" t="inlineStr">
@@ -10858,863 +9061,44 @@
           <t>Mensual</t>
         </is>
       </c>
-      <c r="D20" s="65" t="n"/>
-      <c r="E20" s="65" t="n"/>
-      <c r="F20" s="65" t="n"/>
+      <c r="D20" s="65" t="inlineStr">
+        <is>
+          <t>Jul 26</t>
+        </is>
+      </c>
+      <c r="E20" s="65" t="inlineStr">
+        <is>
+          <t>48.2</t>
+        </is>
+      </c>
+      <c r="F20" s="65" t="inlineStr">
+        <is>
+          <t>+0.1</t>
+        </is>
+      </c>
       <c r="G20" s="65" t="inlineStr">
         <is>
           <t>Puntos</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>Balanza Comercial de Mercancías de México</t>
-        </is>
-      </c>
-      <c r="B21" s="64" t="inlineStr">
-        <is>
-          <t>INEGI</t>
-        </is>
-      </c>
-      <c r="C21" s="64" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="D21" s="64" t="n"/>
-      <c r="E21" s="64" t="n"/>
-      <c r="F21" s="64" t="n"/>
-      <c r="G21" s="64" t="inlineStr">
-        <is>
-          <t>Millones de dólares</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="66" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="66" t="inlineStr">
         <is>
           <t>Nota: cifras oficiales sujetas a revisión. Análisis por reglas deterministas; no se atribuye causalidad. La fuente de la tasa de desocupación es INEGI/ENOE. Los indicadores en estado 'pendiente de token' o 'dato de respaldo' no se presentan como actualización automática (ver 'Control de actualizaciones').</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
+    <row r="23"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A23:G24"/>
+    <mergeCell ref="A22:G23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:R23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col width="5.7109375" customWidth="1" min="1" max="1"/>
-    <col width="17" bestFit="1" customWidth="1" min="2" max="2"/>
-    <col width="13.28515625" customWidth="1" style="5" min="3" max="4"/>
-    <col width="5.7109375" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="20.1" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nombre </t>
-        </is>
-      </c>
-      <c r="C2" s="57" t="inlineStr">
-        <is>
-          <t>Tasa de desocupación nacional</t>
-        </is>
-      </c>
-      <c r="D2" s="67" t="n"/>
-      <c r="E2" s="67" t="n"/>
-      <c r="F2" s="67" t="n"/>
-      <c r="G2" s="67" t="n"/>
-      <c r="H2" s="67" t="n"/>
-      <c r="I2" s="67" t="n"/>
-      <c r="J2" s="67" t="n"/>
-      <c r="K2" s="67" t="n"/>
-      <c r="L2" s="67" t="n"/>
-      <c r="M2" s="67" t="n"/>
-      <c r="N2" s="67" t="n"/>
-      <c r="O2" s="67" t="n"/>
-      <c r="P2" s="68" t="n"/>
-    </row>
-    <row r="3" ht="39.95" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C3" s="69" t="inlineStr">
-        <is>
-          <t>Mide la proporción de la fuerza de trabajo que se encuentra sin empleo pero en búsqueda activa del mismo. Personas desocupadas: son personas de 15 años o más que no trabajaron en la semana de referencia, estaban disponibles para trabajar y realizaron actividades de búsqueda de empleo en las semanas previas.</t>
-        </is>
-      </c>
-      <c r="D3" s="67" t="n"/>
-      <c r="E3" s="67" t="n"/>
-      <c r="F3" s="67" t="n"/>
-      <c r="G3" s="67" t="n"/>
-      <c r="H3" s="67" t="n"/>
-      <c r="I3" s="67" t="n"/>
-      <c r="J3" s="67" t="n"/>
-      <c r="K3" s="67" t="n"/>
-      <c r="L3" s="67" t="n"/>
-      <c r="M3" s="67" t="n"/>
-      <c r="N3" s="67" t="n"/>
-      <c r="O3" s="67" t="n"/>
-      <c r="P3" s="68" t="n"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1">
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Frecuencia</t>
-        </is>
-      </c>
-      <c r="C4" s="57" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="D4" s="67" t="n"/>
-      <c r="E4" s="67" t="n"/>
-      <c r="F4" s="67" t="n"/>
-      <c r="G4" s="67" t="n"/>
-      <c r="H4" s="67" t="n"/>
-      <c r="I4" s="67" t="n"/>
-      <c r="J4" s="67" t="n"/>
-      <c r="K4" s="67" t="n"/>
-      <c r="L4" s="67" t="n"/>
-      <c r="M4" s="67" t="n"/>
-      <c r="N4" s="67" t="n"/>
-      <c r="O4" s="67" t="n"/>
-      <c r="P4" s="68" t="n"/>
-    </row>
-    <row r="5" ht="20.1" customHeight="1">
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Publicación</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="inlineStr">
-        <is>
-          <t>Aproximadamente 25-30 días después de haber concluido el mes</t>
-        </is>
-      </c>
-      <c r="D5" s="67" t="n"/>
-      <c r="E5" s="67" t="n"/>
-      <c r="F5" s="67" t="n"/>
-      <c r="G5" s="67" t="n"/>
-      <c r="H5" s="67" t="n"/>
-      <c r="I5" s="67" t="n"/>
-      <c r="J5" s="67" t="n"/>
-      <c r="K5" s="67" t="n"/>
-      <c r="L5" s="67" t="n"/>
-      <c r="M5" s="67" t="n"/>
-      <c r="N5" s="67" t="n"/>
-      <c r="O5" s="67" t="n"/>
-      <c r="P5" s="67" t="n"/>
-      <c r="Q5" s="67" t="n"/>
-      <c r="R5" s="68" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1">
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>Próximo dato</t>
-        </is>
-      </c>
-      <c r="C6" s="59" t="n"/>
-      <c r="D6" s="70" t="n"/>
-      <c r="E6" s="70" t="n"/>
-      <c r="F6" s="70" t="n"/>
-      <c r="G6" s="70" t="n"/>
-      <c r="H6" s="70" t="n"/>
-      <c r="I6" s="70" t="n"/>
-      <c r="J6" s="70" t="n"/>
-      <c r="K6" s="70" t="n"/>
-      <c r="L6" s="70" t="n"/>
-      <c r="M6" s="70" t="n"/>
-      <c r="N6" s="70" t="n"/>
-      <c r="O6" s="70" t="n"/>
-      <c r="P6" s="74" t="n"/>
-    </row>
-    <row r="7" ht="39.95" customHeight="1">
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="C7" s="56" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> INEGI:
-https://www.oecd.org/es/data/indicators/unemployment-rate.html</t>
-        </is>
-      </c>
-      <c r="D7" s="75" t="n"/>
-      <c r="E7" s="75" t="n"/>
-      <c r="F7" s="75" t="n"/>
-      <c r="G7" s="75" t="n"/>
-      <c r="H7" s="75" t="n"/>
-      <c r="I7" s="75" t="n"/>
-      <c r="J7" s="75" t="n"/>
-      <c r="K7" s="75" t="n"/>
-      <c r="L7" s="75" t="n"/>
-      <c r="M7" s="75" t="n"/>
-      <c r="N7" s="75" t="n"/>
-      <c r="O7" s="75" t="n"/>
-      <c r="P7" s="76" t="n"/>
-    </row>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
-        <is>
-          <t>Periodo</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>Tasa</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>OCDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C10" s="34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>Jul 25</t>
-        </is>
-      </c>
-      <c r="C11" s="34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>Ago 25</t>
-        </is>
-      </c>
-      <c r="C12" s="34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Sep 25</t>
-        </is>
-      </c>
-      <c r="C13" s="34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="C14" s="34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="D14" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Nov 25</t>
-        </is>
-      </c>
-      <c r="C15" s="34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D15" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="16" ht="17.25" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Dic 25</t>
-        </is>
-      </c>
-      <c r="C16" s="34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="D16" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="17" ht="17.25" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>Ene 26</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="D17" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="18" ht="17.25" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>Feb 26</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D18" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="19" ht="17.25" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>Mar 26</t>
-        </is>
-      </c>
-      <c r="C19" s="34" t="n">
-        <v>0.028</v>
-      </c>
-      <c r="D19" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="20" ht="17.25" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>Abr 26</t>
-        </is>
-      </c>
-      <c r="C20" s="34" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="D20" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="21" ht="17.25" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="C21" s="34" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="D21" s="34" t="n">
-        <v>0.049</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>* Cifras oportunas</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C5:R5"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="C4:P4"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="C7:P7"/>
-    <mergeCell ref="C2:P2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="B2:R21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col width="5.7109375" customWidth="1" min="1" max="1"/>
-    <col width="15.7109375" customWidth="1" min="2" max="2"/>
-    <col width="12" bestFit="1" customWidth="1" style="5" min="3" max="3"/>
-    <col width="12" customWidth="1" style="5" min="4" max="4"/>
-    <col width="15" bestFit="1" customWidth="1" style="5" min="5" max="5"/>
-    <col width="8.42578125" bestFit="1" customWidth="1" style="5" min="6" max="6"/>
-    <col width="5.7109375" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="2" ht="20.1" customHeight="1">
-      <c r="B2" s="18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Nombre </t>
-        </is>
-      </c>
-      <c r="C2" s="41" t="inlineStr">
-        <is>
-          <t>Índice Nacional de Precios al Consumidor (INPC)</t>
-        </is>
-      </c>
-      <c r="D2" s="67" t="n"/>
-      <c r="E2" s="67" t="n"/>
-      <c r="F2" s="67" t="n"/>
-      <c r="G2" s="67" t="n"/>
-      <c r="H2" s="67" t="n"/>
-      <c r="I2" s="67" t="n"/>
-      <c r="J2" s="67" t="n"/>
-      <c r="K2" s="67" t="n"/>
-      <c r="L2" s="67" t="n"/>
-      <c r="M2" s="67" t="n"/>
-      <c r="N2" s="67" t="n"/>
-      <c r="O2" s="67" t="n"/>
-      <c r="P2" s="67" t="n"/>
-      <c r="Q2" s="67" t="n"/>
-      <c r="R2" s="68" t="n"/>
-    </row>
-    <row r="3" ht="39.95" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
-        <is>
-          <t>Descripción</t>
-        </is>
-      </c>
-      <c r="C3" s="47" t="inlineStr">
-        <is>
-          <t>Mide la trayectoria agregada de los precios de una canasta de bienes y servicios representativa del consumo de las familias mexicanas. Su objetivo principal es cuantificar la inflación, definida como el aumento sostenido y generalizado de los precios a lo largo del tiempo.</t>
-        </is>
-      </c>
-      <c r="D3" s="67" t="n"/>
-      <c r="E3" s="67" t="n"/>
-      <c r="F3" s="67" t="n"/>
-      <c r="G3" s="67" t="n"/>
-      <c r="H3" s="67" t="n"/>
-      <c r="I3" s="67" t="n"/>
-      <c r="J3" s="67" t="n"/>
-      <c r="K3" s="67" t="n"/>
-      <c r="L3" s="67" t="n"/>
-      <c r="M3" s="67" t="n"/>
-      <c r="N3" s="67" t="n"/>
-      <c r="O3" s="67" t="n"/>
-      <c r="P3" s="67" t="n"/>
-      <c r="Q3" s="67" t="n"/>
-      <c r="R3" s="68" t="n"/>
-    </row>
-    <row r="4" ht="20.1" customHeight="1">
-      <c r="B4" s="18" t="inlineStr">
-        <is>
-          <t>Frecuencia</t>
-        </is>
-      </c>
-      <c r="C4" s="41" t="inlineStr">
-        <is>
-          <t>Mensual</t>
-        </is>
-      </c>
-      <c r="D4" s="67" t="n"/>
-      <c r="E4" s="67" t="n"/>
-      <c r="F4" s="67" t="n"/>
-      <c r="G4" s="67" t="n"/>
-      <c r="H4" s="67" t="n"/>
-      <c r="I4" s="67" t="n"/>
-      <c r="J4" s="67" t="n"/>
-      <c r="K4" s="67" t="n"/>
-      <c r="L4" s="67" t="n"/>
-      <c r="M4" s="67" t="n"/>
-      <c r="N4" s="67" t="n"/>
-      <c r="O4" s="67" t="n"/>
-      <c r="P4" s="67" t="n"/>
-      <c r="Q4" s="67" t="n"/>
-      <c r="R4" s="68" t="n"/>
-    </row>
-    <row r="5" ht="20.1" customHeight="1">
-      <c r="B5" s="18" t="inlineStr">
-        <is>
-          <t>Publicación</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="n"/>
-      <c r="D5" s="67" t="n"/>
-      <c r="E5" s="67" t="n"/>
-      <c r="F5" s="67" t="n"/>
-      <c r="G5" s="67" t="n"/>
-      <c r="H5" s="67" t="n"/>
-      <c r="I5" s="67" t="n"/>
-      <c r="J5" s="67" t="n"/>
-      <c r="K5" s="67" t="n"/>
-      <c r="L5" s="67" t="n"/>
-      <c r="M5" s="67" t="n"/>
-      <c r="N5" s="67" t="n"/>
-      <c r="O5" s="67" t="n"/>
-      <c r="P5" s="67" t="n"/>
-      <c r="Q5" s="67" t="n"/>
-      <c r="R5" s="68" t="n"/>
-    </row>
-    <row r="6" ht="20.1" customHeight="1">
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>Próximo dato</t>
-        </is>
-      </c>
-      <c r="C6" s="41" t="n"/>
-      <c r="D6" s="67" t="n"/>
-      <c r="E6" s="67" t="n"/>
-      <c r="F6" s="67" t="n"/>
-      <c r="G6" s="67" t="n"/>
-      <c r="H6" s="67" t="n"/>
-      <c r="I6" s="67" t="n"/>
-      <c r="J6" s="67" t="n"/>
-      <c r="K6" s="67" t="n"/>
-      <c r="L6" s="67" t="n"/>
-      <c r="M6" s="67" t="n"/>
-      <c r="N6" s="67" t="n"/>
-      <c r="O6" s="67" t="n"/>
-      <c r="P6" s="67" t="n"/>
-      <c r="Q6" s="67" t="n"/>
-      <c r="R6" s="68" t="n"/>
-    </row>
-    <row r="7" ht="39.95" customHeight="1">
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>Fuente</t>
-        </is>
-      </c>
-      <c r="C7" s="43" t="inlineStr">
-        <is>
-          <t>INEGI 
-https://www.inegi.org.mx/temas/inpc/</t>
-        </is>
-      </c>
-      <c r="D7" s="70" t="n"/>
-      <c r="E7" s="70" t="n"/>
-      <c r="F7" s="70" t="n"/>
-      <c r="G7" s="70" t="n"/>
-      <c r="H7" s="70" t="n"/>
-      <c r="I7" s="70" t="n"/>
-      <c r="J7" s="70" t="n"/>
-      <c r="K7" s="70" t="n"/>
-      <c r="L7" s="70" t="n"/>
-      <c r="M7" s="70" t="n"/>
-      <c r="N7" s="70" t="n"/>
-      <c r="O7" s="70" t="n"/>
-      <c r="P7" s="70" t="n"/>
-      <c r="Q7" s="70" t="n"/>
-      <c r="R7" s="70" t="n"/>
-    </row>
-    <row r="8" ht="20.1" customHeight="1"/>
-    <row r="9" ht="17.25" customHeight="1">
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Mes</t>
-        </is>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Inflación</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>Subyacente</t>
-        </is>
-      </c>
-      <c r="E9" s="26" t="inlineStr">
-        <is>
-          <t>No subyacente</t>
-        </is>
-      </c>
-      <c r="F9" s="35" t="inlineStr">
-        <is>
-          <t>Banxico</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="17.25" customHeight="1">
-      <c r="B10" s="27" t="inlineStr">
-        <is>
-          <t>Jun 25</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>4.24</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="F10" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1">
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Jul 25</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="F11" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" ht="17.25" customHeight="1">
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Ago 25</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="F12" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" ht="17.25" customHeight="1">
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Sep 25</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" ht="17.25" customHeight="1">
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>Oct 25</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E14" s="5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="F14" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" ht="17.25" customHeight="1">
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>Nov 25</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D15" s="5" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E15" s="5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" ht="17.25" customHeight="1">
-      <c r="B16" s="27" t="inlineStr">
-        <is>
-          <t>Dic 25</t>
-        </is>
-      </c>
-      <c r="C16" s="12" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="D16" s="5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" ht="17.25" customHeight="1">
-      <c r="B17" s="27" t="inlineStr">
-        <is>
-          <t>Ene 26</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>3.79</v>
-      </c>
-      <c r="D17" s="5" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" ht="17.25" customHeight="1">
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Feb 26</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="D18" s="5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="E18" s="5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" ht="17.25" customHeight="1">
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>Mar 26</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="D19" s="5" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" ht="17.25" customHeight="1">
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>Abr 26</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" ht="17.25" customHeight="1">
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="D21" s="5" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="C2:R2"/>
-    <mergeCell ref="C5:R5"/>
-    <mergeCell ref="C3:R3"/>
-    <mergeCell ref="C4:R4"/>
-    <mergeCell ref="C6:R6"/>
-    <mergeCell ref="C7:R7"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-  </tableParts>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12090,13 +9474,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -12150,70 +9534,72 @@
     <row r="5">
       <c r="A5" s="82" t="inlineStr">
         <is>
-          <t>Feb 24</t>
+          <t>Dic 23</t>
         </is>
       </c>
       <c r="B5" s="82" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C5" s="82" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D5" s="82" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
       <c r="E5" s="82" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="82" t="inlineStr">
         <is>
-          <t>Mar 24</t>
+          <t>Ene 24</t>
         </is>
       </c>
       <c r="B6" s="82" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C6" s="82" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="D6" s="82" t="n">
-        <v>-0.9</v>
+        <v>-0.7</v>
       </c>
       <c r="E6" s="82" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="82" t="inlineStr">
         <is>
-          <t>Jun 24</t>
+          <t>Feb 24</t>
         </is>
       </c>
       <c r="B7" s="82" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C7" s="82" t="n">
-        <v>0.9</v>
+        <v>2.4</v>
       </c>
       <c r="D7" s="82" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="E7" s="82" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="82" t="inlineStr">
         <is>
-          <t>Nov 24</t>
+          <t>Mar 24</t>
         </is>
       </c>
       <c r="B8" s="82" t="n">
         <v>0.2</v>
       </c>
-      <c r="C8" s="82" t="n"/>
+      <c r="C8" s="82" t="n">
+        <v>2.1</v>
+      </c>
       <c r="D8" s="82" t="n">
         <v>-0.9</v>
       </c>
@@ -12224,131 +9610,129 @@
     <row r="9">
       <c r="A9" s="82" t="inlineStr">
         <is>
-          <t>Dic 24</t>
+          <t>Abr 24</t>
         </is>
       </c>
       <c r="B9" s="82" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="C9" s="82" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="D9" s="82" t="n">
         <v>-0.8</v>
       </c>
       <c r="E9" s="82" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="82" t="inlineStr">
         <is>
-          <t>Ene 25</t>
+          <t>May 24</t>
         </is>
       </c>
       <c r="B10" s="82" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="C10" s="82" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="D10" s="82" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="E10" s="82" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="82" t="inlineStr">
         <is>
-          <t>Feb 25</t>
+          <t>Jun 24</t>
         </is>
       </c>
       <c r="B11" s="82" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="C11" s="82" t="n">
-        <v>-0.7</v>
+        <v>0.9</v>
       </c>
       <c r="D11" s="82" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="E11" s="82" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="82" t="inlineStr">
         <is>
-          <t>Mar 25</t>
+          <t>Nov 24</t>
         </is>
       </c>
       <c r="B12" s="82" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="82" t="n">
-        <v>-0.2</v>
-      </c>
+        <v>0.2</v>
+      </c>
+      <c r="C12" s="82" t="n"/>
       <c r="D12" s="82" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
       <c r="E12" s="82" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="82" t="inlineStr">
         <is>
-          <t>Abr 25</t>
+          <t>Dic 24</t>
         </is>
       </c>
       <c r="B13" s="82" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="C13" s="82" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="D13" s="82" t="n">
-        <v>-1.4</v>
+        <v>-0.8</v>
       </c>
       <c r="E13" s="82" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="82" t="inlineStr">
         <is>
-          <t>May 25</t>
+          <t>Ene 25</t>
         </is>
       </c>
       <c r="B14" s="82" t="n">
         <v>0.1</v>
       </c>
       <c r="C14" s="82" t="n">
-        <v>-0.3</v>
+        <v>1.8</v>
       </c>
       <c r="D14" s="82" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
       <c r="E14" s="82" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="82" t="inlineStr">
         <is>
-          <t>Jun 25</t>
+          <t>Feb 25</t>
         </is>
       </c>
       <c r="B15" s="82" t="n">
         <v>0.2</v>
       </c>
       <c r="C15" s="82" t="n">
-        <v>1.3</v>
+        <v>-0.7</v>
       </c>
       <c r="D15" s="82" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="E15" s="82" t="n">
         <v>1.4</v>
@@ -12357,112 +9741,112 @@
     <row r="16">
       <c r="A16" s="82" t="inlineStr">
         <is>
-          <t>Jul 25</t>
+          <t>Mar 25</t>
         </is>
       </c>
       <c r="B16" s="82" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="C16" s="82" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="D16" s="82" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
       <c r="E16" s="82" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="82" t="inlineStr">
         <is>
-          <t>Ago 25</t>
+          <t>Abr 25</t>
         </is>
       </c>
       <c r="B17" s="82" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C17" s="82" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="D17" s="82" t="n">
-        <v>-1.1</v>
+        <v>-1.4</v>
       </c>
       <c r="E17" s="82" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="82" t="inlineStr">
         <is>
-          <t>Sep 25</t>
+          <t>May 25</t>
         </is>
       </c>
       <c r="B18" s="82" t="n">
         <v>0.1</v>
       </c>
       <c r="C18" s="82" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="D18" s="82" t="n">
         <v>-1</v>
       </c>
       <c r="E18" s="82" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="82" t="inlineStr">
         <is>
-          <t>Oct 25</t>
+          <t>Jun 25</t>
         </is>
       </c>
       <c r="B19" s="82" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="C19" s="82" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="D19" s="82" t="n">
         <v>-0.9</v>
       </c>
       <c r="E19" s="82" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="82" t="inlineStr">
         <is>
-          <t>Nov 25</t>
+          <t>Jul 25</t>
         </is>
       </c>
       <c r="B20" s="82" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="C20" s="82" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D20" s="82" t="n">
-        <v>-1.3</v>
+        <v>-1</v>
       </c>
       <c r="E20" s="82" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="82" t="inlineStr">
         <is>
-          <t>Dic 25</t>
+          <t>Ago 25</t>
         </is>
       </c>
       <c r="B21" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C21" s="82" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="82" t="n">
-        <v>2.3</v>
-      </c>
       <c r="D21" s="82" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="E21" s="82" t="n">
         <v>1.3</v>
@@ -12471,17 +9855,17 @@
     <row r="22">
       <c r="A22" s="82" t="inlineStr">
         <is>
-          <t>Ene 26</t>
+          <t>Sep 25</t>
         </is>
       </c>
       <c r="B22" s="82" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="C22" s="82" t="n">
-        <v>2.3</v>
+        <v>-0.6</v>
       </c>
       <c r="D22" s="82" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="E22" s="82" t="n">
         <v>1.2</v>
@@ -12490,74 +9874,74 @@
     <row r="23">
       <c r="A23" s="82" t="inlineStr">
         <is>
-          <t>Feb 26</t>
+          <t>Oct 25</t>
         </is>
       </c>
       <c r="B23" s="82" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C23" s="82" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="D23" s="82" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="E23" s="82" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="82" t="inlineStr">
         <is>
-          <t>Mar 26</t>
+          <t>Nov 25</t>
         </is>
       </c>
       <c r="B24" s="82" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="C24" s="82" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="82" t="n">
-        <v>0.5</v>
-      </c>
       <c r="D24" s="82" t="n">
-        <v>-1.2</v>
+        <v>-1.3</v>
       </c>
       <c r="E24" s="82" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="82" t="inlineStr">
         <is>
-          <t>Abr 26</t>
+          <t>Dic 25</t>
         </is>
       </c>
       <c r="B25" s="82" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C25" s="82" t="n">
-        <v>0.3</v>
+        <v>2.3</v>
       </c>
       <c r="D25" s="82" t="n">
-        <v>-0.6</v>
+        <v>-1</v>
       </c>
       <c r="E25" s="82" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="82" t="inlineStr">
         <is>
-          <t>May 26</t>
+          <t>Ene 26</t>
         </is>
       </c>
       <c r="B26" s="82" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="C26" s="82" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="D26" s="82" t="n">
-        <v>-1.1</v>
+        <v>-0.6</v>
       </c>
       <c r="E26" s="82" t="n">
         <v>1.2</v>
@@ -12566,19 +9950,95 @@
     <row r="27">
       <c r="A27" s="82" t="inlineStr">
         <is>
+          <t>Feb 26</t>
+        </is>
+      </c>
+      <c r="B27" s="82" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C27" s="82" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D27" s="82" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E27" s="82" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="82" t="inlineStr">
+        <is>
+          <t>Mar 26</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="82" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D28" s="82" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E28" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="82" t="inlineStr">
+        <is>
+          <t>Abr 26</t>
+        </is>
+      </c>
+      <c r="B29" s="82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C29" s="82" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="82" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E29" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="82" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C30" s="82" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D30" s="82" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="E30" s="82" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="82" t="inlineStr">
+        <is>
           <t>Jun 26</t>
         </is>
       </c>
-      <c r="B27" s="82" t="n">
+      <c r="B31" s="82" t="n">
         <v>0.2</v>
       </c>
-      <c r="C27" s="82" t="n">
+      <c r="C31" s="82" t="n">
         <v>1.7</v>
       </c>
-      <c r="D27" s="82" t="n">
+      <c r="D31" s="82" t="n">
         <v>-1</v>
       </c>
-      <c r="E27" s="82" t="n">
+      <c r="E31" s="82" t="n">
         <v>1.3</v>
       </c>
     </row>
@@ -12587,7 +10047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13950,13 +11410,1701 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:D106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="61" t="inlineStr">
+        <is>
+          <t>Balanza Comercial de Mercancías de México</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="62" t="inlineStr">
+        <is>
+          <t>Fuente: INEGI · Frecuencia: Mensual · Unidad: Millones de dólares · Estado: ACTUALIZADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="63" t="inlineStr">
+        <is>
+          <t>Periodo</t>
+        </is>
+      </c>
+      <c r="B4" s="63" t="inlineStr">
+        <is>
+          <t>Exportaciones</t>
+        </is>
+      </c>
+      <c r="C4" s="63" t="inlineStr">
+        <is>
+          <t>Importaciones</t>
+        </is>
+      </c>
+      <c r="D4" s="63" t="inlineStr">
+        <is>
+          <t>Saldo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="82" t="inlineStr">
+        <is>
+          <t>Ene 18</t>
+        </is>
+      </c>
+      <c r="B5" s="82" t="n">
+        <v>30718.527</v>
+      </c>
+      <c r="C5" s="82" t="n">
+        <v>35140.478</v>
+      </c>
+      <c r="D5" s="82" t="n">
+        <v>-4421.951</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="82" t="inlineStr">
+        <is>
+          <t>Feb 18</t>
+        </is>
+      </c>
+      <c r="B6" s="82" t="n">
+        <v>35093.793</v>
+      </c>
+      <c r="C6" s="82" t="n">
+        <v>34149.86</v>
+      </c>
+      <c r="D6" s="82" t="n">
+        <v>943.933</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="82" t="inlineStr">
+        <is>
+          <t>Mar 18</t>
+        </is>
+      </c>
+      <c r="B7" s="82" t="n">
+        <v>39484.266</v>
+      </c>
+      <c r="C7" s="82" t="n">
+        <v>37734.615</v>
+      </c>
+      <c r="D7" s="82" t="n">
+        <v>1749.651</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="82" t="inlineStr">
+        <is>
+          <t>Abr 18</t>
+        </is>
+      </c>
+      <c r="B8" s="82" t="n">
+        <v>37181.694</v>
+      </c>
+      <c r="C8" s="82" t="n">
+        <v>37471.965</v>
+      </c>
+      <c r="D8" s="82" t="n">
+        <v>-290.271</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="82" t="inlineStr">
+        <is>
+          <t>May 18</t>
+        </is>
+      </c>
+      <c r="B9" s="82" t="n">
+        <v>39213.912</v>
+      </c>
+      <c r="C9" s="82" t="n">
+        <v>40766.241</v>
+      </c>
+      <c r="D9" s="82" t="n">
+        <v>-1552.329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="82" t="inlineStr">
+        <is>
+          <t>Jun 18</t>
+        </is>
+      </c>
+      <c r="B10" s="82" t="n">
+        <v>37483.508</v>
+      </c>
+      <c r="C10" s="82" t="n">
+        <v>38383.337</v>
+      </c>
+      <c r="D10" s="82" t="n">
+        <v>-899.829</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="82" t="inlineStr">
+        <is>
+          <t>Jul 18</t>
+        </is>
+      </c>
+      <c r="B11" s="82" t="n">
+        <v>36742.212</v>
+      </c>
+      <c r="C11" s="82" t="n">
+        <v>39612.118</v>
+      </c>
+      <c r="D11" s="82" t="n">
+        <v>-2869.906</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="82" t="inlineStr">
+        <is>
+          <t>Ago 18</t>
+        </is>
+      </c>
+      <c r="B12" s="82" t="n">
+        <v>39545.208</v>
+      </c>
+      <c r="C12" s="82" t="n">
+        <v>42129.496</v>
+      </c>
+      <c r="D12" s="82" t="n">
+        <v>-2584.288</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="82" t="inlineStr">
+        <is>
+          <t>Sep 18</t>
+        </is>
+      </c>
+      <c r="B13" s="82" t="n">
+        <v>37700.602</v>
+      </c>
+      <c r="C13" s="82" t="n">
+        <v>38001.683</v>
+      </c>
+      <c r="D13" s="82" t="n">
+        <v>-301.081</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="82" t="inlineStr">
+        <is>
+          <t>Oct 18</t>
+        </is>
+      </c>
+      <c r="B14" s="82" t="n">
+        <v>41356.07</v>
+      </c>
+      <c r="C14" s="82" t="n">
+        <v>44290.891</v>
+      </c>
+      <c r="D14" s="82" t="n">
+        <v>-2934.821</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="82" t="inlineStr">
+        <is>
+          <t>Nov 18</t>
+        </is>
+      </c>
+      <c r="B15" s="82" t="n">
+        <v>38595.389</v>
+      </c>
+      <c r="C15" s="82" t="n">
+        <v>40928.716</v>
+      </c>
+      <c r="D15" s="82" t="n">
+        <v>-2333.327</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="82" t="inlineStr">
+        <is>
+          <t>Dic 18</t>
+        </is>
+      </c>
+      <c r="B16" s="82" t="n">
+        <v>37597.547</v>
+      </c>
+      <c r="C16" s="82" t="n">
+        <v>35692.967</v>
+      </c>
+      <c r="D16" s="82" t="n">
+        <v>1904.58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="82" t="inlineStr">
+        <is>
+          <t>Ene 19</t>
+        </is>
+      </c>
+      <c r="B17" s="82" t="n">
+        <v>32637.22</v>
+      </c>
+      <c r="C17" s="82" t="n">
+        <v>37262.788</v>
+      </c>
+      <c r="D17" s="82" t="n">
+        <v>-4625.568</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="82" t="inlineStr">
+        <is>
+          <t>Feb 19</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n">
+        <v>36437.807</v>
+      </c>
+      <c r="C18" s="82" t="n">
+        <v>35073.897</v>
+      </c>
+      <c r="D18" s="82" t="n">
+        <v>1363.91</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="82" t="inlineStr">
+        <is>
+          <t>Mar 19</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>39018.828</v>
+      </c>
+      <c r="C19" s="82" t="n">
+        <v>37530.886</v>
+      </c>
+      <c r="D19" s="82" t="n">
+        <v>1487.942</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="82" t="inlineStr">
+        <is>
+          <t>Abr 19</t>
+        </is>
+      </c>
+      <c r="B20" s="82" t="n">
+        <v>39586.47</v>
+      </c>
+      <c r="C20" s="82" t="n">
+        <v>38076.401</v>
+      </c>
+      <c r="D20" s="82" t="n">
+        <v>1510.069</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="82" t="inlineStr">
+        <is>
+          <t>May 19</t>
+        </is>
+      </c>
+      <c r="B21" s="82" t="n">
+        <v>41749.996</v>
+      </c>
+      <c r="C21" s="82" t="n">
+        <v>40792.86</v>
+      </c>
+      <c r="D21" s="82" t="n">
+        <v>957.136</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="82" t="inlineStr">
+        <is>
+          <t>Jun 19</t>
+        </is>
+      </c>
+      <c r="B22" s="82" t="n">
+        <v>37924.986</v>
+      </c>
+      <c r="C22" s="82" t="n">
+        <v>35382.744</v>
+      </c>
+      <c r="D22" s="82" t="n">
+        <v>2542.242</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="82" t="inlineStr">
+        <is>
+          <t>Jul 19</t>
+        </is>
+      </c>
+      <c r="B23" s="82" t="n">
+        <v>39115.793</v>
+      </c>
+      <c r="C23" s="82" t="n">
+        <v>40406.335</v>
+      </c>
+      <c r="D23" s="82" t="n">
+        <v>-1290.542</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="82" t="inlineStr">
+        <is>
+          <t>Ago 19</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="n">
+        <v>40051.141</v>
+      </c>
+      <c r="C24" s="82" t="n">
+        <v>39648.433</v>
+      </c>
+      <c r="D24" s="82" t="n">
+        <v>402.708</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="82" t="inlineStr">
+        <is>
+          <t>Sep 19</t>
+        </is>
+      </c>
+      <c r="B25" s="82" t="n">
+        <v>37180.583</v>
+      </c>
+      <c r="C25" s="82" t="n">
+        <v>37332.184</v>
+      </c>
+      <c r="D25" s="82" t="n">
+        <v>-151.601</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="82" t="inlineStr">
+        <is>
+          <t>Oct 19</t>
+        </is>
+      </c>
+      <c r="B26" s="82" t="n">
+        <v>40762.123</v>
+      </c>
+      <c r="C26" s="82" t="n">
+        <v>41449.532</v>
+      </c>
+      <c r="D26" s="82" t="n">
+        <v>-687.409</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="82" t="inlineStr">
+        <is>
+          <t>Nov 19</t>
+        </is>
+      </c>
+      <c r="B27" s="82" t="n">
+        <v>37484.491</v>
+      </c>
+      <c r="C27" s="82" t="n">
+        <v>36697.66</v>
+      </c>
+      <c r="D27" s="82" t="n">
+        <v>786.831</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="82" t="inlineStr">
+        <is>
+          <t>Dic 19</t>
+        </is>
+      </c>
+      <c r="B28" s="82" t="n">
+        <v>38654.441</v>
+      </c>
+      <c r="C28" s="82" t="n">
+        <v>35587.869</v>
+      </c>
+      <c r="D28" s="82" t="n">
+        <v>3066.572</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="82" t="inlineStr">
+        <is>
+          <t>Ene 20</t>
+        </is>
+      </c>
+      <c r="B29" s="82" t="n">
+        <v>33580.843</v>
+      </c>
+      <c r="C29" s="82" t="n">
+        <v>36062</v>
+      </c>
+      <c r="D29" s="82" t="n">
+        <v>-2481.157</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="82" t="inlineStr">
+        <is>
+          <t>Feb 20</t>
+        </is>
+      </c>
+      <c r="B30" s="82" t="n">
+        <v>36433.717</v>
+      </c>
+      <c r="C30" s="82" t="n">
+        <v>33715.379</v>
+      </c>
+      <c r="D30" s="82" t="n">
+        <v>2718.338</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="82" t="inlineStr">
+        <is>
+          <t>Mar 20</t>
+        </is>
+      </c>
+      <c r="B31" s="82" t="n">
+        <v>38310.269</v>
+      </c>
+      <c r="C31" s="82" t="n">
+        <v>34995.932</v>
+      </c>
+      <c r="D31" s="82" t="n">
+        <v>3314.337</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="82" t="inlineStr">
+        <is>
+          <t>Abr 20</t>
+        </is>
+      </c>
+      <c r="B32" s="82" t="n">
+        <v>23222.658</v>
+      </c>
+      <c r="C32" s="82" t="n">
+        <v>26457.052</v>
+      </c>
+      <c r="D32" s="82" t="n">
+        <v>-3234.394</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="82" t="inlineStr">
+        <is>
+          <t>May 20</t>
+        </is>
+      </c>
+      <c r="B33" s="82" t="n">
+        <v>18116.042</v>
+      </c>
+      <c r="C33" s="82" t="n">
+        <v>21578.337</v>
+      </c>
+      <c r="D33" s="82" t="n">
+        <v>-3462.295</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="82" t="inlineStr">
+        <is>
+          <t>Jun 20</t>
+        </is>
+      </c>
+      <c r="B34" s="82" t="n">
+        <v>33047.725</v>
+      </c>
+      <c r="C34" s="82" t="n">
+        <v>27512.168</v>
+      </c>
+      <c r="D34" s="82" t="n">
+        <v>5535.557</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="82" t="inlineStr">
+        <is>
+          <t>Jul 20</t>
+        </is>
+      </c>
+      <c r="B35" s="82" t="n">
+        <v>35499.49</v>
+      </c>
+      <c r="C35" s="82" t="n">
+        <v>29844.448</v>
+      </c>
+      <c r="D35" s="82" t="n">
+        <v>5655.042</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="82" t="inlineStr">
+        <is>
+          <t>Ago 20</t>
+        </is>
+      </c>
+      <c r="B36" s="82" t="n">
+        <v>37001.121</v>
+      </c>
+      <c r="C36" s="82" t="n">
+        <v>30845.723</v>
+      </c>
+      <c r="D36" s="82" t="n">
+        <v>6155.398</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="82" t="inlineStr">
+        <is>
+          <t>Sep 20</t>
+        </is>
+      </c>
+      <c r="B37" s="82" t="n">
+        <v>38539.74</v>
+      </c>
+      <c r="C37" s="82" t="n">
+        <v>34142.602</v>
+      </c>
+      <c r="D37" s="82" t="n">
+        <v>4397.138</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="82" t="inlineStr">
+        <is>
+          <t>Oct 20</t>
+        </is>
+      </c>
+      <c r="B38" s="82" t="n">
+        <v>41950.815</v>
+      </c>
+      <c r="C38" s="82" t="n">
+        <v>35694.81</v>
+      </c>
+      <c r="D38" s="82" t="n">
+        <v>6256.005</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="82" t="inlineStr">
+        <is>
+          <t>Nov 20</t>
+        </is>
+      </c>
+      <c r="B39" s="82" t="n">
+        <v>38313.68</v>
+      </c>
+      <c r="C39" s="82" t="n">
+        <v>35257.525</v>
+      </c>
+      <c r="D39" s="82" t="n">
+        <v>3056.155</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="82" t="inlineStr">
+        <is>
+          <t>Dic 20</t>
+        </is>
+      </c>
+      <c r="B40" s="82" t="n">
+        <v>43154.635</v>
+      </c>
+      <c r="C40" s="82" t="n">
+        <v>36879.948</v>
+      </c>
+      <c r="D40" s="82" t="n">
+        <v>6274.687</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="82" t="inlineStr">
+        <is>
+          <t>Ene 21</t>
+        </is>
+      </c>
+      <c r="B41" s="82" t="n">
+        <v>32716.091</v>
+      </c>
+      <c r="C41" s="82" t="n">
+        <v>33910.702</v>
+      </c>
+      <c r="D41" s="82" t="n">
+        <v>-1194.611</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="82" t="inlineStr">
+        <is>
+          <t>Feb 21</t>
+        </is>
+      </c>
+      <c r="B42" s="82" t="n">
+        <v>36213.207</v>
+      </c>
+      <c r="C42" s="82" t="n">
+        <v>33486.199</v>
+      </c>
+      <c r="D42" s="82" t="n">
+        <v>2727.008</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="82" t="inlineStr">
+        <is>
+          <t>Mar 21</t>
+        </is>
+      </c>
+      <c r="B43" s="82" t="n">
+        <v>43029.98</v>
+      </c>
+      <c r="C43" s="82" t="n">
+        <v>45974.454</v>
+      </c>
+      <c r="D43" s="82" t="n">
+        <v>-2944.474</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="82" t="inlineStr">
+        <is>
+          <t>Abr 21</t>
+        </is>
+      </c>
+      <c r="B44" s="82" t="n">
+        <v>40944.531</v>
+      </c>
+      <c r="C44" s="82" t="n">
+        <v>39259.65</v>
+      </c>
+      <c r="D44" s="82" t="n">
+        <v>1684.881</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="82" t="inlineStr">
+        <is>
+          <t>May 21</t>
+        </is>
+      </c>
+      <c r="B45" s="82" t="n">
+        <v>40845.6</v>
+      </c>
+      <c r="C45" s="82" t="n">
+        <v>40458.684</v>
+      </c>
+      <c r="D45" s="82" t="n">
+        <v>386.916</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="82" t="inlineStr">
+        <is>
+          <t>Jun 21</t>
+        </is>
+      </c>
+      <c r="B46" s="82" t="n">
+        <v>42619.373</v>
+      </c>
+      <c r="C46" s="82" t="n">
+        <v>41909.429</v>
+      </c>
+      <c r="D46" s="82" t="n">
+        <v>709.944</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="82" t="inlineStr">
+        <is>
+          <t>Jul 21</t>
+        </is>
+      </c>
+      <c r="B47" s="82" t="n">
+        <v>40952.956</v>
+      </c>
+      <c r="C47" s="82" t="n">
+        <v>44950.628</v>
+      </c>
+      <c r="D47" s="82" t="n">
+        <v>-3997.672</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="82" t="inlineStr">
+        <is>
+          <t>Ago 21</t>
+        </is>
+      </c>
+      <c r="B48" s="82" t="n">
+        <v>40471.381</v>
+      </c>
+      <c r="C48" s="82" t="n">
+        <v>44215.64</v>
+      </c>
+      <c r="D48" s="82" t="n">
+        <v>-3744.259</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="82" t="inlineStr">
+        <is>
+          <t>Sep 21</t>
+        </is>
+      </c>
+      <c r="B49" s="82" t="n">
+        <v>41754.363</v>
+      </c>
+      <c r="C49" s="82" t="n">
+        <v>44078.456</v>
+      </c>
+      <c r="D49" s="82" t="n">
+        <v>-2324.093</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="82" t="inlineStr">
+        <is>
+          <t>Oct 21</t>
+        </is>
+      </c>
+      <c r="B50" s="82" t="n">
+        <v>41858.778</v>
+      </c>
+      <c r="C50" s="82" t="n">
+        <v>44658.126</v>
+      </c>
+      <c r="D50" s="82" t="n">
+        <v>-2799.348</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="82" t="inlineStr">
+        <is>
+          <t>Nov 21</t>
+        </is>
+      </c>
+      <c r="B51" s="82" t="n">
+        <v>45676.554</v>
+      </c>
+      <c r="C51" s="82" t="n">
+        <v>45698.67</v>
+      </c>
+      <c r="D51" s="82" t="n">
+        <v>-22.116</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="82" t="inlineStr">
+        <is>
+          <t>Dic 21</t>
+        </is>
+      </c>
+      <c r="B52" s="82" t="n">
+        <v>47866.2</v>
+      </c>
+      <c r="C52" s="82" t="n">
+        <v>47102.458</v>
+      </c>
+      <c r="D52" s="82" t="n">
+        <v>763.742</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="82" t="inlineStr">
+        <is>
+          <t>Ene 22</t>
+        </is>
+      </c>
+      <c r="B53" s="82" t="n">
+        <v>33923.041</v>
+      </c>
+      <c r="C53" s="82" t="n">
+        <v>40185.365</v>
+      </c>
+      <c r="D53" s="82" t="n">
+        <v>-6262.324</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="82" t="inlineStr">
+        <is>
+          <t>Feb 22</t>
+        </is>
+      </c>
+      <c r="B54" s="82" t="n">
+        <v>46288.481</v>
+      </c>
+      <c r="C54" s="82" t="n">
+        <v>44953.077</v>
+      </c>
+      <c r="D54" s="82" t="n">
+        <v>1335.404</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="82" t="inlineStr">
+        <is>
+          <t>Mar 22</t>
+        </is>
+      </c>
+      <c r="B55" s="82" t="n">
+        <v>51948.842</v>
+      </c>
+      <c r="C55" s="82" t="n">
+        <v>51801.683</v>
+      </c>
+      <c r="D55" s="82" t="n">
+        <v>147.159</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="82" t="inlineStr">
+        <is>
+          <t>Abr 22</t>
+        </is>
+      </c>
+      <c r="B56" s="82" t="n">
+        <v>47580.499</v>
+      </c>
+      <c r="C56" s="82" t="n">
+        <v>49363.532</v>
+      </c>
+      <c r="D56" s="82" t="n">
+        <v>-1783.033</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="82" t="inlineStr">
+        <is>
+          <t>May 22</t>
+        </is>
+      </c>
+      <c r="B57" s="82" t="n">
+        <v>49964.741</v>
+      </c>
+      <c r="C57" s="82" t="n">
+        <v>52220.452</v>
+      </c>
+      <c r="D57" s="82" t="n">
+        <v>-2255.711</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="82" t="inlineStr">
+        <is>
+          <t>Jun 22</t>
+        </is>
+      </c>
+      <c r="B58" s="82" t="n">
+        <v>51220.139</v>
+      </c>
+      <c r="C58" s="82" t="n">
+        <v>55191.302</v>
+      </c>
+      <c r="D58" s="82" t="n">
+        <v>-3971.163</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="82" t="inlineStr">
+        <is>
+          <t>Jul 22</t>
+        </is>
+      </c>
+      <c r="B59" s="82" t="n">
+        <v>46216.526</v>
+      </c>
+      <c r="C59" s="82" t="n">
+        <v>52463.962</v>
+      </c>
+      <c r="D59" s="82" t="n">
+        <v>-6247.436</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="82" t="inlineStr">
+        <is>
+          <t>Ago 22</t>
+        </is>
+      </c>
+      <c r="B60" s="82" t="n">
+        <v>50464.229</v>
+      </c>
+      <c r="C60" s="82" t="n">
+        <v>56168.196</v>
+      </c>
+      <c r="D60" s="82" t="n">
+        <v>-5703.967</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="82" t="inlineStr">
+        <is>
+          <t>Sep 22</t>
+        </is>
+      </c>
+      <c r="B61" s="82" t="n">
+        <v>52323.438</v>
+      </c>
+      <c r="C61" s="82" t="n">
+        <v>53520.102</v>
+      </c>
+      <c r="D61" s="82" t="n">
+        <v>-1196.664</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="82" t="inlineStr">
+        <is>
+          <t>Oct 22</t>
+        </is>
+      </c>
+      <c r="B62" s="82" t="n">
+        <v>49199.055</v>
+      </c>
+      <c r="C62" s="82" t="n">
+        <v>51861.889</v>
+      </c>
+      <c r="D62" s="82" t="n">
+        <v>-2662.834</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="82" t="inlineStr">
+        <is>
+          <t>Nov 22</t>
+        </is>
+      </c>
+      <c r="B63" s="82" t="n">
+        <v>49249.147</v>
+      </c>
+      <c r="C63" s="82" t="n">
+        <v>49699.319</v>
+      </c>
+      <c r="D63" s="82" t="n">
+        <v>-450.172</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="82" t="inlineStr">
+        <is>
+          <t>Dic 22</t>
+        </is>
+      </c>
+      <c r="B64" s="82" t="n">
+        <v>49319.342</v>
+      </c>
+      <c r="C64" s="82" t="n">
+        <v>48376.487</v>
+      </c>
+      <c r="D64" s="82" t="n">
+        <v>942.855</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="82" t="inlineStr">
+        <is>
+          <t>Ene 23</t>
+        </is>
+      </c>
+      <c r="B65" s="82" t="n">
+        <v>42609.734</v>
+      </c>
+      <c r="C65" s="82" t="n">
+        <v>46739.068</v>
+      </c>
+      <c r="D65" s="82" t="n">
+        <v>-4129.334</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="82" t="inlineStr">
+        <is>
+          <t>Feb 23</t>
+        </is>
+      </c>
+      <c r="B66" s="82" t="n">
+        <v>44891.18</v>
+      </c>
+      <c r="C66" s="82" t="n">
+        <v>46877.022</v>
+      </c>
+      <c r="D66" s="82" t="n">
+        <v>-1985.842</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="82" t="inlineStr">
+        <is>
+          <t>Mar 23</t>
+        </is>
+      </c>
+      <c r="B67" s="82" t="n">
+        <v>53564.189</v>
+      </c>
+      <c r="C67" s="82" t="n">
+        <v>52403.727</v>
+      </c>
+      <c r="D67" s="82" t="n">
+        <v>1160.462</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="82" t="inlineStr">
+        <is>
+          <t>Abr 23</t>
+        </is>
+      </c>
+      <c r="B68" s="82" t="n">
+        <v>46086.56</v>
+      </c>
+      <c r="C68" s="82" t="n">
+        <v>47732.749</v>
+      </c>
+      <c r="D68" s="82" t="n">
+        <v>-1646.189</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="82" t="inlineStr">
+        <is>
+          <t>May 23</t>
+        </is>
+      </c>
+      <c r="B69" s="82" t="n">
+        <v>52835.329</v>
+      </c>
+      <c r="C69" s="82" t="n">
+        <v>53029.653</v>
+      </c>
+      <c r="D69" s="82" t="n">
+        <v>-194.324</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="82" t="inlineStr">
+        <is>
+          <t>Jun 23</t>
+        </is>
+      </c>
+      <c r="B70" s="82" t="n">
+        <v>51820.219</v>
+      </c>
+      <c r="C70" s="82" t="n">
+        <v>52006.715</v>
+      </c>
+      <c r="D70" s="82" t="n">
+        <v>-186.496</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="82" t="inlineStr">
+        <is>
+          <t>Jul 23</t>
+        </is>
+      </c>
+      <c r="B71" s="82" t="n">
+        <v>47786.853</v>
+      </c>
+      <c r="C71" s="82" t="n">
+        <v>48627.636</v>
+      </c>
+      <c r="D71" s="82" t="n">
+        <v>-840.783</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="82" t="inlineStr">
+        <is>
+          <t>Ago 23</t>
+        </is>
+      </c>
+      <c r="B72" s="82" t="n">
+        <v>52458.59</v>
+      </c>
+      <c r="C72" s="82" t="n">
+        <v>54575.454</v>
+      </c>
+      <c r="D72" s="82" t="n">
+        <v>-2116.864</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="82" t="inlineStr">
+        <is>
+          <t>Sep 23</t>
+        </is>
+      </c>
+      <c r="B73" s="82" t="n">
+        <v>49642.255</v>
+      </c>
+      <c r="C73" s="82" t="n">
+        <v>52303.579</v>
+      </c>
+      <c r="D73" s="82" t="n">
+        <v>-2661.324</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="82" t="inlineStr">
+        <is>
+          <t>Oct 23</t>
+        </is>
+      </c>
+      <c r="B74" s="82" t="n">
+        <v>51856.871</v>
+      </c>
+      <c r="C74" s="82" t="n">
+        <v>53663.09</v>
+      </c>
+      <c r="D74" s="82" t="n">
+        <v>-1806.219</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="82" t="inlineStr">
+        <is>
+          <t>Nov 23</t>
+        </is>
+      </c>
+      <c r="B75" s="82" t="n">
+        <v>50171.872</v>
+      </c>
+      <c r="C75" s="82" t="n">
+        <v>50942.41</v>
+      </c>
+      <c r="D75" s="82" t="n">
+        <v>-770.538</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="82" t="inlineStr">
+        <is>
+          <t>Dic 23</t>
+        </is>
+      </c>
+      <c r="B76" s="82" t="n">
+        <v>49277.811</v>
+      </c>
+      <c r="C76" s="82" t="n">
+        <v>46378.863</v>
+      </c>
+      <c r="D76" s="82" t="n">
+        <v>2898.948</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="82" t="inlineStr">
+        <is>
+          <t>Ene 24</t>
+        </is>
+      </c>
+      <c r="B77" s="82" t="n">
+        <v>42135.801</v>
+      </c>
+      <c r="C77" s="82" t="n">
+        <v>47219.837</v>
+      </c>
+      <c r="D77" s="82" t="n">
+        <v>-5084.036</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="82" t="inlineStr">
+        <is>
+          <t>Feb 24</t>
+        </is>
+      </c>
+      <c r="B78" s="82" t="n">
+        <v>50794.819</v>
+      </c>
+      <c r="C78" s="82" t="n">
+        <v>52224.739</v>
+      </c>
+      <c r="D78" s="82" t="n">
+        <v>-1429.92</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="82" t="inlineStr">
+        <is>
+          <t>Mar 24</t>
+        </is>
+      </c>
+      <c r="B79" s="82" t="n">
+        <v>50645.665</v>
+      </c>
+      <c r="C79" s="82" t="n">
+        <v>49111.325</v>
+      </c>
+      <c r="D79" s="82" t="n">
+        <v>1534.34</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="82" t="inlineStr">
+        <is>
+          <t>Abr 24</t>
+        </is>
+      </c>
+      <c r="B80" s="82" t="n">
+        <v>51522.649</v>
+      </c>
+      <c r="C80" s="82" t="n">
+        <v>55943.361</v>
+      </c>
+      <c r="D80" s="82" t="n">
+        <v>-4420.712</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="82" t="inlineStr">
+        <is>
+          <t>May 24</t>
+        </is>
+      </c>
+      <c r="B81" s="82" t="n">
+        <v>55754.041</v>
+      </c>
+      <c r="C81" s="82" t="n">
+        <v>54863.065</v>
+      </c>
+      <c r="D81" s="82" t="n">
+        <v>890.976</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="82" t="inlineStr">
+        <is>
+          <t>Jun 24</t>
+        </is>
+      </c>
+      <c r="B82" s="82" t="n">
+        <v>48824.268</v>
+      </c>
+      <c r="C82" s="82" t="n">
+        <v>51230.591</v>
+      </c>
+      <c r="D82" s="82" t="n">
+        <v>-2406.323</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="82" t="inlineStr">
+        <is>
+          <t>Jul 24</t>
+        </is>
+      </c>
+      <c r="B83" s="82" t="n">
+        <v>54550.711</v>
+      </c>
+      <c r="C83" s="82" t="n">
+        <v>55771.222</v>
+      </c>
+      <c r="D83" s="82" t="n">
+        <v>-1220.511</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="82" t="inlineStr">
+ 